--- a/workspaces/nasdaq_hourly_24hrs/roc/roc_3.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/roc/roc_3.xlsx
@@ -618,1887 +618,1887 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.0201</t>
+          <t>X ≈ -0.02007</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>23.09126950831948</v>
+        <v>17.66754466338924</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.482134006762209</v>
+        <v>3.148797433519164</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.69756195420652</v>
+        <v>8.81862428425206</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.99245536462239</v>
+        <v>8.112891001864767</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.98331328269785</v>
+        <v>0.677903261110103</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.480621304517172</v>
+        <v>-6.241043757802046</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.250867067420735</v>
+        <v>0.09516490094328134</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.529610993994538</v>
+        <v>-0.1822386308392367</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-11.14677985693942</v>
+        <v>-7.251475555702001</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-11.92089074481267</v>
+        <v>-8.023507662371586</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-11.65105450523218</v>
+        <v>-14.86794931708879</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-11.93292441051396</v>
+        <v>-8.033162195345469</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-5.390354611910119</v>
+        <v>-2.035725941095343</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>2.056524742797166</v>
+        <v>4.864645219961375</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1.400315354610747</v>
+        <v>-2.913591965618885</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>9.668263288033806</v>
+        <v>4.804276217905837</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>17.2136354787456</v>
+        <v>11.80008160037846</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>1.757135477331786</v>
+        <v>-2.560994852192309</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>9.654290792995461</v>
+        <v>11.91819294492311</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>17.52708177216917</v>
+        <v>19.24267702087243</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>16.98965094604899</v>
+        <v>18.70640856055982</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>9.231099280969367</v>
+        <v>11.497593228913</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>17.19853067246569</v>
+        <v>18.91611723177098</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>17.12775528565177</v>
+        <v>18.84596128170895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01873</t>
+          <t>X ≈ -0.01871</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-14.56329134521326</v>
+        <v>-11.54754860374576</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-11.0766243441736</v>
+        <v>-4.278415611015859</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.68492589464455</v>
+        <v>9.477149814773192</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.123804360286748</v>
+        <v>1.062346446778797</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-20.69417752028049</v>
+        <v>-22.23981261324438</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-13.41027815839356</v>
+        <v>-10.06621077716528</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-14.18377703899372</v>
+        <v>-18.49112873078934</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.357189664743416</v>
+        <v>-11.11861948288064</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-7.317513778846973</v>
+        <v>-11.08009257207848</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-29.42909509733148</v>
+        <v>-34.83342865940492</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-36.27955246829146</v>
+        <v>-34.57066609397869</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-15.21741329338425</v>
+        <v>-19.52990001497159</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-16.34294673465206</v>
+        <v>-20.65539473374248</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-16.56876517925009</v>
+        <v>-20.88221927302563</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-24.35409780208941</v>
+        <v>-21.54441934301838</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-9.516481935735207</v>
+        <v>-5.610321883263424</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-9.653106535943493</v>
+        <v>-5.745599703949757</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-16.89051845607089</v>
+        <v>-13.53017445664599</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>4.716552606626514</v>
+        <v>2.042788623281979</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>4.90475149013524</v>
+        <v>2.229989336655557</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>11.49998071813615</v>
+        <v>9.374033342493441</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>11.42753389060207</v>
+        <v>9.301056482340407</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>18.84634414129743</v>
+        <v>17.26821509979369</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>18.77610693400167</v>
+        <v>17.19760963335555</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.01737</t>
+          <t>X ≈ -0.01735</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>15</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>19.53057296135403</v>
+        <v>19.56377384460229</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12.5761629383236</v>
+        <v>12.6132895828944</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-8.725216815403797</v>
+        <v>-8.692931217681689</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.810175194990244</v>
+        <v>-2.775251594891046</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.174767069522481</v>
+        <v>-3.110437434780025</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>16.90151982146944</v>
+        <v>16.96673777016677</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9.504576296948947</v>
+        <v>9.570676510033202</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.039604269651889</v>
+        <v>-3.973222668287754</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.998945480957993</v>
+        <v>-3.932571694563222</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-4.770523892434305</v>
+        <v>-4.703216752963435</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-11.13906880176879</v>
+        <v>-11.07206802229454</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-11.4211880570432</v>
+        <v>-11.35381883741324</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-19.19014447064363</v>
+        <v>-19.12145625408957</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-12.77029843548493</v>
+        <v>-12.70128087572655</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-6.782309369617323</v>
+        <v>-6.712461356850881</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-12.84157076209161</v>
+        <v>-12.772387094042</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-12.97922116522193</v>
+        <v>-12.90983560039771</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.2215498947726218</v>
+        <v>0.2911323552830751</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-12.87595051847016</v>
+        <v>-12.80660144949391</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-6.034446198577825</v>
+        <v>-5.965258547250528</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-13.23956550779191</v>
+        <v>-13.16970849451484</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-13.31946028200645</v>
+        <v>-13.24946778431869</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-19.71347088046711</v>
+        <v>-19.64375438538423</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-13.12865497075872</v>
+        <v>-13.05880062305144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.01601</t>
+          <t>X ≈ -0.01599</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.648911578501533</v>
+        <v>-3.615882499637458</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>12.57520438338636</v>
+        <v>11.33841990352764</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.867949228251298</v>
+        <v>2.266639295740234</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.301197307917924</v>
+        <v>5.382901453783163</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.939373628177798</v>
+        <v>5.050193791665393</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>10.27014230993558</v>
+        <v>9.060218118516232</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9.504004970381679</v>
+        <v>8.294623847594004</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.9363677687755114</v>
+        <v>4.192359473164075</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5.12623569858517</v>
+        <v>8.064141252699287</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.357452555357071</v>
+        <v>7.297161994256086</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.4820957229797429</v>
+        <v>-0.08935101711264792</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.948018925193686</v>
+        <v>-4.199957891583708</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.235450724530409</v>
+        <v>2.345890427644491</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>11.32341112974006</v>
+        <v>9.794793968121709</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>6.514780202123951</v>
+        <v>5.306111407699298</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2.953627792429728</v>
+        <v>2.063648972339905</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>2.820737646786938</v>
+        <v>1.930664534638304</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>11.03511101316718</v>
+        <v>9.50506221171203</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>11.25418566583722</v>
+        <v>9.723439270594845</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>7.28274235840729</v>
+        <v>6.071451431979327</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>6.742311740653214</v>
+        <v>5.531304898681576</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>6.668454794768358</v>
+        <v>5.457187899480694</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>6.945143334365802</v>
+        <v>5.733206963102546</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>6.871345029238817</v>
+        <v>5.659148094894881</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01465</t>
+          <t>X ≈ -0.01463</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1100510337710219</v>
+        <v>-0.08416270679762761</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-18.8579134639275</v>
+        <v>-23.39108264843014</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-10.93216342623119</v>
+        <v>-17.29273518540576</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-7.963570444598439</v>
+        <v>-14.2400584876063</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.9652774185590758</v>
+        <v>-4.772637686385409</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.902605443471927</v>
+        <v>-0.745460777270992</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>9.503242780766421</v>
+        <v>12.12013618599818</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>9.228866364069717</v>
+        <v>4.192033549265417</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>9.273431065656297</v>
+        <v>4.235036154461817</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>12.19383740439945</v>
+        <v>7.296678173339942</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>8.782264326067633</v>
+        <v>11.40327351736693</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.816196985844833</v>
+        <v>7.296408549941518</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.696687523562623</v>
+        <v>6.178979550412897</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2157560959561877</v>
+        <v>2.125546641221021</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2.821011782867807</v>
+        <v>5.305881886907123</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>3.415341872757352</v>
+        <v>5.900300294987403</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.4131437543326371</v>
+        <v>1.930597915755257</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-4.214870431208261</v>
+        <v>-2.012463770872984</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-4.00042751334616</v>
+        <v>-1.797576834799784</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.1157130729603111</v>
+        <v>2.229895196515308</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.6583711910458021</v>
+        <v>1.688608897735051</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2.9669618772609</v>
+        <v>5.457134978535827</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>6.945109767183347</v>
+        <v>9.578152349648676</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.5360623781676495</v>
+        <v>1.812994248741042</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01329</t>
+          <t>X ≈ -0.01327</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>39</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>8.993505041945397</v>
+        <v>11.57926529775425</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.19538999675775</v>
+        <v>13.78597905980988</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>12.27625249585196</v>
+        <v>14.8733352823313</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.453339941863916</v>
+        <v>9.046584994276927</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>16.28465491662897</v>
+        <v>18.91208127725919</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>11.38445740052541</v>
+        <v>14.00562654327796</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10.60155241101878</v>
+        <v>10.66969630488088</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.664238542090523</v>
+        <v>5.284291787000384</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.953375245059632</v>
+        <v>-2.332575534621547</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-5.746227892602803</v>
+        <v>-3.123687247915697</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.470706056998999</v>
+        <v>-5.401569997234972</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-8.310691605407449</v>
+        <v>-8.241187558537334</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.7630566622085482</v>
+        <v>-1.722194048791145</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>8.210970764539091</v>
+        <v>8.282208378301462</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2.421042774672266</v>
+        <v>2.493096433239174</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.4736824272017301</v>
+        <v>0.5450721568741628</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>5.454347366596835</v>
+        <v>5.525953477823379</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>4.316380466159558</v>
+        <v>2.858597444650059</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.5868069598424128</v>
+        <v>-2.040190676468967</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>2.160658466165188</v>
+        <v>0.714109927257752</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.9429942724288622</v>
+        <v>-2.405713592364727</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.019201030864281</v>
+        <v>-0.9492091622049728</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.818454079277863</v>
+        <v>1.888173380254969</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.8209626630679239</v>
+        <v>-0.7511083153594811</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01193</t>
+          <t>X ≈ -0.01191</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.5536382323128</v>
+        <v>4.466193948438466</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.191696652979424</v>
+        <v>4.104021961489643</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.683594023578152</v>
+        <v>2.594428176045767</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-13.19885221217925</v>
+        <v>-14.75328315903293</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.817065524217227</v>
+        <v>-4.031342570275555</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-5.30193587154222</v>
+        <v>-6.589522247194004</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.963149870886774</v>
+        <v>0.9023065960506074</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.207618637719577</v>
+        <v>0.6061132038325709</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.246947763183854</v>
+        <v>0.640542193751763</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2374884770020671</v>
+        <v>-2.943082178993947</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.653403144200254</v>
+        <v>-5.431902101491239</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2440301180155018</v>
+        <v>-1.340493852599501</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.30355133490729</v>
+        <v>3.051436419079579</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.778836105148507</v>
+        <v>2.832413941382207</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3.099969951827752</v>
+        <v>2.153420161640831</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.683320885761972</v>
+        <v>-2.780255726158273</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.820749787290204</v>
+        <v>-2.91792666118247</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.7679926734689673</v>
+        <v>-0.2547686324400473</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.596011209597236</v>
+        <v>-0.03362105596200848</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.08420209084600572</v>
+        <v>-2.614894845381023</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.241823678029547</v>
+        <v>-0.398871562290914</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.5343913178652429</v>
+        <v>-3.252475258354401</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.259909214238256</v>
+        <v>-1.315963573591269</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.3358621779674422</v>
+        <v>-1.392133956386921</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01057</t>
+          <t>X ≈ -0.01055</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>52</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-13.21361741500661</v>
+        <v>-13.18489904506225</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-5.897288746840367</v>
+        <v>-5.867706206113155</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-11.15289502852453</v>
+        <v>-11.12852972848809</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.301397265974771</v>
+        <v>-2.267975777616932</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.072233493673565</v>
+        <v>3.139643488443213</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.5691643746563386</v>
+        <v>-0.5040938608495011</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.5749001863272554</v>
+        <v>0.6409801057836617</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.616624369423192</v>
+        <v>-1.550578461803106</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3401402374705</v>
+        <v>0.4067473122201832</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.346012306579723</v>
+        <v>-2.279368633224841</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.676198600935884</v>
+        <v>3.744451293033777</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.4351444531589763</v>
+        <v>-0.3677084150454419</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.195509808560182</v>
+        <v>4.264312725107381</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.057219144250347</v>
+        <v>2.126315828632961</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.436589671516899</v>
+        <v>-2.366698312010513</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-7.601567018212826</v>
+        <v>-7.532335223086847</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-3.897870533507835</v>
+        <v>-3.828428042962095</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-9.762623885588248</v>
+        <v>-9.696103997358527</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-7.626844818368212</v>
+        <v>-7.562253679207728</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-3.601319474197972</v>
+        <v>-3.534287144100681</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.302573663012069</v>
+        <v>-0.2328105203982105</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.543290567150471</v>
+        <v>1.61382648761289</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>1.818428552901381</v>
+        <v>1.888150783259917</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.1799370220418552</v>
+        <v>-0.1100826743345777</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.009206</t>
+          <t>X ≈ -0.009192</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>63</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.440574060206195</v>
+        <v>-4.409118615981065</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.773149731047646</v>
+        <v>-4.742983849631429</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.469842937334931</v>
+        <v>-1.436394556648516</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12.02748812769006</v>
+        <v>12.07485626299633</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.191042735290438</v>
+        <v>2.257940474685952</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.957000912528464</v>
+        <v>4.023553565231403</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.607894451105771</v>
+        <v>1.673969027260824</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.491241281245017</v>
+        <v>4.559279805871178</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.534746190220496</v>
+        <v>4.602734622169969</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.765934242426134</v>
+        <v>3.834556904229281</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.8774934890729327</v>
+        <v>0.9448590527281198</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>10.09222984305934</v>
+        <v>10.15970165989405</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.808142927476815</v>
+        <v>5.876945224727656</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>8.75501206311538</v>
+        <v>8.824125001214284</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>4.933826438990629</v>
+        <v>5.003732914180311</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>7.113749025326051</v>
+        <v>7.183011584994389</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>5.397323661284418</v>
+        <v>5.466780848139635</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>8.462187513417689</v>
+        <v>8.534558420182123</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>5.508463408120953</v>
+        <v>5.581453204098104</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>5.69684325339567</v>
+        <v>5.769864331375956</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>3.570322301501399</v>
+        <v>3.642607755458727</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.909313900182553</v>
+        <v>1.979987815111876</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>3.771368626892802</v>
+        <v>3.841090856899037</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>5.284043441937818</v>
+        <v>5.353897789645096</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.007846</t>
+          <t>X ≈ -0.007831</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>68</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-16.13914347721316</v>
+        <v>-16.1109490491974</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.242362474488537</v>
+        <v>-6.212807187438656</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-15.00662985040942</v>
+        <v>-14.98656929947697</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-9.880052167099471</v>
+        <v>-9.853889919514508</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-10.24951065813042</v>
+        <v>-10.19035059292052</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-5.671132159921768</v>
+        <v>-5.606968757575132</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-10.84477170169036</v>
+        <v>-10.77767879372093</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-9.662445068711584</v>
+        <v>-9.598297431180733</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-7.319419263085621</v>
+        <v>-8.095979790103591</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-9.556674842776545</v>
+        <v>-10.34778065067076</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-10.75125049394237</v>
+        <v>-11.5417003700623</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-9.568119931129608</v>
+        <v>-10.3546392777722</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-10.69299994458585</v>
+        <v>-10.62427114613556</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-13.85139458282379</v>
+        <v>-13.78236772745589</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-11.57804570752371</v>
+        <v>-11.50819683899989</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-9.520209926779096</v>
+        <v>-9.450996569586572</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-9.65730418259529</v>
+        <v>-9.587884817221315</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-9.76196186823222</v>
+        <v>-9.695581350109229</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-9.546164435758755</v>
+        <v>-9.483080889968242</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-13.7686268118721</v>
+        <v>-13.70844511084995</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-11.37751645059905</v>
+        <v>-11.3151101143831</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-8.517955491564742</v>
+        <v>-8.450737955308526</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-6.77605537197821</v>
+        <v>-6.706338763177989</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-3.912968696250431</v>
+        <v>-3.843114348543153</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.006485</t>
+          <t>X ≈ -0.006471</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.368615012619621</v>
+        <v>-0.9534678782475723</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.52655159974362</v>
+        <v>-3.952230715860054</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>6.900249718897918</v>
+        <v>6.16743556616732</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.541732458498707</v>
+        <v>2.791932565658854</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.177591846216075</v>
+        <v>1.567583492195467</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.841285079661134</v>
+        <v>7.085603825216054</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.247696594099956</v>
+        <v>5.427922396836273</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.057164183679518</v>
+        <v>4.263755837002591</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4.098978205406702</v>
+        <v>4.307045441173855</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.416966339859165</v>
+        <v>3.5389699247674</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.605578530928476</v>
+        <v>4.703873024677115</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5848487716785016</v>
+        <v>1.754873608900908</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.292610974526305</v>
+        <v>1.524685758111822</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.7581336067297357</v>
+        <v>0.4137037324615136</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.414866923781915</v>
+        <v>-0.2418375679659945</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.652591314544985</v>
+        <v>-1.430779247829847</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.03995940202469228</v>
+        <v>0.2175479468252348</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.1445971518757787</v>
+        <v>0.1130642021571902</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-2.676354772626887</v>
+        <v>-2.347045509234825</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.2578434654843562</v>
+        <v>0.5154610772154058</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.201215405933532</v>
+        <v>-0.9193168804718326</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.3608230924615796</v>
+        <v>-0.1026147530712151</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.837730335574619</v>
+        <v>-2.505980387960079</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.914587692472772</v>
+        <v>-2.582610146862486</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.005123</t>
+          <t>X ≈ -0.005111</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4.634415775641443</v>
+        <v>4.055576995582577</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.57045456574685</v>
+        <v>4.120434517740378</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.571101270695799</v>
+        <v>4.154703164918047</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7.209734846030081</v>
+        <v>7.128833659656287</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.393050774776185</v>
+        <v>6.055203346524166</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.135413468343849</v>
+        <v>4.769210212983239</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.040760933935395</v>
+        <v>2.519907779288388</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.214709818308236</v>
+        <v>3.717054353829297</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.802512886131915</v>
+        <v>2.283501497854019</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.026254115401599</v>
+        <v>0.7688972927700917</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>4.483676214213737</v>
+        <v>3.687494989448702</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.933138356850193</v>
+        <v>4.147410053009814</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.350735685710312</v>
+        <v>2.288957880546718</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.6738356950798376</v>
+        <v>-0.1469963127735525</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.7383381649798011</v>
+        <v>-0.06364585504510245</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.6079165991593101</v>
+        <v>-0.2096083305053824</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.931776504422665</v>
+        <v>1.874567465116662</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.825582251076682</v>
+        <v>1.770716723142996</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.500044507341748</v>
+        <v>3.466963393082978</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>3.69048458458807</v>
+        <v>3.654692460469747</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>5.332772939591102</v>
+        <v>5.335058724159133</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>6.718107996409294</v>
+        <v>6.740143737501405</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>8.160829863807898</v>
+        <v>7.754914260627217</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>5.898109019507409</v>
+        <v>5.459717895465566</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.003763</t>
+          <t>X ≈ -0.00375</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.424537358511877</v>
+        <v>0.120059524691662</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.41375036412439</v>
+        <v>-1.839801308673856</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-6.618035905119761</v>
+        <v>-5.992985723977036</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.689715838303073</v>
+        <v>-5.62883601525489</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.059329394927985</v>
+        <v>-5.965631905074574</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.461807035945277</v>
+        <v>-0.9018028885311367</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.796549028546593</v>
+        <v>-2.762525954438473</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.8766468280634001</v>
+        <v>-0.8776008962031696</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.466327321053562</v>
+        <v>2.413160795400948</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7540745200578414</v>
+        <v>-1.077748830321951</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.231781716876938</v>
+        <v>-3.511343594298438</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-5.165907943497253</v>
+        <v>-5.416685421731607</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.891798729684126</v>
+        <v>-2.212070535912524</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.769253411868974</v>
+        <v>-3.7396418348089</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-4.439387633235114</v>
+        <v>-4.402339270598887</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.081738874343564</v>
+        <v>-1.095778395367205</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.871607629854481</v>
+        <v>-2.857757801641213</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.87471423226684</v>
+        <v>-1.879028319519534</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.656727739511773</v>
+        <v>-1.663164709012278</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.069883843164341</v>
+        <v>0.6979437690348718</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.02787117952384222</v>
+        <v>-0.3906764047900566</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.20829959304394</v>
+        <v>-1.552886863688961</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.3780257731337997</v>
+        <v>-0.7319737690908283</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.6792995379793823</v>
+        <v>-1.029815115806578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.002401</t>
+          <t>X ≈ -0.00239</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.152393393709644</v>
+        <v>2.417970304571213</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.644982088982573</v>
+        <v>-4.349512250047432</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.809580626530199</v>
+        <v>-3.517371004764449</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.8649743814745179</v>
+        <v>-1.20217778164271</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.8863434780372543</v>
+        <v>0.7345468539762265</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.595522666626714</v>
+        <v>2.057657934156616</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.822319179484907</v>
+        <v>1.664560183926348</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.163350146290483</v>
+        <v>1.008200419335957</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.6969088545887416</v>
+        <v>-0.6291591507186212</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.191306313551515</v>
+        <v>1.255528469086457</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.466177360465956</v>
+        <v>1.529235661014461</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.710057402551499</v>
+        <v>2.76738337397483</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3189745539977125</v>
+        <v>-0.2488161488440639</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.5409887008332674</v>
+        <v>-0.4691901248225392</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2.990071821614315</v>
+        <v>3.04700564648504</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.300358772309245</v>
+        <v>1.364457155265114</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.503977283899644</v>
+        <v>-1.425939159800691</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.609486855515051</v>
+        <v>-1.531239206518507</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.774220015143648</v>
+        <v>-1.696164345226123</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.8221751024010047</v>
+        <v>-0.7502955684492036</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.7575986821965657</v>
+        <v>-0.9129025708392575</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.07049134250315348</v>
+        <v>-0.2282922584841955</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.9407543439599593</v>
+        <v>-1.094501956648436</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.6350162939154487</v>
+        <v>-0.7901060729895022</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.001041</t>
+          <t>X ≈ -0.00103</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.229227980403316</v>
+        <v>-1.062997009497558</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.66652514220813</v>
+        <v>2.478295003356656</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.07271526381111215</v>
+        <v>-0.5797442017594463</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.04929754545415221</v>
+        <v>-0.1388610491746434</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3161655734188429</v>
+        <v>-1.121477697705799</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.063831791149788</v>
+        <v>-3.522532979168297</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.07355500481251909</v>
+        <v>-0.4131010650138265</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.5296356321726208</v>
+        <v>-0.5073604081180747</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.138595634941154</v>
+        <v>-1.112117210410844</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.6963537103558508</v>
+        <v>0.7072219445187997</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3319675672214046</v>
+        <v>-0.3133384166151103</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.9369580506601096</v>
+        <v>-0.915478673645886</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.103271519649816</v>
+        <v>-0.09361643930606078</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.933275183102765</v>
+        <v>-2.902124026976772</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-4.897795512226672</v>
+        <v>-4.530567048993902</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-4.958786499206347</v>
+        <v>-4.587690572222499</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.808845413463885</v>
+        <v>-2.455134880273206</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-3.567010561342279</v>
+        <v>-3.533646009758563</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-2.044437366300201</v>
+        <v>-2.022489828995035</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-3.164298087646557</v>
+        <v>-3.135321189057237</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-3.380561356576571</v>
+        <v>-3.354757294062807</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-5.418992065947755</v>
+        <v>-5.053979878848459</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-5.144216899465626</v>
+        <v>-5.104180491041809</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-2.932576539387753</v>
+        <v>-2.907285471537882</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0003204</t>
+          <t>X ≈ 0.0003301</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.9334173454899</v>
+        <v>1.606569734026806</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.8540721416903168</v>
+        <v>1.274021125241731</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4140966388761456</v>
+        <v>1.087435457319117</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.543481633919242</v>
+        <v>-0.873282307470312</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.147687951321814</v>
+        <v>-3.205346153363799</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.072755623855727</v>
+        <v>-3.519491824720269</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.603591485662271</v>
+        <v>-2.04442543252685</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.880661203659201</v>
+        <v>-2.571706613921521</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.594122739432969</v>
+        <v>-1.282084138638801</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.3729524564333886</v>
+        <v>-0.1613577240854411</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.09845998787270105</v>
+        <v>0.1129193073554475</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.37359851689191</v>
+        <v>-1.163532004207703</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.496009470990799</v>
+        <v>-2.282563674763047</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.968988129297124</v>
+        <v>-1.751996586299185</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.1321339796413028</v>
+        <v>-0.1604900533872495</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.785647257982625</v>
+        <v>-1.817122384365931</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-3.420505976577118</v>
+        <v>-3.452659961827244</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-3.525302313833613</v>
+        <v>-3.309277670727738</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-3.809116479490847</v>
+        <v>-3.597204795634809</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.872321966423101</v>
+        <v>-3.664031880117015</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.666209422456454</v>
+        <v>-2.454780078296118</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-3.494155464640571</v>
+        <v>-3.533132305369378</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-3.219380298158441</v>
+        <v>-3.008031026471315</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-3.545321637426817</v>
+        <v>-3.3344898461106</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.001681</t>
+          <t>X ≈ 0.00169</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.063880375092445</v>
+        <v>2.322297698113694</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.769844458866253</v>
+        <v>3.25434860443815</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.546766469714989</v>
+        <v>1.692450404365808</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.13682455592339</v>
+        <v>2.507876108646705</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.024318281758909</v>
+        <v>2.67974106828602</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.963909796144669</v>
+        <v>2.617210280021432</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.445537312363086</v>
+        <v>2.099089312224301</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.139492317984079</v>
+        <v>0.7996122332176725</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.462127311433186</v>
+        <v>1.860741021236763</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.426877702739908</v>
+        <v>1.084306617543554</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.130975853044276</v>
+        <v>2.632647595977744</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.719315885965273</v>
+        <v>1.07772215675007</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.8489769820766426</v>
+        <v>0.2043277356141289</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.138559869308587</v>
+        <v>0.4900922772794658</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.7333578448771974</v>
+        <v>0.2396802610977531</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.842926839553847</v>
+        <v>1.499740009462236</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.122162249595981</v>
+        <v>1.620859220685297</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.9879383917649633</v>
+        <v>0.4941356347349739</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.4338161352499981</v>
+        <v>-0.05739189380324916</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>2.165201996861263</v>
+        <v>1.664071382954248</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.8498305548679426</v>
+        <v>0.5097924784153847</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.445433224305447</v>
+        <v>0.9454554684129093</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.1777919383454289</v>
+        <v>-0.05884219762164378</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.4122882184037664</v>
+        <v>-0.6461834022516015</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.003043</t>
+          <t>X ≈ 0.003051</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.311826654661473</v>
+        <v>-3.450719145757652</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.8575858697027456</v>
+        <v>-0.6143586544227304</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.893558545723238</v>
+        <v>1.478410662385521</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.2142355035759138</v>
+        <v>0.06107525073997522</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.948874862658002</v>
+        <v>3.94944159425156</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.344147228127355</v>
+        <v>1.314974393414644</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.4720972149195859</v>
+        <v>-0.1595794017134722</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.791554223496753</v>
+        <v>-1.489744604261759</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.448099647070379</v>
+        <v>-1.801513887027525</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.7803115285677507</v>
+        <v>-0.1069631531961051</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.899952997558401</v>
+        <v>-1.241666295439835</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.4344237398141928</v>
+        <v>0.2426693187772671</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5090698486704213</v>
+        <v>0.181408183120439</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.7298979113558701</v>
+        <v>-0.036473387589119</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.342095229174916</v>
+        <v>0.3644421964855979</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.2511199419017487</v>
+        <v>0.9570528374634932</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.214928345654918</v>
+        <v>2.937242689456475</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.410644230258939</v>
+        <v>2.130207575199407</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3.025368791792154</v>
+        <v>3.757185278026036</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.9833916083916066</v>
+        <v>-0.2951169128894122</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.575543066340607</v>
+        <v>-1.897733752233655</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.301847772332877</v>
+        <v>-1.620222823183347</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.677422256200394</v>
+        <v>-1.345748110701294</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.452664294769605</v>
+        <v>-2.128294144843302</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.004404</t>
+          <t>X ≈ 0.004411</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>219</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.4167546800466724</v>
+        <v>0.4500111775331703</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.737325621891671</v>
+        <v>-1.703657094142542</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.9143340747903537</v>
+        <v>1.404363605282754</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.2541508584426637</v>
+        <v>0.2367206870759304</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.983288042884581</v>
+        <v>-1.462932664359293</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-3.614509565417393</v>
+        <v>-3.094348408077124</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.023508298053592</v>
+        <v>-2.95708914227621</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5743627215199609</v>
+        <v>-0.5076087988206694</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.740715174052859</v>
+        <v>1.807424785616632</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.785438782741195</v>
+        <v>2.853060887232289</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.059798049856532</v>
+        <v>3.127120529394212</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.599263165839346</v>
+        <v>4.666922903598248</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.202522189244064</v>
+        <v>3.997940191995419</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.988716143419026</v>
+        <v>3.776555589442381</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5.614012927411856</v>
+        <v>5.391618998710577</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>5.301092800093777</v>
+        <v>4.622109072198228</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>4.253757096812436</v>
+        <v>3.857128279440666</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>4.605394685283386</v>
+        <v>4.214645380049056</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>6.191380861913807</v>
+        <v>5.799406059355839</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.638698630136986</v>
+        <v>3.25136000596747</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>6.748466257668703</v>
+        <v>6.361781874531154</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>6.67251120202608</v>
+        <v>6.285935913122053</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>5.577423354809603</v>
+        <v>5.190547611905473</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>4.131619001842502</v>
+        <v>3.744852344983578</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.005765</t>
+          <t>X ≈ 0.005771</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.686858943273833</v>
+        <v>-3.321865863653109</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.7260411656859631</v>
+        <v>-0.3387078656569074</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.126854985787283</v>
+        <v>0.873910983777435</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.732393075571999</v>
+        <v>1.489079936936434</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.7085190505192713</v>
+        <v>0.4903064486148736</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.878289736957782</v>
+        <v>2.673123893405347</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.855118111534573</v>
+        <v>-2.085782037554168</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.476766855360871</v>
+        <v>-1.702736019375529</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.091732107446418</v>
+        <v>-2.322074912181925</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.866416687384039</v>
+        <v>-3.095853364639694</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.592057420268702</v>
+        <v>-2.821793722477771</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.872000492911802</v>
+        <v>-3.101405902347011</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.7030459266713649</v>
+        <v>-0.9092215021209356</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-4.488471492614188</v>
+        <v>-5.11984595490047</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-4.495591494485957</v>
+        <v>-5.114574848496154</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-2.585447464202048</v>
+        <v>-2.526493608913221</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-2.057289502721829</v>
+        <v>-1.996564953695078</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.148985359328513</v>
+        <v>1.627794506070828</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-2.608401411514471</v>
+        <v>-2.152969711286943</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.09685430463572</v>
+        <v>-0.6390509529366071</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.333455220141111</v>
+        <v>2.81840287909737</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.9329968532402617</v>
+        <v>1.409223584354926</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.441234602794196</v>
+        <v>-0.9829683698296847</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.1926726308043811</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.007125</t>
+          <t>X ≈ 0.007132</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-5.976366932111539</v>
+        <v>-6.331942979931085</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-5.378723295887887</v>
+        <v>-4.854254689606158</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-4.948811811463209</v>
+        <v>-4.473408240336134</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.80252992840461</v>
+        <v>-3.377097375917231</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-5.099824134941834</v>
+        <v>-4.619520418403489</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-7.711911703894138</v>
+        <v>-7.155652146936248</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-4.75588542054065</v>
+        <v>-5.205302967399767</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.238366801519724</v>
+        <v>-2.763616702335739</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.3415439163748601</v>
+        <v>-0.9176649437790232</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.113789868434473</v>
+        <v>-1.688980517409</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.630735489729112</v>
+        <v>-4.130018277844449</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.465674730735735</v>
+        <v>3.738124628906313</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.348336076442848</v>
+        <v>2.622163022879676</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>9.651944945355488</v>
+        <v>7.843279719677028</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>9.941984861975165</v>
+        <v>8.090968940832305</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>10.55436809561719</v>
+        <v>9.586388074291335</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>8.551115522963542</v>
+        <v>7.642406002248961</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>8.446132106868305</v>
+        <v>7.542365605647419</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>7.727675830547788</v>
+        <v>7.767829834701807</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>9.783878504672799</v>
+        <v>8.876100562214859</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>11.10983697417961</v>
+        <v>11.06082712152155</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>10.09930247928467</v>
+        <v>10.07589025102165</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>13.17781596352381</v>
+        <v>13.07763769077638</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>13.10187462425528</v>
+        <v>13.00180543755315</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.008486</t>
+          <t>X ≈ 0.008492</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.72311580007247</v>
+        <v>-2.705041053470069</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.747148921086662</v>
+        <v>0.9075734294222002</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6741951006693654</v>
+        <v>-1.5317098149796</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4153899751443575</v>
+        <v>-1.252750801252773</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.156999518141518</v>
+        <v>0.3874921573712413</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5814349885594297</v>
+        <v>-1.389106871434386</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.329914598982128</v>
+        <v>-2.170406717525928</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.259311712992755</v>
+        <v>1.495656064895925</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.557908060526415</v>
+        <v>-2.397779818163109</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.398606752461767</v>
+        <v>-1.19933764412886</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.8073817136624086</v>
+        <v>1.044521321070235</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.397311309520148</v>
+        <v>-1.197793297280768</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.535370206434841</v>
+        <v>-2.334982107438783</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-5.673014813798403</v>
+        <v>-4.544562631325064</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-3.439435766322077</v>
+        <v>-2.240993572698912</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-3.228410236657588</v>
+        <v>-3.611730392692401</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-5.304251503622019</v>
+        <v>-5.723239487874864</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-2.496613560493998</v>
+        <v>-2.875718997690541</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-2.280490397562183</v>
+        <v>-3.654966247034238</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-4.03519417475723</v>
+        <v>-3.860173065147819</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-4.578394583755241</v>
+        <v>-5.392818243014787</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-5.625223425805615</v>
+        <v>-6.458763214325025</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-7.292195832139015</v>
+        <v>-8.164486521644861</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-7.368137171407433</v>
+        <v>-8.240318774868229</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.009848</t>
+          <t>X ≈ 0.009851</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>70</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.6299332407959568</v>
+        <v>-0.7605469662306135</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>8.831081003993233</v>
+        <v>8.86530285852421</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.978370179238134</v>
+        <v>6.014360007149953</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.413587095923681</v>
+        <v>2.450426440321586</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.468610310797089</v>
+        <v>3.534889920071507</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.497401300631431</v>
+        <v>6.563411175042418</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.883949168782472</v>
+        <v>2.950954586557643</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.45118240822201</v>
+        <v>5.518486867794572</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.910910719076853</v>
+        <v>6.978133673448212</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.137075308307423</v>
+        <v>7.62861344254631</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.142232559469292</v>
+        <v>2.210138468449038</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.857936770831181</v>
+        <v>1.92615324360542</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.436465469619229</v>
+        <v>6.505997435799777</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>11.92020932992531</v>
+        <v>13.41341459209649</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>5.580135816356282</v>
+        <v>5.635152576005673</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>4.746624437406204</v>
+        <v>4.801955395697505</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.469673600400171</v>
+        <v>8.942413251240325</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>5.93611875573346</v>
+        <v>5.99392314998741</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.295099061522379</v>
+        <v>3.364579427571556</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>6.339285714285708</v>
+        <v>6.408568094682437</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>4.367513876716338</v>
+        <v>4.437450498144948</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>5.720130249645102</v>
+        <v>5.790175965307363</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>4.566333987555858</v>
+        <v>4.636079249217943</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>7.347535505430237</v>
+        <v>7.417389853137557</v>
       </c>
     </row>
     <row r="29">
@@ -2508,79 +2508,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.064007466893869</v>
+        <v>2.901896007761138</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.55361853644802</v>
+        <v>-1.777206212418896</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.555885853803318</v>
+        <v>5.457672589141765</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.103614865230917</v>
+        <v>9.068040000770878</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.73136902551461</v>
+        <v>8.725248197970842</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.484655425487645</v>
+        <v>7.457688024059806</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.882401168173544</v>
+        <v>3.815193936542776</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.020284598958085</v>
+        <v>4.97400552616628</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2136737700245774</v>
+        <v>0.6781686165035623</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4341609365282935</v>
+        <v>-0.09649739209611141</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.980506610302768</v>
+        <v>5.955410041146081</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.837328065471212</v>
+        <v>-2.98573521751441</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.109758980948442</v>
+        <v>-1.215597557422406</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.8972375789489959</v>
+        <v>-1.426174438489859</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1.294421530642005</v>
+        <v>2.246005025254242</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.4609101516919765</v>
+        <v>1.392866917441566</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.183959314685907</v>
+        <v>2.702974145093386</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>4.507547327162044</v>
+        <v>5.491433168220311</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.295099061522471</v>
+        <v>4.275552512457679</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.8035714285714235</v>
+        <v>0.1145722354691898</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-4.203914694712218</v>
+        <v>-3.326524657134456</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>4.291558821073785</v>
+        <v>5.29328155536944</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.2806197018415659</v>
+        <v>1.219930180894963</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>1.633249791144529</v>
+        <v>2.593373289990517</v>
       </c>
     </row>
     <row r="30">
@@ -2593,76 +2593,76 @@
         <v>36</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>7.444052450790629</v>
+        <v>7.477326743109458</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.195499140922287</v>
+        <v>-1.161826132308946</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.901992812428055</v>
+        <v>2.937347236096542</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.348992918201581</v>
+        <v>-3.312799200782678</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.964029632626378</v>
+        <v>-0.8983566027307006</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7938156086525723</v>
+        <v>-0.7283410056663016</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.29996422227287</v>
+        <v>-4.233572171122923</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-7.351352723767917</v>
+        <v>-7.284617471852485</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-15.60291234312528</v>
+        <v>-15.53620597431778</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-16.3795728520669</v>
+        <v>-16.31194674852646</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-21.62545541335507</v>
+        <v>-21.55812893476804</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-10.85559036550639</v>
+        <v>-10.78791938689245</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-14.73313975276493</v>
+        <v>-14.66413962251998</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-6.652945584902803</v>
+        <v>-6.58366752007008</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-7.356372120151647</v>
+        <v>-7.244635915822826</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-6.761312070530309</v>
+        <v>-6.655899190224133</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-12.45096132023479</v>
+        <v>-12.31288325377735</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-12.55594473632999</v>
+        <v>-12.40924866308196</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-9.562043795620433</v>
+        <v>-9.492563429571298</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-9.375</v>
+        <v>-9.305717619603271</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-7.140422631220218</v>
+        <v>-7.070486009791566</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-7.216377686862828</v>
+        <v>-7.146331971200667</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-4.163824742602877</v>
+        <v>-4.094079480940792</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-4.239766081871345</v>
+        <v>-4.169911734164067</v>
       </c>
     </row>
     <row r="31">
@@ -2675,76 +2675,76 @@
         <v>37</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.09417320464911</v>
+        <v>4.127447496967939</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.822218805857439</v>
+        <v>3.85589181447078</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.740507910287185</v>
+        <v>7.775862333955672</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.371427731280846</v>
+        <v>4.40762144869975</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.320221064332806</v>
+        <v>-1.254548034437128</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.740927480249645</v>
+        <v>-3.675452877263375</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.7177537245068564</v>
+        <v>0.7841457756568033</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.4866149158778086</v>
+        <v>0.5533501677932406</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.230833683603123</v>
+        <v>3.297540052410625</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2298991509058439</v>
+        <v>-0.162273047365403</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.402449684725418</v>
+        <v>5.469776163312446</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.234633787265409</v>
+        <v>-0.1669628086514763</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.280356581097493</v>
+        <v>1.349356711342452</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.011583933173611</v>
+        <v>1.080861998006334</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.6746904384699661</v>
+        <v>-2.264178723313712</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.0796303888485852</v>
+        <v>-1.638181243444407</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-2.91642678570021</v>
+        <v>-4.506411641050889</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>2.383995203609878</v>
+        <v>0.7467372236437271</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.600118366541729</v>
+        <v>2.669598732590863</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>5.48986486486487</v>
+        <v>5.559147245261599</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>4.946664455866916</v>
+        <v>5.016601077295569</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.5346960051811038</v>
+        <v>-0.4646502895189428</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>5.145484566706436</v>
+        <v>5.215229828368521</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>2.36684052473526</v>
+        <v>2.436694872442537</v>
       </c>
     </row>
     <row r="32">
@@ -2757,76 +2757,76 @@
         <v>24</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>8.825878594249147</v>
+        <v>8.859152886567976</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.324036412938213</v>
+        <v>4.357709421551554</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.05100261551874</v>
+        <v>7.086357039187227</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.170542635658855</v>
+        <v>2.206736353077758</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-14.86139381603174</v>
+        <v>-14.79572078613607</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-10.50756253635831</v>
+        <v>-10.44208793337204</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-2.947095335079098</v>
+        <v>-2.880703283929151</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-3.225649980597602</v>
+        <v>-3.15891472868217</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7.350800582241575</v>
+        <v>-7.284094213434074</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-8.124635993011005</v>
+        <v>-8.057009889470564</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-12.0169433925624</v>
+        <v>-11.94961691397537</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-16.46270396270391</v>
+        <v>-16.39503298408997</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-5.087195181191106</v>
+        <v>-5.018195050946147</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-5.308551992225517</v>
+        <v>-5.239273927392794</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-1.80081656459609</v>
+        <v>-1.730750558306624</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-1.205756514974709</v>
+        <v>-1.136363636363633</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>6.993483124209632</v>
+        <v>7.063052559992158</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>2.721833041447695</v>
+        <v>2.791545189504319</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2.937956204379567</v>
+        <v>3.007436570428702</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-1.041666666666728</v>
+        <v>-0.9723842862699996</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-5.75153374233129</v>
+        <v>-5.681597120902637</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-1.660822131307292</v>
+        <v>-1.590776415645131</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>6.947286368508223</v>
+        <v>7.017031630170308</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>11.03801169590644</v>
+        <v>11.10786604361372</v>
       </c>
     </row>
     <row r="33">
@@ -2839,76 +2839,76 @@
         <v>25</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>22.32587859424929</v>
+        <v>22.35915288656812</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>17.99070307960488</v>
+        <v>18.02437608821822</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>16.55100261551874</v>
+        <v>16.58635703918723</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.837209302325668</v>
+        <v>3.873403019744572</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.5280604826984572</v>
+        <v>-0.4623874528027798</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.340895869691707</v>
+        <v>-4.275421266705436</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.886237998254352</v>
+        <v>2.952630049404299</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-9.392316647264266</v>
+        <v>-9.325581395348834</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-9.350800582241632</v>
+        <v>-9.28409421343413</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-14.12463599301109</v>
+        <v>-14.05700988947065</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-5.850276725895753</v>
+        <v>-5.782950247308726</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-2.129370629370619</v>
+        <v>-2.061699650756687</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-11.25386184785777</v>
+        <v>-11.18486171761281</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.5247813411079321</v>
+        <v>0.594059405940655</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.1341498979294471</v>
+        <v>-0.06408389163998152</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-3.539089848308038</v>
+        <v>-3.469696969696962</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.326816457543089</v>
+        <v>4.396385893325615</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.22183304144778</v>
+        <v>4.291545189504404</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>8.437956204379567</v>
+        <v>8.507436570428702</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>8.625000000000085</v>
+        <v>8.694282380396814</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>12.08179959100205</v>
+        <v>12.1517362124307</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>12.00584453535949</v>
+        <v>12.07589025102165</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>4.280619701841566</v>
+        <v>4.350364963503651</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.2046783625730981</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
     <row r="34">
@@ -2921,76 +2921,76 @@
         <v>15</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>32.99254526091582</v>
+        <v>33.02581955323465</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>19.32403641293821</v>
+        <v>19.35770942155155</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>11.2176692821854</v>
+        <v>11.25302370585388</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.5038759689922</v>
+        <v>10.5400696864111</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.13860618396819</v>
+        <v>10.20427921386387</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3.659104130308322</v>
+        <v>3.724578733294592</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>9.619296716070899</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>9.274350019402391</v>
+        <v>9.341085271317823</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.315866084425025</v>
+        <v>9.382572453232527</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>8.542030673655695</v>
+        <v>8.609656777196136</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.816389940771032</v>
+        <v>8.883716419358059</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-4.796037296037291</v>
+        <v>-4.728366317423358</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.07947148547562</v>
+        <v>14.14847161572057</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>7.191448007774532</v>
+        <v>7.260726072607255</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>6.532516768737331</v>
+        <v>6.602582775026796</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.196969696969688</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-6.33985020912359</v>
+        <v>-6.270280773341064</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>0.2218330414477947</v>
+        <v>0.2915451895044185</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>0.4379562043795673</v>
+        <v>0.5074365704287018</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-6.041666666666714</v>
+        <v>-5.972384286269985</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-6.584867075664619</v>
+        <v>-6.514930454235966</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-6.660822131307278</v>
+        <v>-6.590776415645117</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-6.386046964825098</v>
+        <v>-6.316301703163013</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-6.461988304093566</v>
+        <v>-6.392133956386289</v>
       </c>
     </row>
   </sheetData>
@@ -3180,1887 +3180,1887 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.02078</t>
+          <t>X &gt; -0.02075</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.2267982026740043</v>
+        <v>0.2258195532346932</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.3527208837591829</v>
+        <v>0.3515841498661132</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.3242290922180615</v>
+        <v>0.3230899179301829</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3989670220405515</v>
+        <v>0.397720931962759</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.2286962740582936</v>
+        <v>0.2270222179180692</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1356341362500899</v>
+        <v>0.1340742822560088</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.03334052425726242</v>
+        <v>0.03188205296612523</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.07959369839387875</v>
+        <v>-0.08092581340108751</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.008699863788699247</v>
+        <v>0.007263077923163053</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.03421362537275741</v>
+        <v>-0.03561951513906791</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.01034813321498262</v>
+        <v>-0.01177639886888215</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.09365634365633468</v>
+        <v>-0.09499334873529364</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1291223420524688</v>
+        <v>-0.1304460173452</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1839738703274989</v>
+        <v>-0.1852386309422087</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.08053059498036674</v>
+        <v>-0.08193572145251693</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.09332107596001293</v>
+        <v>-0.09469696969696884</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.06066491354489756</v>
+        <v>-0.06208388934785347</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.001200960350558944</v>
+        <v>-0.0002951916749012184</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.02638447756775264</v>
+        <v>0.02486284388714211</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.0223747016706497</v>
+        <v>0.02086164142175306</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.06389448804770126</v>
+        <v>0.0623174344873334</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.03569528162808666</v>
+        <v>0.03414904648969497</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.02992075799719629</v>
+        <v>-0.03138272513338336</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.0880337043325099</v>
+        <v>-0.08942910356211087</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.01941</t>
+          <t>X &gt; -0.01939</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3335</v>
+        <v>3338</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1376713280193087</v>
+        <v>0.1526667217361393</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.3249300679873599</v>
+        <v>0.3398522786944085</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.2720991590229076</v>
+        <v>0.2874585574962438</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.349876962534232</v>
+        <v>0.3653625194466912</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.2101625345943248</v>
+        <v>0.2251311650107368</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1458324333205425</v>
+        <v>0.1608123447367831</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.0461425328605074</v>
+        <v>0.03161663658755032</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.06614535511267405</v>
+        <v>-0.08050089445438147</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.05218449238523704</v>
+        <v>0.0377071584716262</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.01212124795639369</v>
+        <v>-0.002117288038633092</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.03502793360247836</v>
+        <v>0.05053229521591618</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.04750627323080181</v>
+        <v>-0.06169965075670092</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1086137904758218</v>
+        <v>-0.1224550290490569</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1927074481297879</v>
+        <v>-0.2064184913114886</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.08630300797727841</v>
+        <v>-0.07005939208812606</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.1313722294028707</v>
+        <v>-0.1152438913945204</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1280010170230952</v>
+        <v>-0.1118353323844588</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.005643761904536859</v>
+        <v>0.01044471103547551</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.01114559202761711</v>
+        <v>-0.02501930752523407</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.04585953878406457</v>
+        <v>-0.05975711691027641</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.002082973407773636</v>
+        <v>-0.01587827424993549</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.0001488718925912735</v>
+        <v>-0.01393010825983509</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.0970781398850562</v>
+        <v>-0.110850969410393</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.155141727381924</v>
+        <v>-0.1688465587429988</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.01805</t>
+          <t>X &gt; -0.01803</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3321</v>
+        <v>3325</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1996446726219219</v>
+        <v>0.1984119245124631</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.3729944346751779</v>
+        <v>0.3579086644286136</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2661432498694296</v>
+        <v>0.2515289375429859</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3771673987039108</v>
+        <v>0.3626374695052448</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2982868226907627</v>
+        <v>0.3129640279031634</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.2029795421082596</v>
+        <v>0.2007976982960926</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1061301492429081</v>
+        <v>0.1040363929111265</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.03540924540630641</v>
+        <v>-0.03734434057481906</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.08325217555213271</v>
+        <v>0.08117524764370643</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1362335722063293</v>
+        <v>0.1340652827366284</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1881155956399709</v>
+        <v>0.1858933716248004</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.01644395208752059</v>
+        <v>0.01441662134399024</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.04017637366808913</v>
+        <v>-0.04217586629386716</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1236725766345472</v>
+        <v>-0.1255807739694461</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.01600025222072787</v>
+        <v>0.01390051147942017</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.09180838240236966</v>
+        <v>-0.09375937593759431</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.087847003995428</v>
+        <v>-0.08980858446555828</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.06553607721571097</v>
+        <v>0.06338547770611314</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.0310756657346829</v>
+        <v>-0.03310397011183852</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.06672932330826598</v>
+        <v>-0.06870950905955908</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.05057104678375168</v>
+        <v>-0.05259071064622844</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.04832338519427992</v>
+        <v>-0.05034960470428018</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1769359875022047</v>
+        <v>-0.1787991976508891</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.2349482559153131</v>
+        <v>-0.2367454852083455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01669</t>
+          <t>X &gt; -0.01667</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3306</v>
+        <v>3310</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1119362865568903</v>
+        <v>0.1106534868081326</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3176261565279503</v>
+        <v>0.3023706844355658</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.3069388944487059</v>
+        <v>0.292062744892938</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3916290257170445</v>
+        <v>0.3768575105825747</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.314044780459426</v>
+        <v>0.3284779318125999</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1272148402962827</v>
+        <v>0.1248191179099791</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.06348747162173396</v>
+        <v>0.06113621111148149</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.01724139139430747</v>
+        <v>-0.01950803395376255</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1017739435036304</v>
+        <v>0.09936443318240862</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1584965371094214</v>
+        <v>0.1559865004210721</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2395093542488951</v>
+        <v>0.2369113235609959</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.06833883416161513</v>
+        <v>0.06593430469182948</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.04671095889532495</v>
+        <v>0.04428612942121646</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.06629224152180058</v>
+        <v>-0.06859119646903622</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.04684557718369575</v>
+        <v>0.04438251390387649</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.03396009574316849</v>
+        <v>-0.03630335908817273</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.02935619564139813</v>
+        <v>-0.03171178529970575</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.06482821052987475</v>
+        <v>0.06235339215817959</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.02720416572055484</v>
+        <v>0.02478197012704442</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.0396525679758355</v>
+        <v>-0.0419879877384588</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.009270125906851945</v>
+        <v>0.006852421304834877</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.01189048457346331</v>
+        <v>0.009465130248656806</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.08829472210763356</v>
+        <v>-0.09058943093911154</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.1764468642871648</v>
+        <v>-0.1786394951576966</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.01533</t>
+          <t>X &gt; -0.01531</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3282</v>
+        <v>3284</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1394379162831001</v>
+        <v>0.1401571212927735</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2279912151980952</v>
+        <v>0.2149963605328935</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2882112137627644</v>
+        <v>0.2764296784124127</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3484146324285504</v>
+        <v>0.3372237887423708</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.2729089205126769</v>
+        <v>0.2910952849319202</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.05304352424771963</v>
+        <v>0.05407600767374987</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.005547391257678669</v>
+        <v>-0.004049744597573124</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.02421476733704253</v>
+        <v>-0.05285412262156086</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.06503199282661853</v>
+        <v>0.03630590781472876</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1277911914549534</v>
+        <v>0.09944857020191478</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2377354137097356</v>
+        <v>0.2394943993397689</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.09770890918431974</v>
+        <v>0.09970811623360021</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.02339293501498929</v>
+        <v>0.0260639273037313</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1495807488070753</v>
+        <v>-0.1466813348001494</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.0004519337847881388</v>
+        <v>0.002724489775168593</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.05580717353601727</v>
+        <v>-0.05292904746124094</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.05019783251473342</v>
+        <v>-0.04724826042710362</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.01539323592451325</v>
+        <v>-0.01240617827677681</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.05489441928943251</v>
+        <v>-0.05200398901185821</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.09319841752890312</v>
+        <v>-0.09038915244998691</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.03996601021560764</v>
+        <v>-0.03688563119570887</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.03678640252119436</v>
+        <v>-0.03366543978789593</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.1397275415333965</v>
+        <v>-0.1366974413669695</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2279846477864425</v>
+        <v>-0.2248582763213278</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01397</t>
+          <t>X &gt; -0.01395</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3255</v>
+        <v>3258</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1415074098780167</v>
+        <v>0.1419472733892633</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.3863074752092714</v>
+        <v>0.4033812758898634</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.3812834457995748</v>
+        <v>0.4166378694680617</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4173619740813095</v>
+        <v>0.4535556915002132</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.283179590606359</v>
+        <v>0.3315056769682059</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.02940660510208915</v>
+        <v>0.06045659589000962</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.08442214844497187</v>
+        <v>-0.1008050650995713</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1009684357081611</v>
+        <v>-0.08672983762127728</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.01135104095722994</v>
+        <v>0.002798545502628258</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.02770417217707433</v>
+        <v>0.04201211541935379</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1668591370173687</v>
+        <v>0.1504034671517118</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.05856937675119411</v>
+        <v>0.04227588441150232</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.007076789682635365</v>
+        <v>-0.02303853009370016</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.149031828876808</v>
+        <v>-0.1648145230679674</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.02385578028236779</v>
+        <v>-0.03959659442539021</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.08460011493384911</v>
+        <v>-0.1004379372413666</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.04718722118168017</v>
+        <v>-0.06303217711855069</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.01944113712391982</v>
+        <v>0.00355499342595067</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.02216649500693535</v>
+        <v>-0.03807369619710244</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.09301166001841921</v>
+        <v>-0.1089058476842055</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.03483638198752459</v>
+        <v>-0.05065569189313379</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.0617022868696111</v>
+        <v>-0.07748398210723906</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.1984957772739122</v>
+        <v>-0.2142254016390339</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.2254291643086219</v>
+        <v>-0.2411210650419022</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01261</t>
+          <t>X &gt; -0.01259</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3216</v>
+        <v>3219</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03416042366824001</v>
+        <v>0.0033777167100979</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2552271834367659</v>
+        <v>0.2412435580977359</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2370347539612609</v>
+        <v>0.2414868290512615</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3441644800690185</v>
+        <v>0.3494462964060006</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.08913184877958713</v>
+        <v>0.1063915271044777</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1082945705886758</v>
+        <v>-0.1084970008630606</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.2140095264981809</v>
+        <v>-0.231295762033163</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1345017292822135</v>
+        <v>-0.1518027929988008</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.04858022271192652</v>
+        <v>0.0310929192599616</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.09772387072384703</v>
+        <v>0.08036634815314159</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.235225132840327</v>
+        <v>0.2176687560958186</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1600622804527418</v>
+        <v>0.1426347145683806</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.01641609460296678</v>
+        <v>-0.00245230293334231</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2504124573417386</v>
+        <v>-0.2671549682849346</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.05350473663909838</v>
+        <v>-0.07028159848842819</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.09137033232914149</v>
+        <v>-0.1082586559957903</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.1139035921155624</v>
+        <v>-0.1307458896201794</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.03266726891848748</v>
+        <v>-0.03103545565691235</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.01531917593710119</v>
+        <v>-0.0138169201080629</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.1203416149068275</v>
+        <v>-0.1188771478465966</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.02382327324150424</v>
+        <v>-0.02212283755377342</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.05009082822042643</v>
+        <v>-0.06692254003708342</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.2229550572507506</v>
+        <v>-0.2396971482975871</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.2182072095662022</v>
+        <v>-0.234942281953245</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01125</t>
+          <t>X &gt; -0.01123</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3179</v>
+        <v>3183</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.03008011704262969</v>
+        <v>-0.04709711343197398</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1977722069117291</v>
+        <v>0.1975552066927406</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1969206636888998</v>
+        <v>0.2148748628270027</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.5017900282329677</v>
+        <v>0.5202594476456497</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.122956731699027</v>
+        <v>0.1531896507317754</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04784640193964407</v>
+        <v>-0.03519605556996908</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.239349223793937</v>
+        <v>-0.2441169008616342</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1734002676839381</v>
+        <v>-0.1603748872136634</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.01135480622954788</v>
+        <v>0.02419999626852842</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1016253670641518</v>
+        <v>0.1145618074611221</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2688455311575666</v>
+        <v>0.2815658817235658</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1647654634484468</v>
+        <v>0.1594090244703708</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.03177903731824472</v>
+        <v>-0.03699204342735385</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2973083984591156</v>
+        <v>-0.3022113555761621</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.09020765059734259</v>
+        <v>-0.09543185402240795</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.07284181063143791</v>
+        <v>-0.07803814247840535</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.09403781381375609</v>
+        <v>-0.09922263866943126</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.04198605402962841</v>
+        <v>-0.02850501444918763</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.04571213732897661</v>
+        <v>-0.01359293365165115</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.1227222745837295</v>
+        <v>-0.09064697596119231</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.05019286657180544</v>
+        <v>-0.01786177751904461</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.04445411286438627</v>
+        <v>-0.03089366857638964</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.2225249522464878</v>
+        <v>-0.2275244837325303</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.2168378374898126</v>
+        <v>-0.221854345955883</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.009887</t>
+          <t>X &gt; -0.009872</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3127</v>
+        <v>3131</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1891536339948345</v>
+        <v>0.1710969780546989</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2991291527368318</v>
+        <v>0.2982877501184404</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.3856608031180997</v>
+        <v>0.4032674015521422</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5484052310787604</v>
+        <v>0.5665667717317717</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.07391215490891057</v>
+        <v>0.1035902896455383</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.03917721915062344</v>
+        <v>-0.0274085481044466</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2528896680940065</v>
+        <v>-0.258816691454264</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1494003785600313</v>
+        <v>-0.1372862299544337</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.005887315847544983</v>
+        <v>0.01784660743764732</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1423280082632274</v>
+        <v>0.1543204733556109</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2121834398149147</v>
+        <v>0.2240538915005956</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1747415797463603</v>
+        <v>0.1681634501665812</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1020761335720621</v>
+        <v>-0.1084285965936971</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3364626780308768</v>
+        <v>-0.3425446080766079</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.05118882581710693</v>
+        <v>-0.05771040534295224</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.05235605019179701</v>
+        <v>0.04576366147932021</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.03078252074560339</v>
+        <v>-0.03728757606219801</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.1196619047938583</v>
+        <v>0.1320555563305348</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.08035722609093199</v>
+        <v>0.1117760726622734</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.06487543915682181</v>
+        <v>-0.03345461290042806</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.04599593615450459</v>
+        <v>-0.01429188463188069</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.07085728630882215</v>
+        <v>-0.05820936583663183</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.2564646971354207</v>
+        <v>-0.2626618564197187</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.2174514743312912</v>
+        <v>-0.2237106624439988</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.008526</t>
+          <t>X &gt; -0.008512</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3064</v>
+        <v>3068</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2843471211797706</v>
+        <v>0.2651496450769457</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.4034220932324004</v>
+        <v>0.4018079948329998</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4238124792436011</v>
+        <v>0.4410440323756788</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.312379701546611</v>
+        <v>0.3302492235082752</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.03038107574310089</v>
+        <v>0.05935167763199445</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1213440671583896</v>
+        <v>-0.1105932329610866</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.2911499159757227</v>
+        <v>-0.2985055768125022</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.2448182716957135</v>
+        <v>-0.2337281009638943</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.08723217145190176</v>
+        <v>-0.0763020056419208</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.06782174431013743</v>
+        <v>0.07874847363428472</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1985037619091514</v>
+        <v>0.2092524817361436</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.02917544394447447</v>
+        <v>-0.03700829273199702</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2235982617855328</v>
+        <v>-0.2313355557668544</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.5233957422254605</v>
+        <v>-0.5307780452947739</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.1536875078284865</v>
+        <v>-0.1616448672497199</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.09283577664680109</v>
+        <v>-0.1007965142643101</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.1423917536006627</v>
+        <v>-0.1503111453988168</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.05187174838606978</v>
+        <v>-0.04048606049562409</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.03125200676412732</v>
+        <v>-0.0005412869467420478</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.1833441981747086</v>
+        <v>-0.1526231570625569</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.1203523490044773</v>
+        <v>-0.08938467385147675</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.1115722943861641</v>
+        <v>-0.1000628281572844</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.3392824188762091</v>
+        <v>-0.3469305725015701</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.3305696792023625</v>
+        <v>-0.3382443431746438</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.007165</t>
+          <t>X &gt; -0.007151</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2996</v>
+        <v>3000</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.6571099251486388</v>
+        <v>0.6363412154804919</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5542609953035154</v>
+        <v>0.5517392722978229</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7740361369259787</v>
+        <v>0.7907366012310177</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5437166064424517</v>
+        <v>0.5610897107501316</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2637030510112623</v>
+        <v>0.2916782624311907</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.004619080474427051</v>
+        <v>0.01399127893017038</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.05161510909034206</v>
+        <v>-0.06097765056257742</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.03106706268467008</v>
+        <v>-0.02146452947897615</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.07691626721001654</v>
+        <v>0.1054773574725445</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2862682623080914</v>
+        <v>0.315083133785194</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4470295594384908</v>
+        <v>0.4756074130435763</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1873293040957691</v>
+        <v>0.1968580095955801</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.01402500738350199</v>
+        <v>0.004237650948169858</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2208910956431254</v>
+        <v>-0.2304086791657838</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.1056103418308183</v>
+        <v>0.0955436441099522</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.1211366673481891</v>
+        <v>0.1111413536563219</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.07356754051536996</v>
+        <v>0.06360719116249669</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.1685174799682443</v>
+        <v>0.1783627660689504</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.1847072873519053</v>
+        <v>0.2143962773884098</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.125</v>
+        <v>0.154642140556625</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.1351507080410599</v>
+        <v>0.1650651028005754</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.07922679019599599</v>
+        <v>0.08921914139147447</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.1931874386322363</v>
+        <v>-0.202783986846228</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.2492602222066083</v>
+        <v>-0.2588006230529558</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.005804</t>
+          <t>X &gt; -0.005791</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.7335920928717954</v>
+        <v>0.6979958617746505</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.7083339335993699</v>
+        <v>0.7264084685144709</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.5427381527088215</v>
+        <v>0.5822219599315375</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.46828060787157</v>
+        <v>0.474575029396334</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1914433077908555</v>
+        <v>0.2421971731882522</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2912578138488655</v>
+        <v>-0.2602540829756563</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2516930362284597</v>
+        <v>-0.2738435803785961</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.185420095540124</v>
+        <v>-0.1876503608660727</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.07493851327610912</v>
+        <v>-0.05746434106434606</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2058227858782118</v>
+        <v>0.1900570532484949</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3277771043320143</v>
+        <v>0.311630353312637</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1723207755309986</v>
+        <v>0.136436352004786</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.03424858818925713</v>
+        <v>-0.05472709559003164</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2006072599283968</v>
+        <v>-0.2553881078715534</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.1630166535564115</v>
+        <v>0.1086276800353332</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.2258600307102796</v>
+        <v>0.170938828506209</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.07785380194137304</v>
+        <v>0.05763718955784469</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.1803392655141423</v>
+        <v>0.1808951203480831</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.2927279886119294</v>
+        <v>0.3137319699444419</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.1199844344517444</v>
+        <v>0.1406491624036477</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.1856058193757448</v>
+        <v>0.2071186977197286</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.09584107395410513</v>
+        <v>0.09665868300498204</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.09334151699499671</v>
+        <v>-0.1134633507919531</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.1486295695363609</v>
+        <v>-0.1686805861185192</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.004443</t>
+          <t>X &gt; -0.004431</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2750</v>
+        <v>2753</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.5392601494029066</v>
+        <v>0.5333487665824848</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5657482875614761</v>
+        <v>0.5599742089265689</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3918706082854726</v>
+        <v>0.4070367210382742</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.1324336149160388</v>
+        <v>0.148267395874683</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.06769131874623469</v>
+        <v>-0.04285761555142642</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5117865286344738</v>
+        <v>-0.5068860044992505</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.4157171067420862</v>
+        <v>-0.4108419216626586</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.4046265676118352</v>
+        <v>-0.3791269814559257</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2182879102647988</v>
+        <v>-0.1722592514363015</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1151322069165062</v>
+        <v>0.161672224939224</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1207377668578999</v>
+        <v>0.1460866824523492</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.06485450033836315</v>
+        <v>-0.06025142483344581</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1530641683798919</v>
+        <v>-0.1696553454187466</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.2441704180506221</v>
+        <v>-0.2607033611727658</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.1343551818964031</v>
+        <v>0.1170755286498917</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.206826667118456</v>
+        <v>0.1895998769866196</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.01450525632770194</v>
+        <v>-0.03146037208416175</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.0983762513242965</v>
+        <v>0.102934380654176</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.1329453111333834</v>
+        <v>0.1591056560600563</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.05789139120958708</v>
+        <v>-0.03167043267041691</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.07081668806771546</v>
+        <v>-0.04434221894184986</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.2340682236372942</v>
+        <v>-0.2291206422245864</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.5045493276022697</v>
+        <v>-0.4993082391107251</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.449867091972358</v>
+        <v>-0.444682691099942</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.003082</t>
+          <t>X &gt; -0.00307</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2569</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.6071649173797766</v>
+        <v>0.5629498644835778</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7756701466331535</v>
+        <v>0.7318538100314669</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.885756586847684</v>
+        <v>0.8654268066290882</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.5426356589147332</v>
+        <v>0.5620420271116799</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.3544521190851739</v>
+        <v>0.3813504300975623</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.444852425161038</v>
+        <v>-0.4786007936538397</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.247974569627786</v>
+        <v>-0.242406786578691</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.3713701771323841</v>
+        <v>-0.3434246847204392</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.4074336311167244</v>
+        <v>-0.3574353077298227</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.1763725407360255</v>
+        <v>0.2504435266784455</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.35694096909846</v>
+        <v>0.4080435415111836</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.2945424141076316</v>
+        <v>0.3233935169451669</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.03056087698399068</v>
+        <v>-0.02337103438299692</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.004190820517358418</v>
+        <v>-0.01153065617119609</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.4566001992334208</v>
+        <v>0.4407704772920766</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.297613106590866</v>
+        <v>0.2816627816627886</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.1867931203201607</v>
+        <v>0.1709680930923696</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.2373911900280703</v>
+        <v>0.2448888909040647</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.259037495705897</v>
+        <v>0.2896224903042324</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.1373492804356289</v>
+        <v>-0.08392773633478612</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.07384243234425725</v>
+        <v>-0.01953665638985314</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.1654283334611151</v>
+        <v>-0.1343082698036255</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.513463599053722</v>
+        <v>-0.4826439893963084</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.433702330303511</v>
+        <v>-0.402773634600905</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.001721</t>
+          <t>X &gt; -0.00171</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3181099278702675</v>
+        <v>0.3513842201890967</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.27771214304898</v>
+        <v>1.311385151662321</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.30542643942897</v>
+        <v>1.365286227442837</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7024942764188467</v>
+        <v>0.7632518318395185</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.2940465984759726</v>
+        <v>0.3410682707393278</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.7901399301668377</v>
+        <v>-0.767861871457022</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.4830924553094178</v>
+        <v>-0.459896948435933</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.5456643794456895</v>
+        <v>-0.4975779381318972</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.3745586815936832</v>
+        <v>-0.3264451209535721</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.06110914737770656</v>
+        <v>0.1358132838973063</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.230967872202811</v>
+        <v>0.2801712399373102</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.02021864862332734</v>
+        <v>0.04465573186328697</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.002193515464028906</v>
+        <v>0.002341049356495262</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.06610544322817447</v>
+        <v>0.04066554515374321</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.1688804051008788</v>
+        <v>0.1435285651074452</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.1837338849097989</v>
+        <v>0.158169754664776</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.3788095251340238</v>
+        <v>0.3530958500355084</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.4471363343420336</v>
+        <v>0.447456839569341</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.4899492719705592</v>
+        <v>0.5161020816938731</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.05957538994800871</v>
+        <v>-0.007928282802225795</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.003809989615568554</v>
+        <v>0.08235199733963583</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.1762100810254736</v>
+        <v>-0.1235893673652129</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.4649372985918987</v>
+        <v>-0.4128614024980877</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.4108396261568572</v>
+        <v>-0.3585982524256153</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003601</t>
+          <t>X &gt; -0.0003499</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.5547343156422357</v>
+        <v>0.5694169623029595</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.065329945276517</v>
+        <v>1.131501150500235</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.516176744871977</v>
+        <v>1.665120748060609</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.8023834316788196</v>
+        <v>0.9023162799638271</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.3873624028736771</v>
+        <v>0.5665258074165536</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.4424389259385606</v>
+        <v>-0.3432178768749026</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.5682169544584994</v>
+        <v>-0.4671107282627602</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.5481155521920869</v>
+        <v>-0.4960699297456443</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.2577194473486486</v>
+        <v>-0.2053305045607488</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.03603469883484678</v>
+        <v>0.0477282651428439</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.3170539513951169</v>
+        <v>0.3716632190254643</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.1665934961899111</v>
+        <v>0.1926644390188628</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.01832160179328213</v>
+        <v>0.01713329485602344</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.5247813411078752</v>
+        <v>0.4943087824991963</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.9436944134478225</v>
+        <v>0.8640598209348838</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.9701462974732848</v>
+        <v>0.8897638390898521</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.866276997003574</v>
+        <v>0.7859962829359546</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.060993880608599</v>
+        <v>1.061160381908181</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.8775166439400053</v>
+        <v>0.9074365704287004</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.4152097902097935</v>
+        <v>0.4741723253692172</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.5213600305624837</v>
+        <v>0.6121966728911588</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.6255346902819738</v>
+        <v>0.6364508115821579</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.2506346943453153</v>
+        <v>0.310324923463611</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.0252066948981593</v>
+        <v>0.03429247004013547</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.001001</t>
+          <t>X &gt; 0.00101</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.2102788428508191</v>
+        <v>0.3106152387771246</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.118111407759017</v>
+        <v>1.09593800483303</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.791524678912161</v>
+        <v>1.809271111416365</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.388483385607131</v>
+        <v>1.345383094464282</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.520416832404088</v>
+        <v>1.50772462689833</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4645733658583566</v>
+        <v>0.449360800542415</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.05969115028516825</v>
+        <v>-0.07352188085728528</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.03465662806202374</v>
+        <v>0.02186567812563567</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.07617269308465779</v>
+        <v>0.06335286004033946</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.04814213004674173</v>
+        <v>0.09990169209849142</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4208675527112433</v>
+        <v>0.4362278348830841</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.5514009947737435</v>
+        <v>0.5310774351710776</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6465117511459582</v>
+        <v>0.5909788801455917</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.147834300609432</v>
+        <v>1.054831510548318</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.212483518529424</v>
+        <v>1.119716731413007</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.658664362546602</v>
+        <v>1.565215748507526</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.937303348928793</v>
+        <v>1.843672231441595</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>2.206851768039506</v>
+        <v>2.151719971027468</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.048443095765329</v>
+        <v>2.031484040759743</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.486423220973791</v>
+        <v>1.506782380396729</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.317754647181829</v>
+        <v>1.377502316245582</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.654813929488107</v>
+        <v>1.676890876412465</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.117596591285661</v>
+        <v>1.138357458813225</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.8542723663207497</v>
+        <v>0.8749079448019543</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.002362</t>
+          <t>X &gt; 0.002371</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3846477215402615</v>
+        <v>-0.3405170804286684</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.2670188690785622</v>
+        <v>0.3973133819475905</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.870081562887158</v>
+        <v>1.84708311179449</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.8273408812729528</v>
+        <v>0.9691125907015845</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.037728990985748</v>
+        <v>1.128371623104805</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.337606396007466</v>
+        <v>-0.2523189564743831</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.8637620017457053</v>
+        <v>-0.7767428878894904</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.3199482262116362</v>
+        <v>-0.2298718243917364</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.6896163717153172</v>
+        <v>-0.5184176457773688</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.3943728351163287</v>
+        <v>-0.2187260610877786</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4489609364220399</v>
+        <v>-0.2746994222261918</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1765504232609558</v>
+        <v>0.3541419334017206</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.5815290986442818</v>
+        <v>0.716128381397084</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.150810995144113</v>
+        <v>1.237623762376238</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1.366262303224737</v>
+        <v>1.404562973046509</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.599524013078096</v>
+        <v>1.586408640864079</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.87797157305458</v>
+        <v>1.915791343366848</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.59807066521013</v>
+        <v>2.688239404380411</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.566669075666695</v>
+        <v>2.707601996400577</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.26856435643564</v>
+        <v>1.455871784370245</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.46793820486343</v>
+        <v>1.658358728986983</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.722016152521157</v>
+        <v>1.913638595392456</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.419233563227706</v>
+        <v>1.525861652245375</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.260783973134146</v>
+        <v>1.367247942068452</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.003723</t>
+          <t>X &gt; 0.003731</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.5194269813459869</v>
+        <v>0.6110366325314374</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.6143589935833731</v>
+        <v>0.7068303401019662</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.862830572507988</v>
+        <v>1.95987695307312</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.149037259314831</v>
+        <v>1.24692293363038</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1386061839682</v>
+        <v>0.2652767022025984</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.8570249019497425</v>
+        <v>-0.7318260029809736</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.9847297436811928</v>
+        <v>-0.9655615544708951</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.1345650731658452</v>
+        <v>0.1555811450171447</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.1464995069728161</v>
+        <v>-0.125859552508409</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2751736274196617</v>
+        <v>-0.2529194696643771</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.0008143603043251346</v>
+        <v>0.02114017249754596</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.3652530265433569</v>
+        <v>0.3882465279300717</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.9183663545103684</v>
+        <v>0.8797238582752414</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.73167789283201</v>
+        <v>1.627428620149416</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.893897567011244</v>
+        <v>1.722783707929466</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.015985745644436</v>
+        <v>1.778957497472028</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.773900690804375</v>
+        <v>1.603282445049693</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.964813603002824</v>
+        <v>2.858966980227144</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.424997241096627</v>
+        <v>2.386486246454623</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.964092872570191</v>
+        <v>1.99157967769402</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.71678879186598</v>
+        <v>2.746330807025295</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.964807818296798</v>
+        <v>2.994809169940517</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.375652099249777</v>
+        <v>2.404419017557707</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.407702120672447</v>
+        <v>2.436694872442537</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.005084</t>
+          <t>X &gt; 0.005091</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.5512307069252671</v>
+        <v>0.6609864549742426</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.342815755661221</v>
+        <v>1.454559445058841</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.156636418335644</v>
+        <v>2.132196249342378</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.583688175565023</v>
+        <v>1.560285953453935</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.7958831792733676</v>
+        <v>0.8013643102437555</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.00286770067759079</v>
+        <v>0.001024431461026154</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3531986214640099</v>
+        <v>-0.3477930817664188</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.3541622259751733</v>
+        <v>0.361301538360614</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.7310822723824728</v>
+        <v>-0.7255610681590952</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.223227542306837</v>
+        <v>-1.216389297086984</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.9488682751915007</v>
+        <v>-0.9423296549250608</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9462720378213305</v>
+        <v>-0.9389916112644485</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.0989322703929858</v>
+        <v>-0.087541548360349</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.032538745903359</v>
+        <v>0.9607730871817779</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.7415563167598336</v>
+        <v>0.584717236709821</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.9983924713524956</v>
+        <v>0.8970167115442109</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.005741492903709</v>
+        <v>0.904143298121042</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.456627949509979</v>
+        <v>2.438437844871615</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.258323955440389</v>
+        <v>1.327804321489523</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.445367751060822</v>
+        <v>1.600797961133267</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.46793820486343</v>
+        <v>1.624824031127581</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.816311296321253</v>
+        <v>1.973907248188738</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.383872884302669</v>
+        <v>1.540166663220369</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.873702407834763</v>
+        <v>2.03090664795743</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.006445</t>
+          <t>X &gt; 0.006451</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>556</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.702222680270708</v>
+        <v>1.735496972589537</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.904681574228526</v>
+        <v>1.938354582841868</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.436307275016944</v>
+        <v>2.471661698685431</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.54330249228974</v>
+        <v>1.579496209708644</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.8196097681975871</v>
+        <v>0.8852827980932645</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.7853403141361213</v>
+        <v>-0.7198657111498505</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.05469677961630026</v>
+        <v>0.1210888307662472</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.8514109513020429</v>
+        <v>0.918146203217475</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.3615532704136726</v>
+        <v>-0.2948469016061708</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.77696574211501</v>
+        <v>-0.7093396385745692</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.5026064749996735</v>
+        <v>-0.4352799964126461</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.4232774394064691</v>
+        <v>-0.3556064607925364</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.06513456791283545</v>
+        <v>0.1341346981577942</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.531949799889233</v>
+        <v>2.601227864721956</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>2.163875236720486</v>
+        <v>2.122296036675458</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>1.971701518598422</v>
+        <v>1.820625610948191</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.837607824449499</v>
+        <v>1.686708473970718</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.811761099001707</v>
+        <v>2.65713658735384</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.308459801501876</v>
+        <v>2.266862064145037</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>2.135791366906467</v>
+        <v>2.205073747303196</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>1.232878727692693</v>
+        <v>1.302815349121346</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>2.056204247589655</v>
+        <v>2.126249963251816</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.151123298963874</v>
+        <v>2.220868560625959</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.434894189911226</v>
+        <v>2.504748537618504</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.007806</t>
+          <t>X &gt; 0.007812</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.532087019969822</v>
+        <v>3.725224315139464</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.64037048536985</v>
+        <v>3.613661802503927</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.19623543148326</v>
+        <v>4.184571324901519</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.817253648223591</v>
+        <v>2.801974448315917</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.23025437317736</v>
+        <v>2.242969690054352</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.8653125560289396</v>
+        <v>0.8674358761517311</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.201093874085778</v>
+        <v>1.434772906547103</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.587727698633742</v>
+        <v>1.826204318936874</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.3663216465431844</v>
+        <v>-0.1412370705769916</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.6966980772682732</v>
+        <v>-0.4677241751849124</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.2428496599135883</v>
+        <v>0.4759783241198718</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.588350673716519</v>
+        <v>-1.365271079328124</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.7172764820041166</v>
+        <v>-0.4795045747556728</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.8352026271389192</v>
+        <v>1.308345120226306</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.3102945465150171</v>
+        <v>0.650201822645748</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.07361100643722551</v>
+        <v>-0.09469696969696884</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.2377295978548375</v>
+        <v>0.2178144647541274</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.469049077082495</v>
+        <v>1.452259475218668</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.017020792352845</v>
+        <v>0.9101211341870936</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.3131959910913196</v>
+        <v>0.5597532324146641</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.1208730147886</v>
+        <v>-1.103869168735216</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.1394748248917281</v>
+        <v>0.1655763496763001</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.4766186055081008</v>
+        <v>-0.4568099243887218</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.1071256463355823</v>
+        <v>-0.08421168433846304</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.009167</t>
+          <t>X &gt; 0.009172</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.691872830560442</v>
+        <v>5.60770779986283</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.203959563754729</v>
+        <v>4.405878978391627</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.64610348007205</v>
+        <v>5.858033339765264</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.779572414717514</v>
+        <v>3.989009956160672</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.549749315572434</v>
+        <v>2.78616746049201</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.295991738377488</v>
+        <v>1.528046941387082</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.252232234565533</v>
+        <v>2.490202303739501</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.685493151006632</v>
+        <v>1.922973517945962</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.2860870258275341</v>
+        <v>0.5193739946583591</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.4877483849418951</v>
+        <v>-0.253541681378131</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.07479532021378077</v>
+        <v>0.3095353018242477</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.645220773462846</v>
+        <v>-1.414300806826056</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.1760520495868718</v>
+        <v>0.06369319568198506</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.772619957822577</v>
+        <v>3.021805070680486</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.426543743689074</v>
+        <v>1.496609749978539</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.865534429148596</v>
+        <v>0.934927307759672</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.887510099161531</v>
+        <v>1.957079534944057</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.64957870618764</v>
+        <v>2.719290854244264</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1.998649845998067</v>
+        <v>2.246567005211311</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.607658959537574</v>
+        <v>1.853702670251799</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.091610813622232</v>
+        <v>0.1517362124306985</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.855555518018392</v>
+        <v>2.10487575826798</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>1.552296002419602</v>
+        <v>1.799640325822494</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>2.054389345232053</v>
+        <v>2.303518217526758</v>
       </c>
     </row>
     <row r="29">
@@ -5070,79 +5070,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>6.975698088834037</v>
+        <v>7.228718103959345</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.030414270940618</v>
+        <v>3.270752899812422</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.561832940428488</v>
+        <v>5.81824109715825</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.126017966585515</v>
+        <v>4.38064939655608</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.316704860261829</v>
+        <v>2.595583561689963</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.02320633900575331</v>
+        <v>0.2463178637293737</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.092014171539489</v>
+        <v>2.372919904476703</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.7304270350462048</v>
+        <v>1.007751937984501</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.394121881880622</v>
+        <v>-1.124673923579053</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.167957292650051</v>
+        <v>-2.259908440195254</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4495547042350694</v>
+        <v>-0.1742545951347836</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.533702759334524</v>
+        <v>-2.264598201481327</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.853139826197115</v>
+        <v>-1.576166065438898</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.4525791750428922</v>
+        <v>0.3766681015927702</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.373096478882168</v>
+        <v>0.4431624851716336</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.1187999932355837</v>
+        <v>-0.04940711462450764</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.4717439937749148</v>
+        <v>0.17899458897773</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1.816035939998471</v>
+        <v>1.885748088055095</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.66984026235059</v>
+        <v>1.961982024974155</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.4076086956521721</v>
+        <v>0.6942823803967286</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-1.222548235084908</v>
+        <v>-0.9391728784783879</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.8754097527507483</v>
+        <v>1.166799341930691</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.7878660786531597</v>
+        <v>1.077637690776378</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.7119247393846919</v>
+        <v>1.001805437553102</v>
       </c>
     </row>
     <row r="30">
@@ -5155,76 +5155,76 @@
         <v>206</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8.644719173959345</v>
+        <v>8.677993466278174</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.927901147237726</v>
+        <v>4.961574155851068</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.90365962034965</v>
+        <v>5.939014044018137</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.774407369958432</v>
+        <v>2.810601087377336</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.4767704351759292</v>
+        <v>0.5424434650716066</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.234615676454965</v>
+        <v>-2.169141073468694</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.823436065887144</v>
+        <v>1.889828117037091</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3874857293898728</v>
+        <v>-0.3207504774744407</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.795245026686075</v>
+        <v>-1.728538657878573</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.052172224895116</v>
+        <v>-2.984546121354676</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.294721170340168</v>
+        <v>-2.22739469175314</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.09072328637545</v>
+        <v>-2.023052307761517</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.765939142543758</v>
+        <v>-1.696939012298799</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.9112547710595678</v>
+        <v>0.9805328358922907</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.06002485935212576</v>
+        <v>-0.1607022491278869</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.3157888774342652</v>
+        <v>-0.5324989020641198</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4498825715831885</v>
+        <v>-0.666416039041593</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.901444691933186</v>
+        <v>0.6780186194560684</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.117567854865001</v>
+        <v>1.187048220914136</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.8191747572815515</v>
+        <v>0.8884571376782802</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.2094625449202923</v>
+        <v>-0.1395259234916395</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.2854176005629014</v>
+        <v>-0.2153718849007404</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.9602313523269999</v>
+        <v>1.029976613989085</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.3988531198546497</v>
+        <v>0.4687074675619272</v>
       </c>
     </row>
     <row r="31">
@@ -5237,76 +5237,76 @@
         <v>170</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8.898978009453884</v>
+        <v>8.932252301772714</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6.224621208259848</v>
+        <v>6.258294216873189</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.539306709085992</v>
+        <v>6.574661132754478</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.071127430980553</v>
+        <v>4.107321148399457</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.7818810377693666</v>
+        <v>0.8475540676650439</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.539726279048409</v>
+        <v>-2.474251676062138</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.120156126909265</v>
+        <v>3.186548178059212</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.087215516478423</v>
+        <v>1.153950768393855</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.128731581501057</v>
+        <v>1.195437950308559</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2298991509057942</v>
+        <v>-0.1622730473653533</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.798846081121816</v>
+        <v>1.866172559708843</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.2346337872653592</v>
+        <v>-0.1669628086514265</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.9800562807972</v>
+        <v>1.049056411042159</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.513085434675126</v>
+        <v>2.582363499507849</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>1.630555984423516</v>
+        <v>1.339424880289869</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>1.0491454458096</v>
+        <v>0.7642211589580015</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>2.091522339895974</v>
+        <v>1.799894665255387</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>3.751244806153629</v>
+        <v>3.449439926346479</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.379132674967799</v>
+        <v>3.448613041016934</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>2.977941176470587</v>
+        <v>3.047223556867316</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.258270179237343</v>
+        <v>1.328206800665996</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1.182315123594734</v>
+        <v>1.252360839256895</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.045325584194508</v>
+        <v>2.115070845856593</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>1.381148950808395</v>
+        <v>1.451003298515673</v>
       </c>
     </row>
     <row r="32">
@@ -5319,76 +5319,76 @@
         <v>133</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>10.23565303033944</v>
+        <v>10.26892732265826</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.892958718702623</v>
+        <v>6.926631727315964</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.2051379538646</v>
+        <v>6.240492377533087</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.987585242175207</v>
+        <v>4.023778959594111</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.366676359406803</v>
+        <v>1.43234938930248</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-2.205557523827018</v>
+        <v>-2.140082920840747</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.78849363735204</v>
+        <v>3.854885688501987</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.254299894089115</v>
+        <v>1.321035146004547</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.543936259863635</v>
+        <v>0.6106426286711368</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2298991509057942</v>
+        <v>-0.1622730473653533</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.7963398154576566</v>
+        <v>0.863666294044684</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2346337872653592</v>
+        <v>-0.1669628086514265</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.8965140919918539</v>
+        <v>0.9655142222368127</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>2.930796378701864</v>
+        <v>3.000074443534587</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>2.271865139664563</v>
+        <v>2.341931145954028</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>1.363165790789701</v>
+        <v>1.432558669400777</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.484711194385135</v>
+        <v>3.554280630167661</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>4.131607477537983</v>
+        <v>4.201319625594607</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.59585094122167</v>
+        <v>3.665331307270804</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2.27913533834586</v>
+        <v>2.348417718742589</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.23217553085167</v>
+        <v>0.3021121522803227</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>1.659979873705296</v>
+        <v>1.730025589367457</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>1.182875340939312</v>
+        <v>1.252620602601397</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>1.106934001670844</v>
+        <v>1.176788349378121</v>
       </c>
     </row>
     <row r="33">
@@ -5401,76 +5401,76 @@
         <v>109</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>10.54606208048774</v>
+        <v>10.57933637280657</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.458592987861756</v>
+        <v>7.492265996475098</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.018892523775619</v>
+        <v>6.054246947444106</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.387668017921918</v>
+        <v>4.423861735340822</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.939829425558415</v>
+        <v>5.005502455454092</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3775931173981064</v>
+        <v>-0.3121185144118357</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.271559099171732</v>
+        <v>5.337951150321679</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.24071087567151</v>
+        <v>2.307446127586942</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.282226940694144</v>
+        <v>2.348933309501646</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.508391529924715</v>
+        <v>1.576017633465156</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>3.617613182361154</v>
+        <v>3.684939660948181</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.338519278886253</v>
+        <v>3.406190257500185</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.214028060399109</v>
+        <v>2.283028190644067</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.744964827346415</v>
+        <v>4.814242892179138</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>3.168602395648556</v>
+        <v>3.238668401938021</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>1.928800059948834</v>
+        <v>1.99819293855991</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>2.712137558460469</v>
+        <v>2.781706994242995</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.442016527686292</v>
+        <v>4.511728675742916</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.740708497957549</v>
+        <v>3.810188864006683</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>3.010321100917437</v>
+        <v>3.079603481314166</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>1.549689499258925</v>
+        <v>1.619626120687577</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>2.391165636276874</v>
+        <v>2.461211351939035</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.08635277522265739</v>
+        <v>-0.01660751356057233</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-1.079725307151669</v>
+        <v>-1.009870959444392</v>
       </c>
     </row>
     <row r="34">
@@ -5483,76 +5483,76 @@
         <v>84</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>7.040164308534912</v>
+        <v>7.073438600853741</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.324036412938213</v>
+        <v>4.357709421551554</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.884335948852076</v>
+        <v>2.919690372520563</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.551495016611291</v>
+        <v>4.587688734030195</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.567177612539631</v>
+        <v>6.632850642435308</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.8019612731654604</v>
+        <v>0.8674358761517311</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.98147609349239</v>
+        <v>6.047868144642337</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.702921447973829</v>
+        <v>5.769656699889261</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.744437512996463</v>
+        <v>5.811143881803964</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.16107829270323</v>
+        <v>6.228704396243671</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.435437559818567</v>
+        <v>6.502764038405594</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.965867465867468</v>
+        <v>5.033538444481401</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.222328628332711</v>
+        <v>6.29132875857767</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.000971817298357</v>
+        <v>6.07024988213108</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>4.151564387784866</v>
+        <v>4.221630394074332</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>3.55614824693005</v>
+        <v>3.625541125541126</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>2.231578362304937</v>
+        <v>2.301147798087463</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>4.507547327162044</v>
+        <v>4.577259475218668</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2.342718109141472</v>
+        <v>2.412198475190607</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>1.339285714285708</v>
+        <v>1.408568094682437</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-1.584867075664619</v>
+        <v>-1.514930454235966</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.470345940831038</v>
+        <v>-0.400300225168877</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-1.386046964825098</v>
+        <v>-1.316301703163013</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-1.461988304093566</v>
+        <v>-1.392133956386289</v>
       </c>
     </row>
     <row r="35">
@@ -5565,76 +5565,76 @@
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.398342362365149</v>
+        <v>1.431616654683978</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.063166847720822</v>
+        <v>1.096839856334164</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.072741745953522</v>
+        <v>1.108096169622009</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.257499157398044</v>
+        <v>3.293692874816948</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.790780097011677</v>
+        <v>5.856453126907354</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.180843260743103</v>
+        <v>0.2463178637293737</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>5.205078577964436</v>
+        <v>5.271470629114383</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4.926523932445875</v>
+        <v>4.993259184361307</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.968039997468509</v>
+        <v>5.034746366276011</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.643479949017916</v>
+        <v>5.711106052558357</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>5.917839216133252</v>
+        <v>5.98516569472028</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>7.088020674977201</v>
+        <v>7.155691653591134</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>4.514254094171207</v>
+        <v>4.583254224416166</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>5.742172645455703</v>
+        <v>5.811450710288426</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>3.633966044099552</v>
+        <v>3.704032050389017</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>2.779750731402096</v>
+        <v>2.849143610013172</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>4.094932399572009</v>
+        <v>4.164501835354535</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>5.43922434579558</v>
+        <v>5.508936493852204</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>2.756796784089708</v>
+        <v>2.826277150138843</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>2.943840579710141</v>
+        <v>3.01312296010687</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4979105539254931</v>
+        <v>-0.4279739324968403</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>0.8754097527507483</v>
+        <v>0.9454554684129093</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2990904430859729</v>
+        <v>-0.2293451814238878</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.3750317823544407</v>
+        <v>-0.3051774346471632</v>
       </c>
     </row>
   </sheetData>
@@ -5824,1887 +5824,1887 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.02078</t>
+          <t>X &lt; -0.02075</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-11.64513589850442</v>
+        <v>-11.61186160618559</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-17.77741286242411</v>
+        <v>-17.74373985381077</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-16.31856260187256</v>
+        <v>-16.28320817820408</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-21.38018200202225</v>
+        <v>-21.34398828460334</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-13.04979961313325</v>
+        <v>-12.98412658323757</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-8.514808913169936</v>
+        <v>-8.449334310183666</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.490573595948597</v>
+        <v>-3.42418154479865</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.027973207808195</v>
+        <v>2.094708459723627</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.278336814125687</v>
+        <v>-2.211630445318185</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1536215002574366</v>
+        <v>-0.08599539671699574</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.328537595460944</v>
+        <v>-1.261211116873916</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.740194588020685</v>
+        <v>2.807865566634618</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.514254094171207</v>
+        <v>4.583254224416166</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.191448007774532</v>
+        <v>7.260726072607255</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>2.184690681780715</v>
+        <v>2.254756688070181</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>2.779750731402096</v>
+        <v>2.849143610013172</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>1.196381674934344</v>
+        <v>1.26595111071687</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.807152465798623</v>
+        <v>-1.737440317741999</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-3.040304665185651</v>
+        <v>-2.970824299136517</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-2.853260869565219</v>
+        <v>-2.78397848916849</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-4.845736640882009</v>
+        <v>-4.775800019453357</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-3.472416334205782</v>
+        <v>-3.402370618543621</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.2990904430859729</v>
+        <v>-0.2293451814238878</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>2.523518942283239</v>
+        <v>2.593373289990517</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.01941</t>
+          <t>X &lt; -0.01939</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-6.113145795994697</v>
+        <v>-6.65289530620305</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-13.76539448137073</v>
+        <v>-14.21658776720347</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-11.54655836009101</v>
+        <v>-12.04014898490916</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-15.91888825865002</v>
+        <v>-16.3675608356772</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10.18659706806432</v>
+        <v>-10.6792549226823</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-7.560408064813629</v>
+        <v>-8.082650182368056</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.455225416379847</v>
+        <v>-2.830502480716241</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.144268718589387</v>
+        <v>1.710563182964421</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.692263996875774</v>
+        <v>-3.067226743554613</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.027075017401302</v>
+        <v>-1.430503865374227</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.972227945407916</v>
+        <v>-3.56608277742918</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.4072147364830272</v>
+        <v>0.9744449275565614</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.941260103361742</v>
+        <v>3.465740692025747</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.378439877693246</v>
+        <v>6.85911964690446</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>2.060972053290087</v>
+        <v>1.381699240890157</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>3.875544298033418</v>
+        <v>3.18090543994159</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>3.741450603884495</v>
+        <v>3.046988302964117</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-1.241581592698594</v>
+        <v>-1.87712950929081</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-1.025458429766779</v>
+        <v>-0.4564188512580429</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.3810975609756042</v>
+        <v>0.9352462358184184</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-1.381615043144301</v>
+        <v>-0.8121192092560463</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-1.45757009878691</v>
+        <v>-0.8879651706651472</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>2.475741653061078</v>
+        <v>3.00096737314221</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>4.838824704036519</v>
+        <v>5.334773674135796</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.01805</t>
+          <t>X &lt; -0.01803</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>96</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-7.28236882843121</v>
+        <v>-7.249094536112381</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-13.38429692039512</v>
+        <v>-12.73851050971993</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-9.615664051147931</v>
+        <v>-9.021890383493187</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-14.49612403100775</v>
+        <v>-13.85855574314211</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-11.73639381603179</v>
+        <v>-12.13249054558629</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-8.424229203025007</v>
+        <v>-8.358754600038736</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-5.03042866841237</v>
+        <v>-4.964036617262423</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.100649980597602</v>
+        <v>-0.03391472868216994</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.225800582241632</v>
+        <v>-4.15909421343413</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-6.041302659677726</v>
+        <v>-5.973676556137285</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.850276725895725</v>
+        <v>-7.782950247308698</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.879370629370626</v>
+        <v>-1.811699650756694</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1211381521422297</v>
+        <v>0.1901382823871884</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.024781341107875</v>
+        <v>3.094059405940598</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-1.80081656459609</v>
+        <v>-1.730750558306624</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.919243485025291</v>
+        <v>1.988636363636367</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.785149790876368</v>
+        <v>1.854719226658894</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-3.528166958552248</v>
+        <v>-3.458454810495624</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.1870437956204327</v>
+        <v>-0.1175634295712982</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.041666666666664</v>
+        <v>1.110949047063393</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.49846625766871</v>
+        <v>0.5684028790973628</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.4225112020261008</v>
+        <v>0.4925569176882618</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>4.863953035174909</v>
+        <v>4.933698296836994</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01669</t>
+          <t>X &lt; -0.01667</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>111</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-9.86515277625098</v>
+        <v>-9.332766768924635</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-9.503051438535309</v>
+        <v>-8.985071532241342</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-12.91954745443118</v>
+        <v>-12.37659698025551</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-10.58211453675251</v>
+        <v>-10.9266731670885</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.989544518340331</v>
+        <v>-4.92406991535406</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.059707947691649</v>
+        <v>-2.993315896541702</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.6355598905075084</v>
+        <v>-0.5688246385920763</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.197647429088477</v>
+        <v>-4.130941060280975</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.872383740758814</v>
+        <v>-5.804757637218373</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.300727176346179</v>
+        <v>-8.233400697759151</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.17441567441567</v>
+        <v>-3.106744695801737</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.497105091101012</v>
+        <v>-2.428104960856054</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.8851417014682426</v>
+        <v>0.9544197663009655</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-2.476492240271767</v>
+        <v>-2.406426233982302</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.0796303888485852</v>
+        <v>-0.01023751023750918</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.2137240829975084</v>
+        <v>-0.1441546472149824</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.02141020179549</v>
+        <v>-2.951698053738866</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-1.904386137962774</v>
+        <v>-1.83490577191364</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.08445945945945965</v>
+        <v>0.1537418398561883</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-1.359641850439395</v>
+        <v>-1.289705229010742</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-1.435596906082004</v>
+        <v>-1.365551190419843</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.54188096310282</v>
+        <v>1.611626224764905</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>4.168642326537061</v>
+        <v>4.238496674244338</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.01533</t>
+          <t>X &lt; -0.01531</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.861148772246978</v>
+        <v>-5.424899274100625</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-7.300849236333114</v>
+        <v>-6.862918323131616</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-9.496124031007753</v>
+        <v>-9.025147704893193</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-7.639171593809579</v>
+        <v>-7.91166281512163</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.266821795617602</v>
+        <v>-2.260822726559425</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8174657054494077</v>
+        <v>-0.8429903885519678</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.3552796102272282</v>
+        <v>0.3386521812934973</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.535985767426816</v>
+        <v>-1.809641658689607</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-4.050561918936985</v>
+        <v>-3.312484342025364</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.739165614784618</v>
+        <v>-6.68805973635979</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.31455581455581</v>
+        <v>-3.317174103311437</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.476084070079999</v>
+        <v>-1.52062814097048</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.747003563330097</v>
+        <v>2.63785502637856</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.8748906386701734</v>
+        <v>-0.9399963003990806</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.4609101516919551</v>
+        <v>0.3843176288431849</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.3268164575430319</v>
+        <v>0.2504004918657117</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.5189076992929955</v>
+        <v>-0.5843672192547444</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.4379562043795673</v>
+        <v>0.3614511689688555</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.36574074074074</v>
+        <v>1.278223986236149</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.0817995910020457</v>
+        <v>0.005750810970852172</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.00584453535943652</v>
+        <v>-0.07009515043824877</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.502841924063787</v>
+        <v>2.394160583941613</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.649122807017541</v>
+        <v>4.508109352616138</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01397</t>
+          <t>X &lt; -0.01395</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.064365308189821</v>
+        <v>-3.038437474877753</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-7.997026981744817</v>
+        <v>-8.192491381661299</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-7.918133186950392</v>
+        <v>-8.425691153583855</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-9.249210450760842</v>
+        <v>-9.741054811580817</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-6.528060482698464</v>
+        <v>-7.371478361893693</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.402624264753406</v>
+        <v>-2.007128583778574</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.9109293562789915</v>
+        <v>1.234838638361296</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.249658661377715</v>
+        <v>0.9566271936082202</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5606771254515124</v>
+        <v>-0.8423764220230936</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.334512536220942</v>
+        <v>-1.615292098059584</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.146573022192015</v>
+        <v>-3.795220185959003</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.956531123197784</v>
+        <v>-1.619981859345657</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.6118865392157886</v>
+        <v>-0.2891561961404179</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.253176402836267</v>
+        <v>2.557249589989674</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.2576066880528813</v>
+        <v>0.0586154948631048</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.9547373121857845</v>
+        <v>1.266499349321442</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.2033596674195763</v>
+        <v>0.519085279828623</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.136191649910266</v>
+        <v>-0.8127492890232304</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.3027845363611803</v>
+        <v>0.01663902441643472</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.118827160493829</v>
+        <v>1.43047869941514</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.04165719912140986</v>
+        <v>0.2744355989337635</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.4996716958532659</v>
+        <v>0.8120865700400088</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>3.243582664804528</v>
+        <v>3.540549012583405</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>3.784925276153352</v>
+        <v>4.078213691875469</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01261</t>
+          <t>X &lt; -0.01259</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.732944935162557</v>
+        <v>-0.242788861004783</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.255602339114333</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.963848869629771</v>
+        <v>-3.957332281201126</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-6.162790697674417</v>
+        <v>-6.126596980255513</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.072614938144007</v>
+        <v>-2.316045989388151</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.084846704565742</v>
+        <v>1.077519909765179</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.78722809726419</v>
+        <v>3.051152216891929</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.518574441844642</v>
+        <v>1.787719097262006</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.410206522835686</v>
+        <v>-1.126458745453839</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.184041933605116</v>
+        <v>-1.899374421490329</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.384930191242255</v>
+        <v>-4.08836896652052</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.178875579865675</v>
+        <v>-2.889285857653249</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3429707587488622</v>
+        <v>-0.5641720624404059</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.396068469820747</v>
+        <v>3.648246598058826</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.2618897060309706</v>
+        <v>0.5270491132861537</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.8569497556523515</v>
+        <v>1.121436035229145</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.217905566453922</v>
+        <v>1.480129735690092</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.0766744212388204</v>
+        <v>-0.1025434804463572</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.3580636961179451</v>
+        <v>-0.3792629369604583</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.321517412935322</v>
+        <v>1.285415385322842</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.2167078716845268</v>
+        <v>-0.2423524575200346</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.2048495104838182</v>
+        <v>0.4719298549819939</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>2.967186866020675</v>
+        <v>3.221652092216523</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>2.891245526752208</v>
+        <v>3.145819838993248</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01125</t>
+          <t>X &lt; -0.01123</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>238</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2353436148253323</v>
+        <v>0.4575135423057404</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.769627498907525</v>
+        <v>-2.746115715060476</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.751901948796608</v>
+        <v>-2.954626567370148</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.20013509601467</v>
+        <v>-7.356105176976826</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.17121400966942</v>
+        <v>-2.552922432226659</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.09063940001786364</v>
+        <v>-0.07707415926739003</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.637275342652636</v>
+        <v>2.703667393802583</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.774350019402398</v>
+        <v>1.595580430377311</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.6841339155749679</v>
+        <v>-0.8525589437245884</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.874635993011061</v>
+        <v>-2.040412379097177</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.100276725895725</v>
+        <v>-4.255979292951849</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.712703962703955</v>
+        <v>-2.645032984090022</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.08719518119110603</v>
+        <v>-0.01819505094614726</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.44144800777454</v>
+        <v>3.510726072607262</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.6991834354039028</v>
+        <v>0.7692494416933684</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.4609101516919551</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.7434831242096962</v>
+        <v>0.8130525599922223</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.05446902471134507</v>
+        <v>-0.1251214771622884</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.1018217505980559</v>
+        <v>-0.3258967629046339</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1.129201680672267</v>
+        <v>0.6942823803967286</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.1658332044474236</v>
+        <v>-0.2649304542359658</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.08987814880481437</v>
+        <v>-0.09147376571480947</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2.465493651421397</v>
+        <v>2.535238913083482</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2.389552312152929</v>
+        <v>2.459406659860207</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.009887</t>
+          <t>X &lt; -0.009872</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>290</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.148697676937239</v>
+        <v>-1.951657924242781</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.329024811551584</v>
+        <v>-3.299948236106104</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.254458135334509</v>
+        <v>-4.400129447299264</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-6.333439161838243</v>
+        <v>-6.464434818093352</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.237958093619966</v>
+        <v>-1.547133215514648</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.02690269563024117</v>
+        <v>-0.1529722871135775</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.271903527264527</v>
+        <v>2.338295578414474</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.16932718835217</v>
+        <v>1.036193348678474</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5014855137484773</v>
+        <v>-0.6288041110450564</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.960252431367223</v>
+        <v>-2.084313643736834</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.713290424525866</v>
+        <v>-2.83414478655785</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.30745282115145</v>
+        <v>-2.239781842537518</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.677645001457293</v>
+        <v>0.7466451317022518</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.196014217820199</v>
+        <v>3.265292282652922</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.1398227048102996</v>
+        <v>0.2098887110997651</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.9774460126916082</v>
+        <v>-0.9080531340805322</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.08414244656655256</v>
+        <v>-0.01457301078402651</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.702565583981794</v>
+        <v>-1.831742481728504</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.28618172665491</v>
+        <v>-1.615851100804178</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.2801724137931032</v>
+        <v>-0.05914227713751075</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.0817995910020457</v>
+        <v>-0.259222691678886</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.3506721215663333</v>
+        <v>0.2133472956951366</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.349585219082947</v>
+        <v>2.419330480745032</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>1.928816293607582</v>
+        <v>1.99867064131486</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.008526</t>
+          <t>X &lt; -0.008512</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>353</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.55680296999661</v>
+        <v>-2.387365219281548</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.589128853168233</v>
+        <v>-3.557796613731639</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.76360412605429</v>
+        <v>-3.881609534628929</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.072903057224977</v>
+        <v>-3.201805893904535</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6291840782040836</v>
+        <v>-0.8757952740318302</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6815760404206799</v>
+        <v>0.5873238313338049</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.155900919602601</v>
+        <v>2.222292970752548</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.762612930200518</v>
+        <v>1.663182649594987</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3956782909978074</v>
+        <v>0.3001754494872202</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.9415374014617655</v>
+        <v>-1.034537979358262</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.075628838571781</v>
+        <v>-2.16497271921881</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1012016152861221</v>
+        <v>-0.03353063667218947</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.591208574677438</v>
+        <v>1.660208704922397</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.186753172093795</v>
+        <v>4.256031236926518</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.9926106654508544</v>
+        <v>1.06267667174032</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.4609101516919551</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.8901967392331684</v>
+        <v>0.9597661750156945</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.1088386911652677</v>
+        <v>0.009855048659304089</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.07195880978474634</v>
+        <v>-0.3376338521065136</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.248229461756381</v>
+        <v>0.9759725212417933</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.7050290527584266</v>
+        <v>0.4334263532757632</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.6290739971158175</v>
+        <v>0.5278676521515422</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>2.603565877478964</v>
+        <v>2.673311139141049</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>2.527624538210496</v>
+        <v>2.597478885917774</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.007165</t>
+          <t>X &lt; -0.007151</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>421</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.727985574369065</v>
+        <v>-4.575426552684306</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.566644443304789</v>
+        <v>-5.647287820625856</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-4.162790697674417</v>
+        <v>-4.257438101750843</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.17511930622787</v>
+        <v>-2.36402679706508</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3408958696916713</v>
+        <v>-0.4068766657664469</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.06270858648959177</v>
+        <v>0.1291006376395387</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.08099589254729267</v>
+        <v>-0.1491108071135372</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.8496185491447008</v>
+        <v>-1.048800095787072</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.332673818070162</v>
+        <v>-2.527598124764737</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.476754267266884</v>
+        <v>-3.665303188485169</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.628188596273695</v>
+        <v>-1.693775122454809</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3886136209074209</v>
+        <v>-0.3196134906624621</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.281282523140973</v>
+        <v>1.350560587973696</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.032495051593735</v>
+        <v>-0.962429045304269</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.146654860128379</v>
+        <v>-1.077261981517303</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.8079353155066187</v>
+        <v>-0.7383658797240926</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.484328095993007</v>
+        <v>-1.5524264417013</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.60479914003848</v>
+        <v>-1.809348299547651</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.180225653206648</v>
+        <v>-1.386095870194296</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.248366679781803</v>
+        <v>-1.455828799389636</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.8492623530016132</v>
+        <v>-0.919370412485506</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>1.088220651960334</v>
+        <v>1.157965913622419</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>1.487338695114673</v>
+        <v>1.55719304282195</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.005804</t>
+          <t>X &lt; -0.005791</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.047255734109008</v>
+        <v>-3.82603229861715</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.915838976469885</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.014540455642312</v>
+        <v>-3.191420738590544</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.792004180820484</v>
+        <v>-2.793263646922178</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.284614789814569</v>
+        <v>-1.545875393433583</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.337006752031165</v>
+        <v>1.159522971212809</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.125938372786131</v>
+        <v>1.239408447914485</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.7690341970134043</v>
+        <v>0.7749772638690473</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1679964102395672</v>
+        <v>0.07158548861428216</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.357718699777976</v>
+        <v>-1.259989405299294</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.023209056722791</v>
+        <v>-1.917028459599202</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.174483411325511</v>
+        <v>-0.9721474119507221</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.04333553206830487</v>
+        <v>0.06747473098531742</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.8631272057695298</v>
+        <v>1.154807069492001</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.111593506951984</v>
+        <v>-0.8117474430418312</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.456383081390754</v>
+        <v>-1.151939960351172</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.6506271514795259</v>
+        <v>-0.5381935459267808</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.209428728797072</v>
+        <v>-1.203781913299359</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.826194739016664</v>
+        <v>-1.922469971627372</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.8844339622641542</v>
+        <v>-0.9879606102574741</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.238955125979089</v>
+        <v>-1.343590890373036</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.7488724457726406</v>
+        <v>-0.7480797864315889</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.2806197018415659</v>
+        <v>0.3878884156612514</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.5820368531391367</v>
+        <v>0.6872906840139663</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.004443</t>
+          <t>X &lt; -0.004431</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.266713998343384</v>
+        <v>-2.237597482708189</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.377249442650317</v>
+        <v>-2.348404976870533</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.659992926828956</v>
+        <v>-1.715418108741765</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.7393137288779812</v>
+        <v>-0.8011531932732581</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.08412376693006252</v>
+        <v>-0.01794300835834406</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.905760891080988</v>
+        <v>1.884816122018627</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.517190379206681</v>
+        <v>1.49646363038493</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.475045498786407</v>
+        <v>1.366840595735866</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7089009102956894</v>
+        <v>0.5167973170264872</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.6619494258468848</v>
+        <v>-0.8504719994260483</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6860976214181136</v>
+        <v>-0.7889026282610843</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.07958459450997424</v>
+        <v>0.06050601243258313</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4476306894556572</v>
+        <v>0.516630819700616</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.8232888037944406</v>
+        <v>0.8925668686271635</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.7311648233025565</v>
+        <v>-0.6610988170130909</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.031627161740879</v>
+        <v>-0.9622342831298027</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.1209447364868197</v>
+        <v>-0.05137530070429364</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.5853418464446207</v>
+        <v>-0.6039771985553273</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.7297084662791207</v>
+        <v>-0.835847011660853</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.05613772455090071</v>
+        <v>-0.05198627631969543</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.111739710762528</v>
+        <v>0.00248248108741933</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.7842876491318904</v>
+        <v>0.7634836740410336</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>1.899810106639165</v>
+        <v>1.877311071288084</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.673943729889437</v>
+        <v>1.651778219262411</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.003082</t>
+          <t>X &lt; -0.00307</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.869697657205982</v>
+        <v>-1.728912003350857</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.377595288693492</v>
+        <v>-2.235484700644889</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.706873697200045</v>
+        <v>-2.629420222993744</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.787061409459717</v>
+        <v>-1.834253592784513</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.218842279664628</v>
+        <v>-1.29397862585737</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.185358506037616</v>
+        <v>1.282718268178314</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5965183720860736</v>
+        <v>0.5777755674484837</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.9702564521509416</v>
+        <v>0.8816362996453506</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.080112766704502</v>
+        <v>0.9231234815600544</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6803218077824553</v>
+        <v>-0.8975221129863371</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.226595600456093</v>
+        <v>-1.372693837052289</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.03675632690873</v>
+        <v>-1.118875846789372</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.05104824879563807</v>
+        <v>-0.07271218490253517</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.1551717655744227</v>
+        <v>-0.1076949800243199</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.517502770145136</v>
+        <v>-1.467592663569782</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.039676014779324</v>
+        <v>-0.9901648059542794</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.7048365319059755</v>
+        <v>-0.6562456856218191</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.8579791651250233</v>
+        <v>-0.8780454537704827</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.9251460282878838</v>
+        <v>-1.013031265828609</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.2720588235294059</v>
+        <v>0.1094870587593064</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.0817995910020457</v>
+        <v>-0.08218191622426474</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.3587857118300235</v>
+        <v>0.2632438809981821</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.411361751311532</v>
+        <v>1.311677976399309</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.171659494648566</v>
+        <v>1.072654776008072</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.001721</t>
+          <t>X &lt; -0.00171</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.6910403728033288</v>
+        <v>-0.7570849128995789</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.672398524673191</v>
+        <v>-2.732284657785335</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.728212371100348</v>
+        <v>-2.838154506105845</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.568678298031237</v>
+        <v>-1.686099644553913</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.7244890541270337</v>
+        <v>-0.8179430083583483</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.516246987451183</v>
+        <v>1.464792256426257</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8844506881559937</v>
+        <v>0.8333068080863484</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.015554551304604</v>
+        <v>0.9112841433866947</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6617329898264046</v>
+        <v>0.559043041467838</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2393313335128582</v>
+        <v>-0.3921257539982506</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.5922122097666858</v>
+        <v>-0.691067999315834</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.1544602351053896</v>
+        <v>-0.2045567936138326</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1140769016212104</v>
+        <v>-0.1142629687298822</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.2458279778885455</v>
+        <v>-0.1930604509467031</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.456730543090714</v>
+        <v>-0.4039765571140279</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.4889106368385114</v>
+        <v>-0.4357077031495677</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.8918215352885071</v>
+        <v>-0.8379611549749768</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.033772339718162</v>
+        <v>-1.032247297078811</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.123982754327791</v>
+        <v>-1.174137669285066</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.01403863432165764</v>
+        <v>-0.09283747649057261</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.1160421356166665</v>
+        <v>-0.2776018913260074</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.2576430965105203</v>
+        <v>0.1475106628389682</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.8566773076021477</v>
+        <v>0.7446301964785604</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.7452189031136456</v>
+        <v>0.6332771048992143</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003601</t>
+          <t>X &lt; -0.0003499</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1416</v>
+        <v>1423</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8069885386179223</v>
+        <v>-0.8224755059163087</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.525042196812201</v>
+        <v>-1.607935889497661</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.157680857870616</v>
+        <v>-2.349576108445085</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.222356219748704</v>
+        <v>-1.353077816492451</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.637457397144459</v>
+        <v>-0.883586894922729</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5314743967879849</v>
+        <v>0.3889192776072221</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.7107994017630617</v>
+        <v>0.5643618929796617</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.6835260493649429</v>
+        <v>0.6059350267336256</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.2739358900001108</v>
+        <v>0.1984232690833494</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.03743486783524475</v>
+        <v>-0.1549119873727136</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.5366339692149964</v>
+        <v>-0.6101021017523678</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.3234634563748386</v>
+        <v>-0.3586184182637027</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.1118084020068508</v>
+        <v>-0.1098792368840122</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.8254296293562575</v>
+        <v>-0.7804146473553288</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.414037380348553</v>
+        <v>-1.298305490517947</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.451888723132228</v>
+        <v>-1.335054613455732</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.304688465101123</v>
+        <v>-1.188466841597304</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.579715164041339</v>
+        <v>-1.573812454254387</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.322607175902121</v>
+        <v>-1.357921073330061</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.6716878083157098</v>
+        <v>-0.750317900108179</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.8208802397454917</v>
+        <v>-0.9422329320293343</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.967357157165246</v>
+        <v>-0.9767413279257795</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.4392109262459414</v>
+        <v>-0.5204215533502818</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.04955892556250063</v>
+        <v>-0.1330568891574373</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.001001</t>
+          <t>X &lt; 0.00101</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1816</v>
+        <v>1822</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.206071159983459</v>
+        <v>-0.2929973583965833</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.003832439520799</v>
+        <v>-0.9799812102567245</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.594432048231944</v>
+        <v>-1.601006795235428</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.294081726120801</v>
+        <v>-1.249212784070224</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.41038122708818</v>
+        <v>-1.39150413764466</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.4810930219370206</v>
+        <v>-0.4652739671964028</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.01787159078680389</v>
+        <v>-0.005885234438551379</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.100649980597602</v>
+        <v>-0.08909859906265183</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1374160512487634</v>
+        <v>-0.125624268078937</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.1114636549210459</v>
+        <v>-0.1565178173000348</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.4408365502645495</v>
+        <v>-0.4525344923852828</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5552762276143142</v>
+        <v>-0.5357007454474427</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.6369573473089218</v>
+        <v>-0.5868332400662624</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.077853126510128</v>
+        <v>-0.9949816899498103</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.133052203088596</v>
+        <v>-1.050385261502967</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.525917510218029</v>
+        <v>-1.442299709422997</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.769780688450375</v>
+        <v>-1.685805887496365</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.007711165032198</v>
+        <v>-1.955030152961378</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.869736103312746</v>
+        <v>-1.848727813132946</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.376099505222648</v>
+        <v>-1.387909400425194</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.227331322089263</v>
+        <v>-1.272921321815879</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.523308379932097</v>
+        <v>-1.535951854241553</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.051246010871701</v>
+        <v>-1.064884625086577</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.8195507123167758</v>
+        <v>-0.8341390789622167</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.002362</t>
+          <t>X &lt; 0.002371</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2205</v>
+        <v>2213</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1927850690693447</v>
+        <v>0.1673966141666057</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1631430742412761</v>
+        <v>-0.2329076410511632</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.03855634037685</v>
+        <v>-1.019024126732049</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.5121828633655454</v>
+        <v>-0.5859958138131631</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6271595817975708</v>
+        <v>-0.6724413127668782</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.1259811019171622</v>
+        <v>0.07841797891651225</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.4155436790478007</v>
+        <v>0.3650289712371304</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.1178322025327603</v>
+        <v>0.06767703161744976</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.3206795621626952</v>
+        <v>0.2248985923212672</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1597883862214431</v>
+        <v>0.06264823018750576</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.189470338241577</v>
+        <v>0.09283733144917505</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.1537718946214142</v>
+        <v>-0.2499031626882626</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3745125482644625</v>
+        <v>-0.4461229788740724</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.6862444157832215</v>
+        <v>-0.7308617297060849</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.8029253159140595</v>
+        <v>-0.8215230259952406</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.9308657181679578</v>
+        <v>-0.9221101406487122</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.083671788388259</v>
+        <v>-1.101133276724056</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.478754927796935</v>
+        <v>-1.521715974230396</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.462496284308209</v>
+        <v>-1.531354588795473</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.751188320507012</v>
+        <v>-0.8483427887507702</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.860229394505204</v>
+        <v>-0.9583720908183935</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.000045813530456</v>
+        <v>-1.097924647398273</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.8345208239970603</v>
+        <v>-0.8872140789534413</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.7477025898078509</v>
+        <v>-0.8009304618841071</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.003723</t>
+          <t>X &lt; 0.003731</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2491</v>
+        <v>2496</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2079859475834667</v>
+        <v>-0.2412447277460856</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.24285610732219</v>
+        <v>-0.276339902235236</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.7041807975594097</v>
+        <v>-0.7379565302516866</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.4787061344514356</v>
+        <v>-0.5135396554147462</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1034794771118683</v>
+        <v>-0.1501612481034655</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2658905574540285</v>
+        <v>0.2186026376770656</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.3143530142287432</v>
+        <v>0.3061573511180669</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.1010661478635484</v>
+        <v>-0.1086754942324006</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.003316124393059283</v>
+        <v>-0.004477141236286286</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.05209331526562266</v>
+        <v>0.04354876974726096</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.05027672589572774</v>
+        <v>-0.05839934910510181</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.1861933584622619</v>
+        <v>-0.1942875101816099</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.3903164296905075</v>
+        <v>-0.3754330320355095</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.6917052535299817</v>
+        <v>-0.652942992140936</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.7503963965288634</v>
+        <v>-0.6878343914400418</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.7955924493484545</v>
+        <v>-0.7096969696969708</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.7060098034657685</v>
+        <v>-0.6436141066744412</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.147810530838989</v>
+        <v>-1.10845481049563</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.9482617443383816</v>
+        <v>-0.9325634295712959</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.7778056112224476</v>
+        <v>-0.7857176196032682</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.056933368099799</v>
+        <v>-1.064750382207158</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.14939012168027</v>
+        <v>-1.157096138089692</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.9312583077892569</v>
+        <v>-0.9391824934446902</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.943454917234213</v>
+        <v>-0.9514288281811645</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.005084</t>
+          <t>X &lt; 0.005091</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1576378892672778</v>
+        <v>-0.1856368757719977</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3632727357120871</v>
+        <v>-0.3911323243640794</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.573630815566311</v>
+        <v>-0.5654907471281732</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4605538073187105</v>
+        <v>-0.4530977123199378</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.2551331165942798</v>
+        <v>-0.2558696937401734</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.04731788804030401</v>
+        <v>-0.04831503959918138</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.04482830662433201</v>
+        <v>0.043139393486328</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.1392869006612543</v>
+        <v>-0.1408306622110018</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.1436887638274342</v>
+        <v>0.1416483608232895</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.2730119305464527</v>
+        <v>0.2702094795682655</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.2011938623395721</v>
+        <v>0.1987011288380955</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2008978516885875</v>
+        <v>0.1982122435164371</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.01913042769589168</v>
+        <v>-0.02217350608140833</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.3140707560223674</v>
+        <v>-0.2949927615832806</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.2371668221384056</v>
+        <v>-0.1963881915296994</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.3043584281461662</v>
+        <v>-0.2785204991087298</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.306234701823918</v>
+        <v>-0.280333488800224</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.6839106993475355</v>
+        <v>-0.6794000109369591</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.3723568711268754</v>
+        <v>-0.3899521754337485</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.4214259395725861</v>
+        <v>-0.4605539564918359</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.426862406786384</v>
+        <v>-0.466365332823159</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.5177542846995564</v>
+        <v>-0.5571609083453524</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.4054739905228786</v>
+        <v>-0.4449222235361106</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.533329017500705</v>
+        <v>-0.572612777749093</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.006445</t>
+          <t>X &lt; 0.006451</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2861</v>
+        <v>2865</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3431012808375442</v>
+        <v>-0.3490938216786716</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3820841470525309</v>
+        <v>-0.3881022480036194</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.483719606703481</v>
+        <v>-0.4899259011733861</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3447983392166165</v>
+        <v>-0.3513628491420846</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2042244854781714</v>
+        <v>-0.2167247185904344</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1067926947852058</v>
+        <v>0.09389494294401857</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.05534753721162389</v>
+        <v>-0.06820328392908692</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.2097079516120957</v>
+        <v>-0.2224205756197648</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.025678192984536</v>
+        <v>0.01263962951235698</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1071774424222838</v>
+        <v>0.09384169203789128</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.05362299555274319</v>
+        <v>0.04041553850493074</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.03851512472202501</v>
+        <v>0.02525687098243878</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.05525557608077492</v>
+        <v>-0.06864738219179856</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.5348213078987456</v>
+        <v>-0.5476043601575569</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.4617901907143676</v>
+        <v>-0.4540560364867545</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.4244157458333149</v>
+        <v>-0.3962034134447947</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.3984276149813724</v>
+        <v>-0.3701646293225238</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.5873751901532245</v>
+        <v>-0.5589253577246254</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.490166614880728</v>
+        <v>-0.4824553779853815</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.4570244328097743</v>
+        <v>-0.4698863194987055</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.281328900618071</v>
+        <v>-0.2945678321997036</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.4412389435088784</v>
+        <v>-0.4542806593376696</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.4601210388991817</v>
+        <v>-0.4730823498250274</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.5153495996778616</v>
+        <v>-0.5282596108365567</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.007806</t>
+          <t>X &lt; 0.007812</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2968</v>
+        <v>2975</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5459849052489503</v>
+        <v>-0.5700860987457119</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5621750997793313</v>
+        <v>-0.5532532940856214</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6448460620842056</v>
+        <v>-0.6374238559363476</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4695556005545214</v>
+        <v>-0.4633828138672698</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.380656797606342</v>
+        <v>-0.3794997522680319</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.174676030549584</v>
+        <v>-0.1737830186278373</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2247241204181876</v>
+        <v>-0.2580722917328799</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.2829940449839228</v>
+        <v>-0.3165482739035355</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.01250032349469166</v>
+        <v>-0.02171134864162383</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.06328347007618618</v>
+        <v>0.02802526285612572</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.07921261042073269</v>
+        <v>-0.1138276753060126</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1983661066938467</v>
+        <v>0.1627559606335893</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.06760271378146854</v>
+        <v>0.03095597675716277</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.1674229599673964</v>
+        <v>-0.2373184016356618</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.08710688717673776</v>
+        <v>-0.1378598809089056</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.02968124615750867</v>
+        <v>-0.02655708375264965</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.07654488699478179</v>
+        <v>-0.07341276439256461</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.2623633270794841</v>
+        <v>-0.2589751193240915</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.1944016832759985</v>
+        <v>-0.1773569844554927</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.08832436069986471</v>
+        <v>-0.1247844205431932</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.1289217720858602</v>
+        <v>0.124872545540164</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.06149553198062563</v>
+        <v>-0.06519137477618386</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.03137753276106281</v>
+        <v>0.02778431834236272</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.02443214955628292</v>
+        <v>-0.02798829812298465</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.009167</t>
+          <t>X &lt; 0.009172</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3071</v>
+        <v>3076</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.6511663459383144</v>
+        <v>-0.6389103800555915</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4840705297094772</v>
+        <v>-0.5045228462344795</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6447269218478056</v>
+        <v>-0.6655809453088963</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.4669978174155176</v>
+        <v>-0.4884709705624601</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3286431955505194</v>
+        <v>-0.353790167734914</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1880461287590336</v>
+        <v>-0.2133456120012411</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.2948439583378644</v>
+        <v>-0.3203324344249907</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.2309427004074891</v>
+        <v>-0.2566716573999557</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.07365309439722978</v>
+        <v>-0.09962819401665257</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.01414481113939559</v>
+        <v>-0.01233523747968235</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.04943339148119463</v>
+        <v>-0.07569636129832702</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1444775211809599</v>
+        <v>0.1177626103382252</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.01984691764030799</v>
+        <v>-0.0468189437955786</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.351842035515503</v>
+        <v>-0.3783879198292581</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.1990849628644966</v>
+        <v>-0.2067557463740712</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.1366864705880104</v>
+        <v>-0.1443645013220092</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.2514811382984163</v>
+        <v>-0.2590326660514748</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.3371529839016105</v>
+        <v>-0.3446119023489231</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.2642544588193871</v>
+        <v>-0.2910054938361455</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.2205284552845512</v>
+        <v>-0.2472760611617133</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.02880548381903481</v>
+        <v>-0.05612348227537467</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.2479790897625946</v>
+        <v>-0.2749869419608615</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.2141719648250984</v>
+        <v>-0.241120249366034</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.2707368116372493</v>
+        <v>-0.2976389412150695</v>
       </c>
     </row>
     <row r="29">
@@ -7714,79 +7714,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3141</v>
+        <v>3146</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.623220362437479</v>
+        <v>-0.6421097396945967</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.277481613627252</v>
+        <v>-0.2970637602187907</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.4980324999510515</v>
+        <v>-0.5178754308064626</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4032970267883442</v>
+        <v>-0.4235954004766782</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2444264212866258</v>
+        <v>-0.2676971873160596</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.03943925157894768</v>
+        <v>-0.06296473809333492</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.2243099903424763</v>
+        <v>-0.2478759594509157</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1046106903567932</v>
+        <v>-0.1284918667186474</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.08184601046834672</v>
+        <v>0.05767793846460023</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1505700944968638</v>
+        <v>0.1576149918209211</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.0006097420707931178</v>
+        <v>-0.02487551646639474</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.1828121117461237</v>
+        <v>0.1581293007795708</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.1241133980958935</v>
+        <v>0.09904195792584147</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.07839326206673292</v>
+        <v>-0.07155073669014911</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.07065783443736251</v>
+        <v>-0.07676619982004951</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.02813398930518929</v>
+        <v>-0.03423867600842101</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.07979091221554313</v>
+        <v>-0.05412172088763612</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1976140510212687</v>
+        <v>-0.2035357371855682</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.1850571459065051</v>
+        <v>-0.2097960541349266</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.07452305246422952</v>
+        <v>-0.0993684132540622</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.0690769446916164</v>
+        <v>0.04376542805470507</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.1150590599316885</v>
+        <v>-0.1401199141626464</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.1076680129897483</v>
+        <v>-0.1326347187333994</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.1009567854689308</v>
+        <v>-0.1259758720463893</v>
       </c>
     </row>
     <row r="30">
@@ -7796,79 +7796,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3211</v>
+        <v>3215</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5655535121535138</v>
+        <v>-0.5670133167065998</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3273662273258182</v>
+        <v>-0.329146779519732</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3886445525406828</v>
+        <v>-0.3904590350013351</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2185182518539861</v>
+        <v>-0.2205982171138956</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.07095301908744034</v>
+        <v>-0.07513103461535309</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.1027224698374454</v>
+        <v>0.09834110953221398</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1568360643425493</v>
+        <v>-0.1609570753249514</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.01475930070505882</v>
+        <v>-0.01907984736121193</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.07555600690565711</v>
+        <v>0.07112412041536231</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.157001724110529</v>
+        <v>0.1524077065640768</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.1081471028352752</v>
+        <v>0.1036317173643724</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.09533452270883203</v>
+        <v>0.09081119859234121</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.07553895934496779</v>
+        <v>0.07095223587555921</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.09633667131448931</v>
+        <v>-0.1007296759452529</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.0409821960660679</v>
+        <v>-0.02685149945876475</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.01749929223473146</v>
+        <v>-0.003526889001747691</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.008795723936145805</v>
+        <v>0.005203030860485569</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.09523254761037947</v>
+        <v>-0.08112561794904138</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.109307477212468</v>
+        <v>-0.1136814419936627</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.09039657853809757</v>
+        <v>-0.0947825465992338</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.02398759008071494</v>
+        <v>-0.0284999591044155</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.01905431306882122</v>
+        <v>-0.02358130632997302</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.09920595195668369</v>
+        <v>-0.1036151359988366</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.06315097408214854</v>
+        <v>-0.06761347945523966</v>
       </c>
     </row>
     <row r="31">
@@ -7878,79 +7878,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3247</v>
+        <v>3251</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4774251683693365</v>
+        <v>-0.4786106331386577</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3373262961601142</v>
+        <v>-0.3387045963783635</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.3525786516988916</v>
+        <v>-0.3540281641145171</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2534214386419578</v>
+        <v>-0.2550373472279901</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.08089356079953802</v>
+        <v>-0.08429017534790972</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.09292765972008254</v>
+        <v>0.08932781530194234</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.202943736345766</v>
+        <v>-0.2062312912752802</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.09617930820846965</v>
+        <v>-0.09961691280138041</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.09842401063782802</v>
+        <v>-0.1018583788246374</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.02647648380860801</v>
+        <v>-0.03004910515689119</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1331855936465729</v>
+        <v>-0.1366125212896918</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.02623987430617092</v>
+        <v>-0.02981736994737361</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.08898619541687225</v>
+        <v>-0.09255874306512624</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1693218529953171</v>
+        <v>-0.1728117597035705</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1218648856444062</v>
+        <v>-0.1070418542051641</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.09208524001311247</v>
+        <v>-0.07743177632680442</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.1464472179333001</v>
+        <v>-0.1317074441015293</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.233131606569458</v>
+        <v>-0.2182828203236298</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.2139503146856256</v>
+        <v>-0.217379154387018</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.1932097816056597</v>
+        <v>-0.1966546395725501</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.1028157936133383</v>
+        <v>-0.1064076105563956</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.09880304851251509</v>
+        <v>-0.1024067056337898</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.1442571454490675</v>
+        <v>-0.147790018046166</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.1094577630813589</v>
+        <v>-0.1130403441644035</v>
       </c>
     </row>
     <row r="32">
@@ -7960,79 +7960,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3284</v>
+        <v>3288</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.4234410307885952</v>
+        <v>-0.4242962224624733</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2887887534259761</v>
+        <v>-0.2898233075521759</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2598899714706775</v>
+        <v>-0.2610288780082968</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2003209640182462</v>
+        <v>-0.2015667505094356</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.0945152208153317</v>
+        <v>-0.09710169531865631</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.04917075659541581</v>
+        <v>0.04641781375435983</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.191617197141035</v>
+        <v>-0.1941173030919785</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.08928634423396886</v>
+        <v>-0.09192522101469791</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.06071267681574</v>
+        <v>-0.06338576656764161</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.02882034716508741</v>
+        <v>-0.03157076166928618</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.07047690787935323</v>
+        <v>-0.07316533364616618</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.02864247403081777</v>
+        <v>-0.03139662045366265</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.07328521659828624</v>
+        <v>-0.07604086280831979</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1552429454737876</v>
+        <v>-0.1579114855087624</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.128076408709866</v>
+        <v>-0.130811219513788</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.09194525535542653</v>
+        <v>-0.09469696969696884</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.1775894980935462</v>
+        <v>-0.1802453661585091</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.203698873445866</v>
+        <v>-0.206329734600061</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.182293111521922</v>
+        <v>-0.184941200600754</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.1292579075425806</v>
+        <v>-0.1319630631026598</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.04597649661583603</v>
+        <v>-0.04881073378625445</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.1037111554500569</v>
+        <v>-0.1064805696470899</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.08467710181140831</v>
+        <v>-0.08745808301504354</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.08155793462544381</v>
+        <v>-0.08434806830843655</v>
       </c>
     </row>
     <row r="33">
@@ -8042,79 +8042,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3308</v>
+        <v>3312</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.3567992802629547</v>
+        <v>-0.3574887925923846</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2555431666413668</v>
+        <v>-0.2563677630115393</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2071830258149987</v>
+        <v>-0.2081224087575606</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1832233899821034</v>
+        <v>-0.184220029475199</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2010391421514299</v>
+        <v>-0.2030058857058208</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.02700531046136945</v>
+        <v>-0.02917502045916365</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2115063626479596</v>
+        <v>-0.2134859013317225</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1119315690452538</v>
+        <v>-0.1140429338103743</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1133645304811708</v>
+        <v>-0.1154738347145638</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.08730908151196104</v>
+        <v>-0.08948132663237374</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.156810902348596</v>
+        <v>-0.1588900969327511</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.1474429185272541</v>
+        <v>-0.1495456194690803</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1095412693702755</v>
+        <v>-0.1117350248652969</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1925182369512015</v>
+        <v>-0.1946221112177469</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.1401794426988019</v>
+        <v>-0.142373563425565</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1000066154974277</v>
+        <v>-0.1022270901788929</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.1256722302397719</v>
+        <v>-0.1278684001363217</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1825121607248477</v>
+        <v>-0.1846452866860986</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.1596894340146449</v>
+        <v>-0.1618428989713507</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.1358695652173978</v>
+        <v>-0.1380457257552621</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.087333601386959</v>
+        <v>-0.08959108772013025</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.115001386090718</v>
+        <v>-0.1172298455384535</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.03367464690428079</v>
+        <v>-0.03599181283200181</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.0008839107038056682</v>
+        <v>-0.003245067497402943</v>
       </c>
     </row>
     <row r="34">
@@ -8124,79 +8124,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3333</v>
+        <v>3337</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1878281995529392</v>
+        <v>-0.1884661610510179</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1195800798586077</v>
+        <v>-0.1203098302098908</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.08227108752240042</v>
+        <v>-0.08308905968114288</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1532470054584962</v>
+        <v>-0.1540024017628099</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2034781437963105</v>
+        <v>-0.2049381083450967</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.05918891654336278</v>
+        <v>-0.06081619964132301</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1883888674173448</v>
+        <v>-0.189886348926116</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1812088538931107</v>
+        <v>-0.1827242524916954</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1823418008796267</v>
+        <v>-0.1838555499496479</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.192159148075298</v>
+        <v>-0.1936855086887661</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.199350246517362</v>
+        <v>-0.200860695069899</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1622555322106862</v>
+        <v>-0.1638196865882833</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1928570631687734</v>
+        <v>-0.1944196626546315</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1871540462687307</v>
+        <v>-0.1887311527686961</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.1401343383842502</v>
+        <v>-0.1417886136961428</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.1257405516902637</v>
+        <v>-0.1273950264981636</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.09234521910367732</v>
+        <v>-0.09404472868401115</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.1495356318077157</v>
+        <v>-0.1511709337382214</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.09529724079718704</v>
+        <v>-0.09699191550785713</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.07023524123464142</v>
+        <v>-0.07195527300045512</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.00386194112195426</v>
+        <v>0.002035613628301292</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.02414047213681414</v>
+        <v>-0.02593664325812739</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.00132390943618077</v>
+        <v>-0.003140129366329347</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>0.0006579605328909111</v>
+        <v>-0.001164023312668405</v>
       </c>
     </row>
     <row r="35">
@@ -8206,79 +8206,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.04018488839690093</v>
+        <v>-0.04084711343196545</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.03303579279868529</v>
+        <v>-0.03371519808883505</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.03195968783537495</v>
+        <v>-0.03267646214690245</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1057835717836824</v>
+        <v>-0.1064309067086597</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1574041120420944</v>
+        <v>-0.1586200247398963</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.04261898317950141</v>
+        <v>-0.04396726077068536</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1449655678675512</v>
+        <v>-0.1462123370605894</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1390467304985066</v>
+        <v>-0.1403082362039427</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1399769128987884</v>
+        <v>-0.1412370705769916</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1531904248968416</v>
+        <v>-0.1544549280921288</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1591133816529435</v>
+        <v>-0.1603648089728935</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.18294205794205</v>
+        <v>-0.1841728968922425</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1291223420524688</v>
+        <v>-0.1304460173452</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1541942395949292</v>
+        <v>-0.1554944310611859</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1103190966187313</v>
+        <v>-0.1116887711401162</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.09332107596001293</v>
+        <v>-0.09469696969696884</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1202774321738147</v>
+        <v>-0.1216254195651842</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.1478747701205236</v>
+        <v>-0.1491933453377925</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.09291167513132592</v>
+        <v>-0.0942911626663232</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.09695704057278931</v>
+        <v>-0.09832786990124731</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.02563102672399964</v>
+        <v>-0.02710134345603876</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.05385695717787797</v>
+        <v>-0.05529639179295742</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.02992075799719629</v>
+        <v>-0.03138272513338336</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.02829654782117075</v>
+        <v>-0.02976323244039492</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/roc/roc_3.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/roc/roc_3.xlsx
@@ -618,1887 +618,1887 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.02007</t>
+          <t>X ≈ -0.02004</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>17.66754466338924</v>
+        <v>15.58299415145277</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.148797433519164</v>
+        <v>0.05959180638927819</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.81862428425206</v>
+        <v>6.456969228282496</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.112891001864767</v>
+        <v>5.870304638813955</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.677903261110103</v>
+        <v>-2.05197412686978</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-6.241043757802046</v>
+        <v>-9.548716450617327</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.09516490094328134</v>
+        <v>-2.689545019942663</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1822386308392367</v>
+        <v>-2.994347338854546</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.251475555702001</v>
+        <v>-2.867200025492401</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-8.023507662371586</v>
+        <v>-3.661108447849891</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-14.86794931708879</v>
+        <v>-11.05359319959361</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.033162195345469</v>
+        <v>-11.33286367670807</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-2.035725941095343</v>
+        <v>2.886995207812639</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>4.864645219961375</v>
+        <v>10.30973249113942</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-2.913591965618885</v>
+        <v>1.961007950712812</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>4.804276217905837</v>
+        <v>2.521484721905772</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>11.80008160037846</v>
+        <v>10.09499828314218</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-2.560994852192309</v>
+        <v>-5.391733616169724</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>11.91819294492311</v>
+        <v>10.18262895260879</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>19.24267702087243</v>
+        <v>18.08318275069627</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>18.70640856055982</v>
+        <v>17.52167174615929</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>11.497593228913</v>
+        <v>9.763996696238657</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>18.91611723177098</v>
+        <v>17.70043315101608</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>18.84596128170895</v>
+        <v>17.54354662443965</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01871</t>
+          <t>X ≈ -0.01868</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-11.54754860374576</v>
+        <v>-10.61158287428154</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.278415611015859</v>
+        <v>-3.76144527448308</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9.477149814773192</v>
+        <v>9.186796025061419</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.062346446778797</v>
+        <v>1.50053397961419</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-22.23981261324438</v>
+        <v>-20.08144970666454</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-10.06621077716528</v>
+        <v>-5.722709646572987</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-18.49112873078934</v>
+        <v>-13.62294656138025</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-11.11861948288064</v>
+        <v>-6.822103008303372</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-11.08009257207848</v>
+        <v>-13.80710713079214</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-34.83342865940492</v>
+        <v>-35.94361673020448</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-34.57066609397869</v>
+        <v>-35.68291860649683</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-19.52990001497159</v>
+        <v>-21.73482959912844</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-20.65539473374248</v>
+        <v>-22.85271631798162</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-20.88221927302563</v>
+        <v>-23.10722055131013</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-21.54441934301838</v>
+        <v>-23.79399856942909</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-5.610321883263424</v>
+        <v>-8.989530198403529</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-5.745599703949757</v>
+        <v>-9.095829553399703</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-13.53017445664599</v>
+        <v>-16.36101502983149</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>2.042788623281979</v>
+        <v>-1.887384830698821</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>2.229989336655557</v>
+        <v>-1.673612918830457</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>9.374033342493441</v>
+        <v>4.895494209145824</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>9.301056482340407</v>
+        <v>4.821846838554812</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>17.26821509979369</v>
+        <v>12.20752547408629</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>17.19760963335555</v>
+        <v>12.04904112993577</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.01735</t>
+          <t>X ≈ -0.01732</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>15</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>19.56377384460229</v>
+        <v>19.65644279641524</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12.6132895828944</v>
+        <v>12.79619841653555</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-8.692931217681689</v>
+        <v>-8.322449813728852</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.775251594891046</v>
+        <v>-2.286331401007182</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.110437434780025</v>
+        <v>-2.561243059836677</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>16.96673777016677</v>
+        <v>17.48559826844276</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9.570676510033202</v>
+        <v>10.0663881278833</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.973222668287754</v>
+        <v>-3.504411726256663</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.932571694563222</v>
+        <v>-3.377301425101955</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-4.703216752963435</v>
+        <v>-4.170966868310806</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-11.07206802229454</v>
+        <v>-10.54164866292857</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-11.35381883741324</v>
+        <v>-10.82105529662854</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-19.12145625408957</v>
+        <v>-18.58044866295867</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-12.70128087572655</v>
+        <v>-12.18699921825844</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-6.712461356850881</v>
+        <v>-6.221832036689932</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-12.772387094042</v>
+        <v>-12.31470055278823</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-12.90983560039771</v>
+        <v>-12.42201616630307</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.2911323552830751</v>
+        <v>0.751301045403622</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-12.80660144949391</v>
+        <v>-12.34786369075174</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-5.965258547250528</v>
+        <v>-5.478554760806354</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-13.16970849451484</v>
+        <v>-12.70775155332237</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-13.24946778431869</v>
+        <v>-12.78666250496306</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-19.64375438538423</v>
+        <v>-19.21165387455721</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-13.05880062305144</v>
+        <v>-12.71286363197062</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.01599</t>
+          <t>X ≈ -0.01596</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>26</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.615882499637458</v>
+        <v>-3.51743035964315</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11.33841990352764</v>
+        <v>11.5216083375073</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.266639295740234</v>
+        <v>2.634305689846641</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.382901453783163</v>
+        <v>5.869683825223369</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.050193791665393</v>
+        <v>5.597231595599574</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>9.060218118516232</v>
+        <v>9.578745688266601</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8.294623847594004</v>
+        <v>8.790263535922662</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.192359473164075</v>
+        <v>4.661424942258904</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8.064141252699287</v>
+        <v>8.619774845221961</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.297161994256086</v>
+        <v>7.829750252222468</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.08935101711264792</v>
+        <v>0.4413490804431888</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.199957891583708</v>
+        <v>-3.667036389757229</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.345890427644491</v>
+        <v>2.88738463997467</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.794793968121709</v>
+        <v>10.30954536753766</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>5.306111407699298</v>
+        <v>5.796959500852047</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2.063648972339905</v>
+        <v>2.521578156403194</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.930664534638304</v>
+        <v>2.418695555087282</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>9.50506221171203</v>
+        <v>9.96534272410517</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>9.723439270594845</v>
+        <v>10.18241362619811</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>6.071451431979327</v>
+        <v>6.558253446681519</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>5.531304898681576</v>
+        <v>5.993379103855688</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>5.457187899480694</v>
+        <v>5.920071609935313</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>5.733206963102546</v>
+        <v>6.165361213668625</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>5.659148094894881</v>
+        <v>6.005085085978102</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01463</t>
+          <t>X ≈ -0.0146</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.08416270679762761</v>
+        <v>0.02954097495670993</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-23.39108264843014</v>
+        <v>-21.499890330288</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-17.29273518540576</v>
+        <v>-15.65543202230212</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-14.2400584876063</v>
+        <v>-12.69895716221522</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.772637686385409</v>
+        <v>-5.87526798330957</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.745460777270992</v>
+        <v>1.381124627305617</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>12.12013618599818</v>
+        <v>7.696291307219013</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.192033549265417</v>
+        <v>0.2867852202785031</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.235036154461817</v>
+        <v>0.4149048260724939</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.296678173339942</v>
+        <v>3.178737639568311</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>11.40327351736693</v>
+        <v>7.008713082960227</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>7.296408549941518</v>
+        <v>3.176281799560854</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.178979550412897</v>
+        <v>2.065808384437254</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.125546641221021</v>
+        <v>-1.742140255200731</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>5.305881886907123</v>
+        <v>1.139152762749085</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>5.900300294987403</v>
+        <v>1.699306122291944</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>1.930597915755257</v>
+        <v>-1.967633097386631</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.012463770872984</v>
+        <v>-5.665700231561729</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.797576834799784</v>
+        <v>-5.453344755497255</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.229895196515308</v>
+        <v>-1.67359672513355</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>1.688608897735051</v>
+        <v>-2.240936210085266</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>5.457134978535827</v>
+        <v>1.252530083465309</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>9.578152349648676</v>
+        <v>5.066764383678226</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>1.812994248741042</v>
+        <v>-2.236673155780146</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01327</t>
+          <t>X ≈ -0.01325</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>11.57926529775425</v>
+        <v>14.13184019344356</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>13.78597905980988</v>
+        <v>11.51547623454498</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>14.8733352823313</v>
+        <v>12.60846954927398</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>9.046584994276927</v>
+        <v>6.233442336049499</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>18.91208127725919</v>
+        <v>17.79613284467257</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>14.00562654327796</v>
+        <v>15.58770306371731</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10.66969630488088</v>
+        <v>10.06394652988733</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5.284291787000384</v>
+        <v>5.025236530747165</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.332575534621547</v>
+        <v>-1.955103632451049</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.123687247915697</v>
+        <v>-2.748301514260277</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.401569997234972</v>
+        <v>-4.849022697427522</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-8.241187558537334</v>
+        <v>-7.498686375920357</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.722194048791145</v>
+        <v>-1.493676328574487</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>8.282208378301462</v>
+        <v>7.752451832032257</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2.493096433239174</v>
+        <v>2.326261812328426</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.5450721568741628</v>
+        <v>2.886756072333128</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>5.525953477823379</v>
+        <v>7.535720293863797</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2.858597444650059</v>
+        <v>5.028991768237475</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.040190676468967</v>
+        <v>0.4900366061181316</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.714109927257752</v>
+        <v>0.7044604471078486</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-2.405713592364727</v>
+        <v>0.1378569721264711</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.9492091622049728</v>
+        <v>0.0627729866600788</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.888173380254969</v>
+        <v>2.68651340764896</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.7511083153594811</v>
+        <v>0.1442792251722409</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01191</t>
+          <t>X ≈ -0.01189</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.466193948438466</v>
+        <v>1.708471278871706</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4.104021961489643</v>
+        <v>4.081238819089435</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.594428176045767</v>
+        <v>5.450688684943643</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-14.75328315903293</v>
+        <v>-10.82873112194132</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.031342570275555</v>
+        <v>-3.259350161144191</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-6.589522247194004</v>
+        <v>-5.723160108663926</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.9023065960506074</v>
+        <v>1.337043783021713</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.6061132038325709</v>
+        <v>1.034533271393897</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.640542193751763</v>
+        <v>1.163343714565471</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.943082178993947</v>
+        <v>-2.24892880792958</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-5.431902101491239</v>
+        <v>-4.598907988347911</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.340493852599501</v>
+        <v>-2.25449320547969</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.051436419079579</v>
+        <v>1.878318212447908</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.832413941382207</v>
+        <v>1.630622614242149</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2.153420161640831</v>
+        <v>0.9515198300650169</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-2.780255726158273</v>
+        <v>-3.738467451652518</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.91792666118247</v>
+        <v>-3.843305934177565</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.2547686324400473</v>
+        <v>-1.350255962851833</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.03362105596200848</v>
+        <v>-1.136513783261606</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-2.614894845381023</v>
+        <v>-0.9226016647175328</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.398871562290914</v>
+        <v>-1.489692114407674</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-3.252475258354401</v>
+        <v>-4.195217666940479</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.315963573591269</v>
+        <v>-3.953037172638759</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.392133956386921</v>
+        <v>-4.116372403900435</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01055</t>
+          <t>X ≈ -0.01053</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-13.18489904506225</v>
+        <v>-12.08796704078044</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-5.867706206113155</v>
+        <v>-4.852946330574298</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-11.12852972848809</v>
+        <v>-11.77652349016878</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.267975777616932</v>
+        <v>-1.141224814257541</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.139643488443213</v>
+        <v>3.389316297325053</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.5040938608495011</v>
+        <v>0.8439504923092755</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.6409801057836617</v>
+        <v>0.05277645514581764</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.550578461803106</v>
+        <v>-0.2500707506123874</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.4067473122201832</v>
+        <v>1.756200623800844</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.279368633224841</v>
+        <v>-2.792390254628174</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.744451293033777</v>
+        <v>3.115572092027598</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.3677084150454419</v>
+        <v>0.9609165053303883</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.264312725107381</v>
+        <v>3.609916291334919</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.126315828632961</v>
+        <v>3.362784709039801</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.366698312010513</v>
+        <v>-1.078504970139328</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-7.532335223086847</v>
+        <v>-6.165005664586765</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-3.828428042962095</v>
+        <v>-2.505431345762396</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-9.696103997358527</v>
+        <v>-8.288297106499542</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-7.562253679207728</v>
+        <v>-6.192977425772824</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-3.534287144100681</v>
+        <v>-2.211894926155821</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2328105203982105</v>
+        <v>0.9906065681387304</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.61382648761289</v>
+        <v>2.80140548163709</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>1.888150783259917</v>
+        <v>3.045766506425771</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.1100826743345777</v>
+        <v>0.9978281919291803</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.009192</t>
+          <t>X ≈ -0.00917</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.409118615981065</v>
+        <v>-5.811722952893255</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.742983849631429</v>
+        <v>-6.056928039079665</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.436394556648516</v>
+        <v>-2.717288324509454</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12.07485626299633</v>
+        <v>10.46028583880052</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.257940474685952</v>
+        <v>1.006822650073332</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.023553565231403</v>
+        <v>2.690716377435784</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.673969027260824</v>
+        <v>3.43030915811093</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.559279805871178</v>
+        <v>4.659147115775269</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.602734622169969</v>
+        <v>4.789027718360352</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.834556904229281</v>
+        <v>3.998739449101379</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.9448590527281198</v>
+        <v>1.20735526413678</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>10.15970165989405</v>
+        <v>10.12685795567518</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.876945224727656</v>
+        <v>7.485296806149471</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>8.824125001214284</v>
+        <v>8.772946573981706</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>5.003732914180311</v>
+        <v>5.02859218170628</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>7.183011584994389</v>
+        <v>7.124749140882386</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>5.466780848139635</v>
+        <v>5.488229983939625</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>8.534558420182123</v>
+        <v>9.964146204341631</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>5.581453204098104</v>
+        <v>7.109475878817022</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>5.769864331375956</v>
+        <v>7.32590422730874</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>3.642607755458727</v>
+        <v>5.224477445100746</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.979987815111876</v>
+        <v>3.6135847274927</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>3.841090856899037</v>
+        <v>5.396199522130722</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>5.353897789645096</v>
+        <v>6.774315855208521</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.007831</t>
+          <t>X ≈ -0.00781</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-16.1109490491974</v>
+        <v>-14.55528827795346</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.212807187438656</v>
+        <v>-5.142110576669403</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-14.98656929947697</v>
+        <v>-13.29423262302163</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-9.853889919514508</v>
+        <v>-9.742052358512659</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-10.19035059292052</v>
+        <v>-11.39785959545284</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-5.606968757575132</v>
+        <v>-5.721271912570835</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-10.77767879372093</v>
+        <v>-12.03880573428263</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-9.598297431180733</v>
+        <v>-9.582529430408876</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-8.095979790103591</v>
+        <v>-9.457268429351828</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-10.34778065067076</v>
+        <v>-8.869547829112321</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-11.5417003700623</v>
+        <v>-11.36672702090775</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-10.3546392777722</v>
+        <v>-11.6470725275875</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-10.62427114613556</v>
+        <v>-12.76244669476925</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-13.78236772745589</v>
+        <v>-14.39927562759468</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-11.50819683899989</v>
+        <v>-12.31339006936848</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-9.450996569586572</v>
+        <v>-10.3723192716919</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-9.587884817221315</v>
+        <v>-10.47948148961192</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-9.695581350109229</v>
+        <v>-9.22923565910807</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-9.483080889968242</v>
+        <v>-9.018097566225478</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-13.70844511084995</v>
+        <v>-12.96807329847061</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-11.3151101143831</v>
+        <v>-10.76409018268567</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-8.450737955308526</v>
+        <v>-8.066793667817727</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-6.706338763177989</v>
+        <v>-5.04912986170244</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-3.843114348543153</v>
+        <v>-2.435085854192842</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.006471</t>
+          <t>X ≈ -0.006452</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.9534678782475723</v>
+        <v>0.4408816642611058</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.952230715860054</v>
+        <v>-2.441246711986146</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>6.16743556616732</v>
+        <v>5.986507546178771</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.791932565658854</v>
+        <v>2.757874996475117</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.567583492195467</v>
+        <v>1.603437453696557</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.085603825216054</v>
+        <v>6.153952358807089</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.427922396836273</v>
+        <v>5.365740383952932</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.263755837002591</v>
+        <v>4.184322907907074</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4.307045441173855</v>
+        <v>4.314142044007319</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.5389699247674</v>
+        <v>3.524059034688655</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.703873024677115</v>
+        <v>4.678041321913859</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.754873608900908</v>
+        <v>1.759056443870946</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.524685758111822</v>
+        <v>1.529869953419663</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4137037324615136</v>
+        <v>0.4001758698670912</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.2418375679659945</v>
+        <v>-0.2786406609272163</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.430779247829847</v>
+        <v>-1.484109477838544</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.2175479468252348</v>
+        <v>0.1772251031286416</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.1130642021571902</v>
+        <v>0.04475656543954187</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-2.347045509234825</v>
+        <v>-2.391414581889492</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.5154610772154058</v>
+        <v>0.4731563212763348</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.9193168804718326</v>
+        <v>-0.9775752479302753</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1026147530712151</v>
+        <v>-0.1687585054685456</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.505980387960079</v>
+        <v>-2.579379065836882</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.582610146862486</v>
+        <v>-2.742362157044361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.005111</t>
+          <t>X ≈ -0.005094</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>135</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4.055576995582577</v>
+        <v>3.473764738987427</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.120434517740378</v>
+        <v>3.966798645884218</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.154703164918047</v>
+        <v>5.664507575489274</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7.128833659656287</v>
+        <v>8.018993378000793</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>6.055203346524166</v>
+        <v>6.272434565597898</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.769210212983239</v>
+        <v>4.952148118021967</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.519907779288388</v>
+        <v>2.691697968707963</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.717054353829297</v>
+        <v>3.862880694066149</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.283501497854019</v>
+        <v>2.519273644384853</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.7688972927700917</v>
+        <v>0.9920722597709286</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.687494989448702</v>
+        <v>3.475857177789742</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.147410053009814</v>
+        <v>3.938472248995588</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.288957880546718</v>
+        <v>2.090891121405846</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.1469963127735525</v>
+        <v>-0.3707301006521959</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.06364585504510245</v>
+        <v>-0.3111912337467189</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.2096083305053824</v>
+        <v>-0.4901923652576343</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.874567465116662</v>
+        <v>1.622247807893942</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.770716723142996</v>
+        <v>1.490338548903061</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.466963393082978</v>
+        <v>3.183943621106344</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>3.654692460469747</v>
+        <v>3.399064437987334</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>5.335058724159133</v>
+        <v>5.05334744644172</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>6.740143737501405</v>
+        <v>6.460352617978209</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>7.754914260627217</v>
+        <v>7.446565292573716</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>5.459717895465566</v>
+        <v>5.064914145807158</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.00375</t>
+          <t>X ≈ -0.003734</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.120059524691662</v>
+        <v>-0.4582736183770493</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.839801308673856</v>
+        <v>-1.22776082933234</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.992985723977036</v>
+        <v>-5.846489637432121</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.62883601525489</v>
+        <v>-5.920088313415356</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-5.965631905074574</v>
+        <v>-5.676235495841539</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.9018028885311367</v>
+        <v>-0.8330620086675609</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.762525954438473</v>
+        <v>-2.673695280729959</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.8776008962031696</v>
+        <v>-0.08361836903988973</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.413160795400948</v>
+        <v>2.648094789424981</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.077748830321951</v>
+        <v>-0.9717655211668657</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.511343594298438</v>
+        <v>-3.305760339677512</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-5.416685421731607</v>
+        <v>-4.625520765928655</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.212070535912524</v>
+        <v>-0.5245200577718023</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.7396418348089</v>
+        <v>-2.337021459237413</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-4.402339270598887</v>
+        <v>-3.016281126510101</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.095778395367205</v>
+        <v>0.1518475788042863</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.857757801641213</v>
+        <v>-1.518813536815685</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.879028319519534</v>
+        <v>-0.6071359369135365</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.663164709012278</v>
+        <v>-0.3932469978041269</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.6979437690348718</v>
+        <v>1.91153991939197</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.3906764047900566</v>
+        <v>0.8226001490900359</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.552886863688961</v>
+        <v>-0.2985884329413082</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.7319737690908283</v>
+        <v>0.4681331534625457</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.029815115806578</v>
+        <v>-0.2172266337158177</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.00239</t>
+          <t>X ≈ -0.002376</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.417970304571213</v>
+        <v>2.556065408687644</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-4.349512250047432</v>
+        <v>-4.165553505232147</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.517371004764449</v>
+        <v>-2.826003254152376</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.20217778164271</v>
+        <v>-0.4518459880210983</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.7345468539762265</v>
+        <v>1.497608503935034</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.057657934156616</v>
+        <v>2.397949609831187</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.664560183926348</v>
+        <v>1.810166186217444</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.008200419335957</v>
+        <v>1.134636710039736</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.6291591507186212</v>
+        <v>-0.2209482027391374</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.255528469086457</v>
+        <v>1.582855676854692</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.529235661014461</v>
+        <v>1.855592383184259</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.76738337397483</v>
+        <v>3.278916652386748</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.2488161488440639</v>
+        <v>-0.05945337807933271</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.4691901248225392</v>
+        <v>-0.3065910731499102</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>3.04700564648504</v>
+        <v>3.475783949413461</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.364457155265114</v>
+        <v>1.804746906037167</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.425939159800691</v>
+        <v>-0.9025280866104453</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.531239206518507</v>
+        <v>-1.035491668512087</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.696164345226123</v>
+        <v>-1.194228315689223</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.7502955684492036</v>
+        <v>-0.2362274591370621</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.9129025708392575</v>
+        <v>-0.430159614164026</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.2282922584841955</v>
+        <v>0.2401592189625461</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.094501956648436</v>
+        <v>-0.635229718065986</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.7901060729895022</v>
+        <v>-0.4243064180402669</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.00103</t>
+          <t>X ≈ -0.001017</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.062997009497558</v>
+        <v>-0.8100180347683477</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.478295003356656</v>
+        <v>2.482123953947934</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.5797442017594463</v>
+        <v>-0.381578806711957</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.1388610491746434</v>
+        <v>-0.3306231899573575</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.121477697705799</v>
+        <v>-1.571227801335247</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.522532979168297</v>
+        <v>-3.665471421682788</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.4131010650138265</v>
+        <v>-0.2791467939325543</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.5073604081180747</v>
+        <v>-0.2624565650999955</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.112117210410844</v>
+        <v>-0.9182618153673161</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.7072219445187997</v>
+        <v>0.8625389698486856</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3133384166151103</v>
+        <v>-0.1523700831276429</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.915478673645886</v>
+        <v>-1.072650235469936</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.09361643930606078</v>
+        <v>-0.2541452065638339</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.902124026976772</v>
+        <v>-2.88833890721606</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-4.530567048993902</v>
+        <v>-4.535025746895435</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-4.587690572222499</v>
+        <v>-4.62300401907325</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.455134880273206</v>
+        <v>-2.793269144884782</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-3.533646009758563</v>
+        <v>-3.572508469720738</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-2.022489828995035</v>
+        <v>-2.391886477067779</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-3.135321189057237</v>
+        <v>-3.471990741942243</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-3.354757294062807</v>
+        <v>-3.716869343779337</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-5.053979878848459</v>
+        <v>-5.087146932360262</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-5.104180491041809</v>
+        <v>-5.169716916787692</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-2.907285471537882</v>
+        <v>-3.068850686986799</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0003301</t>
+          <t>X ≈ 0.0003417</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.606569734026806</v>
+        <v>1.428391430527846</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.274021125241731</v>
+        <v>0.4429799540396147</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.087435457319117</v>
+        <v>0.4340434518930181</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.873282307470312</v>
+        <v>-1.396909002455075</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.205346153363799</v>
+        <v>-3.158028555218777</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.519491824720269</v>
+        <v>-3.997438943772984</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.04442543252685</v>
+        <v>-2.312581188117683</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.571706613921521</v>
+        <v>-2.864512788650792</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.282084138638801</v>
+        <v>-1.249275231343496</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1613577240854411</v>
+        <v>-0.3072940475276482</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1129193073554475</v>
+        <v>-0.03473991426388068</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.163532004207703</v>
+        <v>-1.05440941304208</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.282563674763047</v>
+        <v>-2.020511773169417</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.751996586299185</v>
+        <v>-1.520925122493871</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.1604900533872495</v>
+        <v>0.2812271622972702</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.817122384365931</v>
+        <v>-1.393803581876817</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-3.452659961827244</v>
+        <v>-2.988624803869875</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-3.309277670727738</v>
+        <v>-3.122768865976909</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-3.597204795634809</v>
+        <v>-3.408988470754338</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.664031880117015</v>
+        <v>-3.447311013925209</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.454780078296118</v>
+        <v>-2.273306764868799</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-3.533132305369378</v>
+        <v>-3.595397927455593</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-3.008031026471315</v>
+        <v>-2.856319395829054</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-3.3344898461106</v>
+        <v>-2.771051495644741</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.00169</t>
+          <t>X ≈ 0.001701</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.322297698113694</v>
+        <v>1.560791751490662</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.25434860443815</v>
+        <v>2.84586417773734</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.692450404365808</v>
+        <v>1.078507519691577</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.507876108646705</v>
+        <v>2.018076338472397</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.67974106828602</v>
+        <v>2.252734423952255</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.617210280021432</v>
+        <v>1.900377442967113</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.099089312224301</v>
+        <v>1.360337426481451</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7996122332176725</v>
+        <v>0.03366219106300861</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.860741021236763</v>
+        <v>1.183081424586682</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.084306617543554</v>
+        <v>0.3861704078139354</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.632647595977744</v>
+        <v>2.33783149325879</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.07772215675007</v>
+        <v>0.7848523883382086</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2043277356141289</v>
+        <v>-0.07299043249185644</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.4900922772794658</v>
+        <v>0.1905453275652675</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.2396802610977531</v>
+        <v>-0.3361542658794505</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.499740009462236</v>
+        <v>0.7348012131250812</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.620859220685297</v>
+        <v>0.8872172147981772</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.4941356347349739</v>
+        <v>-0.2697582485163466</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.05739189380324916</v>
+        <v>-0.5696955630441209</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.664071382954248</v>
+        <v>1.438002814081052</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.5097924784153847</v>
+        <v>0.3569019252484651</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.9454554684129093</v>
+        <v>0.4381884939908645</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.05884219762164378</v>
+        <v>-0.3473185388372713</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.6461834022516015</v>
+        <v>-1.024774514575618</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.003051</t>
+          <t>X ≈ 0.00306</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.450719145757652</v>
+        <v>-2.847626600279582</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.6143586544227304</v>
+        <v>0.4657212060954166</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.478410662385521</v>
+        <v>2.049391065469855</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.06107525073997522</v>
+        <v>0.3883787104674141</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.94944159425156</v>
+        <v>4.38813884100891</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.314974393414644</v>
+        <v>1.345385499470716</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1595794017134722</v>
+        <v>0.1920522614910354</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.489744604261759</v>
+        <v>-1.898858435469478</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.801513887027525</v>
+        <v>-1.769174234057758</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.1069631531961051</v>
+        <v>-0.4319548232756674</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.241666295439835</v>
+        <v>-1.583948253021077</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.2426693187772671</v>
+        <v>-0.08243876671463823</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.181408183120439</v>
+        <v>-0.4917990059688861</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.036473387589119</v>
+        <v>-0.3874865397696254</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.3644421964855979</v>
+        <v>-0.004541348915644505</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.9570528374634932</v>
+        <v>0.7744727733554484</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.937242689456475</v>
+        <v>3.026188685406694</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.130207575199407</v>
+        <v>2.402019237006286</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3.757185278026036</v>
+        <v>4.043003503592459</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.2951169128894122</v>
+        <v>-0.03290292929636252</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.897733752233655</v>
+        <v>-1.315131912095389</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.620222823183347</v>
+        <v>-0.3160932277196267</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.345748110701294</v>
+        <v>-0.4339066989507785</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.128294144843302</v>
+        <v>-1.315014169605064</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.004411</t>
+          <t>X ≈ 0.004418</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.4500111775331703</v>
+        <v>0.8350679371016412</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.703657094142542</v>
+        <v>-2.172708411874289</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.404363605282754</v>
+        <v>0.7183777920190551</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.2367206870759304</v>
+        <v>0.1260838126972601</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.462932664359293</v>
+        <v>-1.070855034897718</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-3.094348408077124</v>
+        <v>-3.216940319693215</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.95708914227621</v>
+        <v>-3.090749843916619</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5076087988206694</v>
+        <v>-0.6320692622703348</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.807424785616632</v>
+        <v>1.797255245910854</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.853060887232289</v>
+        <v>2.383058372962239</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.127120529394212</v>
+        <v>2.655293387566573</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.666922903598248</v>
+        <v>4.220715311681666</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.997940191995419</v>
+        <v>4.028177877104511</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.776555589442381</v>
+        <v>3.320443876274268</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5.391618998710577</v>
+        <v>4.940875507237031</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>4.622109072198228</v>
+        <v>4.120541342758912</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.857128279440666</v>
+        <v>3.095821320970352</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>4.214645380049056</v>
+        <v>3.424493325448076</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>5.799406059355839</v>
+        <v>5.023450249778335</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.25136000596747</v>
+        <v>2.011754135860514</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>6.361781874531154</v>
+        <v>5.601268560816507</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>6.285935913122053</v>
+        <v>5.062408013078191</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>5.190547611905473</v>
+        <v>4.387520302723637</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.744852344983578</v>
+        <v>2.657506738399782</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.005771</t>
+          <t>X ≈ 0.005777</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.321865863653109</v>
+        <v>-5.157024005657476</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3387078656569074</v>
+        <v>-2.106256094805538</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.873910983777435</v>
+        <v>-0.05928425959263706</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.489079936936434</v>
+        <v>0.006849900422508881</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.4903064486148736</v>
+        <v>-0.9302393128294355</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.673123893405347</v>
+        <v>1.193319226651148</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.085782037554168</v>
+        <v>-3.543996795534198</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.702736019375529</v>
+        <v>-3.184391451460968</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.322074912181925</v>
+        <v>-3.72298480547817</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.095853364639694</v>
+        <v>-3.199967106831302</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.821793722477771</v>
+        <v>-2.927732092226968</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.101405902347011</v>
+        <v>-3.20331580858852</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9092215021209356</v>
+        <v>-1.017540227044599</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-5.11984595490047</v>
+        <v>-5.202018869771855</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-5.114574848496154</v>
+        <v>-5.224638654723755</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-2.526493608913221</v>
+        <v>-2.692716749982672</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.996564953695078</v>
+        <v>-2.138060802884311</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.627794506070828</v>
+        <v>1.02672807661952</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-2.152969711286943</v>
+        <v>-2.720430428004548</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.6390509529366071</v>
+        <v>-1.192804516901987</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.81840287909737</v>
+        <v>2.202209161025081</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.409223584354926</v>
+        <v>0.8061725383005793</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.9829683698296847</v>
+        <v>-1.60149726461276</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>-0.4391329476438699</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.007132</t>
+          <t>X ≈ 0.007136</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-6.331942979931085</v>
+        <v>-5.345411719507702</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.854254689606158</v>
+        <v>-3.803153165622682</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-4.473408240336134</v>
+        <v>-4.166607273071406</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.377097375917231</v>
+        <v>-2.074324787194975</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.619520418403489</v>
+        <v>-3.243559522038517</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-7.155652146936248</v>
+        <v>-5.767655700273039</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.205302967399767</v>
+        <v>-3.881707928273151</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.763616702335739</v>
+        <v>-1.50438028729846</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.9176649437790232</v>
+        <v>0.4165872125772694</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.688980517409</v>
+        <v>-0.3802764827425449</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-4.130018277844449</v>
+        <v>-2.792726152822866</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.738124628906313</v>
+        <v>4.984339846709695</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.622163022879676</v>
+        <v>3.866198928857081</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.843279719677028</v>
+        <v>8.981242736039938</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>8.090968940832305</v>
+        <v>9.193577148999516</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>9.586388074291335</v>
+        <v>10.65180656296515</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>7.642406002248961</v>
+        <v>8.758136361450347</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>7.542365605647419</v>
+        <v>7.728326861142705</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>7.767829834701807</v>
+        <v>7.956766023148916</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>8.876100562214859</v>
+        <v>9.084573511702132</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>11.06082712152155</v>
+        <v>11.2389654966927</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>10.07589025102165</v>
+        <v>12.05342246900806</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>13.07763769077638</v>
+        <v>13.75558166862515</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>13.00180543755315</v>
+        <v>14.49434357523659</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.008492</t>
+          <t>X ≈ 0.008495</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.705041053470069</v>
+        <v>-2.486436251920097</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.9075734294222002</v>
+        <v>1.23718072189984</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.5317098149796</v>
+        <v>-1.985132427610814</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.252750801252773</v>
+        <v>-1.591820340704764</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.3874921573712413</v>
+        <v>0.1116691382435206</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.389106871434386</v>
+        <v>-1.725682970044105</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.170406717525928</v>
+        <v>-2.509336410848221</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.495656064895925</v>
+        <v>1.157171717171721</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.397779818163109</v>
+        <v>-2.699661277906031</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.19933764412886</v>
+        <v>-1.509046106458683</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.044521321070235</v>
+        <v>0.7517603367170125</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.197793297280768</v>
+        <v>-1.522916855849545</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.334982107438783</v>
+        <v>-2.62257087806217</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-4.544562631325064</v>
+        <v>-4.836519225209592</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-2.240993572698912</v>
+        <v>-2.544387892808963</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-3.611730392692401</v>
+        <v>-3.977369588274968</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-5.723239487874864</v>
+        <v>-6.060297619047617</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-2.875718997690541</v>
+        <v>-3.207467438494859</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-3.654966247034238</v>
+        <v>-4.004862442636735</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-3.860173065147819</v>
+        <v>-4.802973363991313</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-5.392818243014787</v>
+        <v>-6.385863267670857</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-6.458763214325025</v>
+        <v>-7.461025789626198</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-8.164486521644861</v>
+        <v>-9.217391304347821</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-8.240318774868229</v>
+        <v>-9.379530298637285</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.009851</t>
+          <t>X ≈ 0.009852</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>70</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.7605469662306135</v>
+        <v>-2.028341013824885</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>8.86530285852421</v>
+        <v>9.025752150471163</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.014360007149953</v>
+        <v>6.388404987355116</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.450426440321586</v>
+        <v>2.957227278342899</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.534889920071507</v>
+        <v>4.08268954640684</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.563411175042418</v>
+        <v>7.053908866690591</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.950954586557643</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.518486867794572</v>
+        <v>5.969212533498265</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.978133673448212</v>
+        <v>7.492039402365982</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.62861344254631</v>
+        <v>8.109253213269071</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.210138468449038</v>
+        <v>2.73148822787342</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.92615324360542</v>
+        <v>2.436538926463399</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.505997435799777</v>
+        <v>6.999197829420744</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>13.41341459209649</v>
+        <v>13.85096376798767</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>5.635152576005673</v>
+        <v>6.093299182021035</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>4.801955395697505</v>
+        <v>5.229092996758993</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>8.942413251240325</v>
+        <v>9.377253401360569</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>5.99392314998741</v>
+        <v>6.427022357423368</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.364579427571556</v>
+        <v>3.813104733383526</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>6.408568094682437</v>
+        <v>6.878619662080411</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>4.437450498144948</v>
+        <v>3.471279589471898</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>5.790175965307363</v>
+        <v>4.824688496088093</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>4.636079249217943</v>
+        <v>3.639751552795033</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>7.417389853137557</v>
+        <v>7.763326844219854</v>
       </c>
     </row>
     <row r="29">
@@ -2511,76 +2511,76 @@
         <v>69</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.901896007761138</v>
+        <v>3.579526480999171</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.777206212418896</v>
+        <v>-0.9555452960435602</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.457672589141765</v>
+        <v>6.383618435053144</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9.068040000770878</v>
+        <v>10.10108511133119</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>8.725248197970842</v>
+        <v>9.834153610293214</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.457688024059806</v>
+        <v>8.565966443344429</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.815193936542776</v>
+        <v>4.886136328972313</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.97400552616628</v>
+        <v>6.021864608821147</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.6781686165035623</v>
+        <v>1.855452593729488</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.09649739209611141</v>
+        <v>1.061126426322495</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.955410041146081</v>
+        <v>7.066625761147662</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.98573521751441</v>
+        <v>-3.247913405193913</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.215597557422406</v>
+        <v>-1.498761354252672</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.426174438489859</v>
+        <v>-1.757347382559509</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2.246005025254242</v>
+        <v>1.863465799392564</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>1.392866917441566</v>
+        <v>0.9944730618285149</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>2.702974145093386</v>
+        <v>2.324340062111773</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>5.491433168220311</v>
+        <v>5.053774797529954</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.275552512457679</v>
+        <v>3.84269452860098</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.1145722354691898</v>
+        <v>0.603267932613619</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-3.326524657134456</v>
+        <v>-2.864124137236089</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>5.29328155536944</v>
+        <v>5.756365514721629</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>1.219930180894963</v>
+        <v>1.652173913043491</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>2.593373289990517</v>
+        <v>2.939310281072856</v>
       </c>
     </row>
     <row r="30">
@@ -2593,76 +2593,76 @@
         <v>36</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>7.477326743109458</v>
+        <v>9.631976446492551</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.161826132308946</v>
+        <v>1.2379214626406</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.937347236096542</v>
+        <v>5.406507784029394</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.312799200782678</v>
+        <v>-0.6091748380592037</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.8983566027307006</v>
+        <v>-0.7524578458834768</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7283410056663016</v>
+        <v>2.314528670167569</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.233572171122923</v>
+        <v>-1.522881384393173</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-7.284617471852485</v>
+        <v>-4.499759499759584</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-15.53620597431778</v>
+        <v>-15.3771215953664</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-16.31194674852646</v>
+        <v>-16.14671806413074</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-21.55812893476804</v>
+        <v>-21.45649363153692</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-10.78791938689245</v>
+        <v>-10.64841950135219</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-14.66413962251998</v>
+        <v>-17.37177722726855</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-6.58366752007008</v>
+        <v>-9.445408114098498</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-7.244635915822826</v>
+        <v>-10.10110746952852</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-6.655899190224133</v>
+        <v>-9.486893397798738</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-12.31288325377735</v>
+        <v>-15.14632936507935</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-12.40924866308196</v>
+        <v>-15.35857854960605</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-9.492563429571298</v>
+        <v>-10.70764635967453</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-9.305717619603271</v>
+        <v>-10.47976911185102</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-7.070486009791566</v>
+        <v>-6.608085489893135</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-7.146331971200667</v>
+        <v>-6.68324801184842</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-4.094079480940792</v>
+        <v>-3.661835748792264</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-4.169911734164067</v>
+        <v>-3.823974743081727</v>
       </c>
     </row>
     <row r="31">
@@ -2672,79 +2672,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.127447496967939</v>
+        <v>4.352110113994669</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.85589181447078</v>
+        <v>4.106203278290749</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.775862333955672</v>
+        <v>8.114667071136054</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.40762144869975</v>
+        <v>4.890685924959413</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.254548034437128</v>
+        <v>-0.6480301098768066</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.675452877263375</v>
+        <v>-3.122675451247105</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.7841457756568033</v>
+        <v>1.345400431256977</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.5533501677932406</v>
+        <v>1.040479987848435</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.297540052410625</v>
+        <v>3.799987844900933</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.162273047365403</v>
+        <v>0.3723574023131277</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.469776163312446</v>
+        <v>5.907750311654347</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.1669628086514763</v>
+        <v>0.3680104624461649</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.349356711342452</v>
+        <v>1.88469729236386</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.080861998006334</v>
+        <v>1.636463230930751</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-2.264178723313712</v>
+        <v>-1.677270098322722</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-1.638181243444407</v>
+        <v>-1.11596607950311</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-4.506411641050889</v>
+        <v>-3.851425438596486</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.7467372236437271</v>
+        <v>1.278848350978748</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.669598732590863</v>
+        <v>1.493310578124522</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>5.559147245261599</v>
+        <v>4.339475970551923</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>5.016601077295569</v>
+        <v>3.772031469171232</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.4646502895189428</v>
+        <v>-1.566288947520931</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>5.215229828368521</v>
+        <v>3.940503432494282</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>2.436694872442537</v>
+        <v>1.1467854908364</v>
       </c>
     </row>
     <row r="32">
@@ -2757,76 +2757,76 @@
         <v>24</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>8.859152886567976</v>
+        <v>8.957373271889402</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.357709421551554</v>
+        <v>4.544799769518924</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.086357039187227</v>
+        <v>7.456772334294008</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.206736353077758</v>
+        <v>2.697703468818943</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-14.79572078613607</v>
+        <v>-14.24452133794682</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-10.44208793337204</v>
+        <v>-9.920921065282194</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-2.880703283929151</v>
+        <v>-2.382669744181634</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-3.15891472868217</v>
+        <v>-2.687590187590196</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7.284094213434074</v>
+        <v>-6.726327944572695</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-8.057009889470564</v>
+        <v>-7.522379439792033</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-11.94961691397537</v>
+        <v>-11.41681109185436</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-16.39503298408997</v>
+        <v>-15.86005971299227</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-5.018195050946147</v>
+        <v>-4.47495183044316</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-5.239273927392794</v>
+        <v>-4.72318589187627</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-1.730750558306624</v>
+        <v>-1.238673607094654</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-1.136363636363633</v>
+        <v>-0.6773695882749351</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>7.063052559992158</v>
+        <v>7.552083333333265</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>2.791545189504319</v>
+        <v>3.252532561505063</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.007436570428702</v>
+        <v>3.466994788650837</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.9723842862699996</v>
+        <v>-0.4850854329569074</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-5.681597120902637</v>
+        <v>-5.219196601004249</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-1.590776415645131</v>
+        <v>-1.127692456292927</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>7.017031630170308</v>
+        <v>7.449275362318836</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>11.10786604361372</v>
+        <v>11.45380303469606</v>
       </c>
     </row>
     <row r="33">
@@ -2836,79 +2836,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>22.35915288656812</v>
+        <v>23.38045019496635</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>18.02437608821822</v>
+        <v>19.28838951310856</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>16.58635703918723</v>
+        <v>18.03369541121697</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.873403019744572</v>
+        <v>5.902831673947347</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4623874528027798</v>
+        <v>1.781119687694037</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.275421266705436</v>
+        <v>-1.908100552461676</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.952630049404299</v>
+        <v>4.989125127613356</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-9.325581395348834</v>
+        <v>-6.85425685425686</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-9.28409421343413</v>
+        <v>-6.726327944572752</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-14.05700988947065</v>
+        <v>-11.36853328594596</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-5.782950247308726</v>
+        <v>-3.403990579033987</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-2.061699650756687</v>
+        <v>0.165581312648591</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-11.18486171761281</v>
+        <v>-8.641618497109882</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.594059405940655</v>
+        <v>2.648608979918606</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.06408389163998152</v>
+        <v>1.966454598033522</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-3.469696969696962</v>
+        <v>-1.318395229300684</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.396385893325615</v>
+        <v>6.270032051282108</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.291545189504404</v>
+        <v>6.137147946120422</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>8.507436570428702</v>
+        <v>10.19776401942006</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>8.694282380396814</v>
+        <v>10.41235046447913</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>12.1517362124307</v>
+        <v>13.69105980925211</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>12.07589025102165</v>
+        <v>13.61589728729692</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>4.350364963503651</v>
+        <v>6.167224080267566</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>2.158931239824255</v>
       </c>
     </row>
     <row r="34">
@@ -2918,79 +2918,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>33.02581955323465</v>
+        <v>32.17165898617507</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>19.35770942155155</v>
+        <v>17.64003786475696</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>11.25302370585388</v>
+        <v>9.242486620008286</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.5400696864111</v>
+        <v>8.650084421199963</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.20427921386387</v>
+        <v>8.374526281100685</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3.724578733294592</v>
+        <v>1.388602744241673</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.619296716070899</v>
+        <v>7.736377874866051</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>9.341085271317823</v>
+        <v>7.431457431457432</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.382572453232527</v>
+        <v>7.55938634114154</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>8.609656777196136</v>
+        <v>6.763334845922245</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.883716419358059</v>
+        <v>7.035569860526579</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-4.728366317423358</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.14847161572057</v>
+        <v>12.78695293146161</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>7.260726072607255</v>
+        <v>5.395861727171358</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>6.602582775026796</v>
+        <v>4.713707345286345</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>7.196969696969688</v>
+        <v>5.275011364105964</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-6.270280773341064</v>
+        <v>-1.971726190476197</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>0.2915451895044185</v>
+        <v>-2.104610295637741</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>0.5074365704287018</v>
+        <v>-1.890148068492024</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-5.972384286269985</v>
+        <v>-1.675561623433083</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-6.514930454235966</v>
+        <v>-2.243006124813775</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-6.590776415645117</v>
+        <v>-2.31816864676906</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-6.316301703163013</v>
+        <v>-2.074534161490682</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-6.392133956386289</v>
+        <v>-2.236673155780146</v>
       </c>
     </row>
   </sheetData>
@@ -3180,1887 +3180,1887 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.02075</t>
+          <t>X &gt; -0.02072</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3352</v>
+        <v>3376</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.2258195532346932</v>
+        <v>0.2084765375557822</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.3515841498661132</v>
+        <v>0.3609661418947709</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.3230899179301829</v>
+        <v>0.3291597349415767</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.397720931962759</v>
+        <v>0.4008836808331964</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.2270222179180692</v>
+        <v>0.2596514651949349</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1340742822560088</v>
+        <v>0.1090337569531243</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.03188205296612523</v>
+        <v>0.008282215735896159</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.08092581340108751</v>
+        <v>-0.1030776089738339</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.007263077923163053</v>
+        <v>0.0415871247283377</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.03561951513906791</v>
+        <v>-0.0297540710605233</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.01177639886888215</v>
+        <v>-0.006119639115169662</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.09499334873529364</v>
+        <v>-0.1182257893402863</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1304460173452</v>
+        <v>-0.1237560819932071</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1852386309422087</v>
+        <v>-0.1775076087496643</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.08193572145251693</v>
+        <v>-0.07422259773965578</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.09469696969696884</v>
+        <v>-0.115903867234799</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.06208388934785347</v>
+        <v>-0.08413698393930957</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.0002951916749012184</v>
+        <v>-0.02215697131575212</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.02486284388714211</v>
+        <v>0.002783016985645759</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.02086164142175306</v>
+        <v>0.02773507986366752</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.0623174344873334</v>
+        <v>0.09919148225510099</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.03414904648969497</v>
+        <v>0.1008451399179151</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.03138272513338336</v>
+        <v>0.03638423607267072</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.08942910356211087</v>
+        <v>-0.01934072517756391</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.01939</t>
+          <t>X &gt; -0.01936</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3338</v>
+        <v>3363</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1526667217361393</v>
+        <v>0.1490448607848549</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.3398522786944085</v>
+        <v>0.3621311333790302</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.2874585574962438</v>
+        <v>0.305472097887332</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3653625194466912</v>
+        <v>0.3797411079953292</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.2251311650107368</v>
+        <v>0.2685872762852739</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1608123447367831</v>
+        <v>0.1463667193968945</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.03161663658755032</v>
+        <v>0.01871092642986127</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.08050089445438147</v>
+        <v>-0.0919011277105426</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.0377071584716262</v>
+        <v>0.05283132126502466</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.002117288038633092</v>
+        <v>-0.0157167214029883</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.05053229521591618</v>
+        <v>0.03658543263215108</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.06169965075670092</v>
+        <v>-0.0748745278071965</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1224550290490569</v>
+        <v>-0.1353944307197779</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.2064184913114886</v>
+        <v>-0.2180470441640381</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.07005939208812606</v>
+        <v>-0.08208997720141298</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.1152438913945204</v>
+        <v>-0.1260989465267528</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1118353323844588</v>
+        <v>-0.123485410484669</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.01044471103547551</v>
+        <v>-0.001400356274693593</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.02501930752523407</v>
+        <v>-0.03656815671732971</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.05975711691027641</v>
+        <v>-0.0420599899314098</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.01587827424993549</v>
+        <v>0.03184320885909386</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.01393010825983509</v>
+        <v>0.06349129804096521</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.110850969410393</v>
+        <v>-0.03189784418135133</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1688465587429988</v>
+        <v>-0.08723175566969132</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.01803</t>
+          <t>X &gt; -0.018</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3325</v>
+        <v>3349</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1984119245124631</v>
+        <v>0.1940280761598672</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.3579086644286136</v>
+        <v>0.3793691356812303</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2515289375429859</v>
+        <v>0.2683450345906948</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3626374695052448</v>
+        <v>0.3750557988873311</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.3129640279031634</v>
+        <v>0.3536576010871002</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.2007976982960926</v>
+        <v>0.1709015265403977</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1040363929111265</v>
+        <v>0.07573786128484983</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.03734434057481906</v>
+        <v>-0.06376651250351983</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.08117524764370643</v>
+        <v>0.1107707474605419</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1340652827366284</v>
+        <v>0.1344745596131958</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1858933716248004</v>
+        <v>0.1859055450680387</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.01441662134399024</v>
+        <v>0.01567171614577489</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.04217586629386716</v>
+        <v>-0.04042802091934306</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1255807739694461</v>
+        <v>-0.1223622340415957</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.01390051147942017</v>
+        <v>0.01703415546242582</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.09375937593759431</v>
+        <v>-0.08904668091723522</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.08980858446555828</v>
+        <v>-0.0859778506158122</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.06338547770611314</v>
+        <v>0.06698859727257656</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.03310397011183852</v>
+        <v>-0.02883109089597014</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.06870950905955908</v>
+        <v>-0.03523952382074924</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.05259071064622844</v>
+        <v>0.0115114339997362</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.05034960470428018</v>
+        <v>0.04359969530367636</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1787991976508891</v>
+        <v>-0.08306294613886678</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.2367454852083455</v>
+        <v>-0.1379656524742501</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01667</t>
+          <t>X &gt; -0.01664</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3310</v>
+        <v>3334</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1106534868081326</v>
+        <v>0.1064647225894291</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3023706844355658</v>
+        <v>0.3235045768291585</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.292062744892938</v>
+        <v>0.3069958812388052</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3768575105825747</v>
+        <v>0.387029646517334</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.3284779318125999</v>
+        <v>0.3667720311752376</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1248191179099791</v>
+        <v>0.09300097131288254</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.06113621111148149</v>
+        <v>0.03078892487243934</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.01950803395376255</v>
+        <v>-0.04828670500313592</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.09936443318240862</v>
+        <v>0.1264639335998439</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1559865004210721</v>
+        <v>0.1538451719163945</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2369113235609959</v>
+        <v>0.2341698861358168</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.06593430469182948</v>
+        <v>0.06442723659916538</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.04428612942121646</v>
+        <v>0.04298538928778584</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.06859119646903622</v>
+        <v>-0.06808222361470939</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.04438251390387649</v>
+        <v>0.04510343947031004</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.03630335908817273</v>
+        <v>-0.03404223938211715</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.03171178529970575</v>
+        <v>-0.0304767784096569</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.06235339215817959</v>
+        <v>0.06390980701404203</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.02478197012704442</v>
+        <v>0.02659347089102226</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.0419879877384588</v>
+        <v>-0.01074950325842394</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.006852421304834877</v>
+        <v>0.06873667239500492</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.009465130248656806</v>
+        <v>0.1013243302778761</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.09058943093911154</v>
+        <v>0.002998500749633592</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.1786394951576966</v>
+        <v>-0.08138992671167244</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.01531</t>
+          <t>X &gt; -0.01528</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3284</v>
+        <v>3308</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1401571212927735</v>
+        <v>0.1349475739008099</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2149963605328935</v>
+        <v>0.2354904602095544</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2764296784124127</v>
+        <v>0.2887038452582047</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3372237887423708</v>
+        <v>0.3439374431780422</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.2910952849319202</v>
+        <v>0.3256620104149448</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.05407600767374987</v>
+        <v>0.01844554125218423</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.004049744597573124</v>
+        <v>-0.03805821535951992</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.05285412262156086</v>
+        <v>-0.08530378566480579</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.03630590781472876</v>
+        <v>0.05970876924006063</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.09944857020191478</v>
+        <v>0.09351459994300626</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2394943993397689</v>
+        <v>0.2325415127827313</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.09970811623360021</v>
+        <v>0.09375554805178865</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.0260639273037313</v>
+        <v>0.0206291678494992</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1466813348001494</v>
+        <v>-0.1496476158063516</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.002724489775168593</v>
+        <v>-0.0001046190532534297</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.05292904746124094</v>
+        <v>-0.05412873584234035</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.04724826042710362</v>
+        <v>-0.04972662141779693</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.01240617827677681</v>
+        <v>-0.01391282171763208</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.05200398901185821</v>
+        <v>-0.05322857386048696</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.09038915244998691</v>
+        <v>-0.06238011894718909</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.03688563119570887</v>
+        <v>0.02217055896755937</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.03366543978789593</v>
+        <v>0.0555905245731978</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.1366974413669695</v>
+        <v>-0.04543603085129888</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2248582763213278</v>
+        <v>-0.1292280011765854</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01395</t>
+          <t>X &gt; -0.01393</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3258</v>
+        <v>3280</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1419472733892633</v>
+        <v>0.1358473863308234</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.4033812758898634</v>
+        <v>0.4210363937869843</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4166378694680617</v>
+        <v>0.4248123221764075</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4535556915002132</v>
+        <v>0.455279226394822</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.3315056769682059</v>
+        <v>0.3785967786540567</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.06045659589000962</v>
+        <v>0.006812914907825984</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1008050650995713</v>
+        <v>-0.1040831503083552</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.08672983762127728</v>
+        <v>-0.08848015522773522</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.002798545502628258</v>
+        <v>0.05667660777929484</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.04201211541935379</v>
+        <v>0.06717733009255511</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1504034671517118</v>
+        <v>0.1746961457202332</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.04227588441150232</v>
+        <v>0.06744129956329914</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.02303853009370016</v>
+        <v>0.003170320878631117</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1648145230679674</v>
+        <v>-0.1360531664456701</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.03959659442539021</v>
+        <v>-0.009829986946684244</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1004379372413666</v>
+        <v>-0.06909708219227184</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.06303217711855069</v>
+        <v>-0.03335424906196494</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.00355499342595067</v>
+        <v>0.03433414397616019</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.03807369619710244</v>
+        <v>-0.007130021090418381</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.1089058476842055</v>
+        <v>-0.04862583084560157</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.05065569189313379</v>
+        <v>0.04148976309362951</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.07748398210723906</v>
+        <v>0.0453727478509478</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.2142254016390339</v>
+        <v>-0.08907676609728554</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.2411210650419022</v>
+        <v>-0.1112376157104578</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01259</t>
+          <t>X &gt; -0.01257</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3219</v>
+        <v>3238</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.0033777167100979</v>
+        <v>-0.04569421277317076</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2412435580977359</v>
+        <v>0.2771307503923381</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2414868290512615</v>
+        <v>0.2667784730293761</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3494462964060006</v>
+        <v>0.3803308475790317</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1063915271044777</v>
+        <v>0.1526744454938509</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1084970008630606</v>
+        <v>-0.1952863396474598</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.231295762033163</v>
+        <v>-0.2359723555486966</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1518027929988008</v>
+        <v>-0.1548100195918352</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.0310929192599616</v>
+        <v>0.08277134838758826</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.08036634815314159</v>
+        <v>0.1036968209705122</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2176687560958186</v>
+        <v>0.239858650788868</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1426347145683806</v>
+        <v>0.1655813126486336</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.00245230293334231</v>
+        <v>0.02258587346572938</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2671549682849346</v>
+        <v>-0.2383747260306208</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.07028159848842819</v>
+        <v>-0.04013136297187003</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.1082586559957903</v>
+        <v>-0.1074373639989616</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.1307458896201794</v>
+        <v>-0.1315324858757023</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.03103545565691235</v>
+        <v>-0.03045140890183973</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.0138169201080629</v>
+        <v>-0.01357875436489309</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.1188771478465966</v>
+        <v>-0.0583940901643345</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.02212283755377342</v>
+        <v>0.04023978694186781</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.06692254003708342</v>
+        <v>0.04514704987997931</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.2396971482975871</v>
+        <v>-0.1250788622360588</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.234942281953245</v>
+        <v>-0.1145519169201776</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01123</t>
+          <t>X &gt; -0.01121</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3183</v>
+        <v>3200</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.04709711343197398</v>
+        <v>-0.06652492798645682</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1975552066927406</v>
+        <v>0.2319569670765631</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2148748628270027</v>
+        <v>0.2052195392628917</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.5202594476456497</v>
+        <v>0.5134384584670926</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.1531896507317754</v>
+        <v>0.1931922376976729</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.03519605556996908</v>
+        <v>-0.1296428386403861</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2441169008616342</v>
+        <v>-0.2546519221942205</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1603748872136634</v>
+        <v>-0.1689334711722879</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.02419999626852842</v>
+        <v>0.06993955153922116</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1145618074611221</v>
+        <v>0.1316342503136951</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2815658817235658</v>
+        <v>0.297319004628612</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1594090244703708</v>
+        <v>0.194319697551407</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.03699204342735385</v>
+        <v>0.0005490519403181793</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.3022113555761621</v>
+        <v>-0.2605690694463618</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.09543185402240795</v>
+        <v>-0.05190722088919131</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.07803814247840535</v>
+        <v>-0.06431888170808264</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.09922263866943126</v>
+        <v>-0.08745517617711585</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.02850501444918763</v>
+        <v>-0.01477872982368922</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.01359293365165115</v>
+        <v>-0.0002439008967414225</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.09064697596119231</v>
+        <v>-0.04813162521651293</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.01786177751904461</v>
+        <v>0.05840772827039586</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.03089366857638964</v>
+        <v>0.09550138089222315</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.2275244837325303</v>
+        <v>-0.07962185730002602</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.221854345955883</v>
+        <v>-0.0670302986372846</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.009872</t>
+          <t>X &gt; -0.009849</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3131</v>
+        <v>3147</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1710969780546989</v>
+        <v>0.1359334234523928</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2982877501184404</v>
+        <v>0.3175940419972818</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4032674015521422</v>
+        <v>0.4070093011185918</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5665667717317717</v>
+        <v>0.5413053645536507</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.1035902896455383</v>
+        <v>0.1393649179772254</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.0274085481044466</v>
+        <v>-0.1460395486945103</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.258816691454264</v>
+        <v>-0.2598294576244768</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1372862299544337</v>
+        <v>-0.1675670028499709</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.01784660743764732</v>
+        <v>0.04154049312490571</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1543204733556109</v>
+        <v>0.1808790227197719</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2240538915005956</v>
+        <v>0.2498555748122371</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1681634501665812</v>
+        <v>0.1814091062542076</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1084285965936971</v>
+        <v>-0.06023787646385159</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3425446080766079</v>
+        <v>-0.3215915512575407</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.05771040534295224</v>
+        <v>-0.03461784030124448</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.04576366147932021</v>
+        <v>0.03842544606204257</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.03728757606219801</v>
+        <v>-0.0467329845698643</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.1320555563305348</v>
+        <v>0.1245592027990696</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.1117760726622734</v>
+        <v>0.1040506262142955</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.03345461290042806</v>
+        <v>-0.01169074344029042</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.01429188463188069</v>
+        <v>0.0427081609005171</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.05820936583663183</v>
+        <v>0.04993006937665712</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.2626618564197187</v>
+        <v>-0.1322578863046218</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.2237106624439988</v>
+        <v>-0.08496404506245625</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.008512</t>
+          <t>X &gt; -0.00849</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3068</v>
+        <v>3082</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2651496450769457</v>
+        <v>0.2613706929081019</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.4018079948329998</v>
+        <v>0.4520339950375103</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4410440323756788</v>
+        <v>0.4729013665520156</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3302492235082752</v>
+        <v>0.3321120709696004</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.05935167763199445</v>
+        <v>0.1210700599025216</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1105932329610866</v>
+        <v>-0.2058673018413231</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.2985055768125022</v>
+        <v>-0.337655223368408</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.2337281009638943</v>
+        <v>-0.2693633745925581</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.0763020056419208</v>
+        <v>-0.05858496749816311</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.07874847363428472</v>
+        <v>0.100359578295766</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2092524817361436</v>
+        <v>0.2296617137460117</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.03700829273199702</v>
+        <v>-0.02834241068685373</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2313355557668544</v>
+        <v>-0.2193747208408325</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.5307780452947739</v>
+        <v>-0.5133971898495346</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.1616448672497199</v>
+        <v>-0.1414019582215857</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.1007965142643101</v>
+        <v>-0.1110265462037958</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.1503111453988168</v>
+        <v>-0.1634664670335653</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.04048606049562409</v>
+        <v>-0.08295966647420983</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.0005412869467420478</v>
+        <v>-0.04369520163098883</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.1526231570625569</v>
+        <v>-0.166442097463225</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.08938467385147675</v>
+        <v>-0.06657639570981644</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.1000628281572844</v>
+        <v>-0.02522812425655019</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.3469305725015701</v>
+        <v>-0.2488541651976419</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.3382443431746438</v>
+        <v>-0.2296276380272886</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.007151</t>
+          <t>X &gt; -0.007131</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3000</v>
+        <v>3010</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.6363412154804919</v>
+        <v>0.6157891134735607</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5517392722978229</v>
+        <v>0.5858474200085766</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7907366012310177</v>
+        <v>0.8022148706215546</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5610897107501316</v>
+        <v>0.5730887616415998</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2916782624311907</v>
+        <v>0.3966059187681594</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.01399127893017038</v>
+        <v>-0.07393735766439846</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.06097765056257742</v>
+        <v>-0.05776059320701421</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.02146452947897615</v>
+        <v>-0.04658996727734888</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1054773574725445</v>
+        <v>0.166234038898331</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.315083133785194</v>
+        <v>0.3149221475095061</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4756074130435763</v>
+        <v>0.5070504143755983</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1968580095955801</v>
+        <v>0.2495807017439944</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.004237650948169858</v>
+        <v>0.08065889448236874</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2304086791657838</v>
+        <v>-0.181243287019754</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.0955436441099522</v>
+        <v>0.1497552324769487</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.1111413536563219</v>
+        <v>0.1344263030437531</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06360719116249669</v>
+        <v>0.08329535410452138</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.1783627660689504</v>
+        <v>0.1358216861735002</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.2143962773884098</v>
+        <v>0.1709748881533244</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.154642140556625</v>
+        <v>0.1397763232917768</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.1650651028005754</v>
+        <v>0.189310977267688</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.08921914139147447</v>
+        <v>0.1671282608386093</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.202783986846228</v>
+        <v>-0.1340302947164673</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.2588006230529558</v>
+        <v>-0.1768724913283179</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.005791</t>
+          <t>X &gt; -0.005773</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2888</v>
+        <v>2897</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6979958617746505</v>
+        <v>0.6226115303741508</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.7264084685144709</v>
+        <v>0.7039218545668788</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.5822219599315375</v>
+        <v>0.5999970341224241</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.474575029396334</v>
+        <v>0.4878692778527878</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2421971731882522</v>
+        <v>0.3495324070502051</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2602540829756563</v>
+        <v>-0.3168616027321534</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2738435803785961</v>
+        <v>-0.2693089571763068</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.1876503608660727</v>
+        <v>-0.2116203969963095</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.05746434106434606</v>
+        <v>0.004441286196474437</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1900570532484949</v>
+        <v>0.1897469772467346</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.311630353312637</v>
+        <v>0.3443572930252969</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.136436352004786</v>
+        <v>0.1907022899868807</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.05472709559003164</v>
+        <v>0.02413115901121898</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2553881078715534</v>
+        <v>-0.2039220459870421</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.1086276800353332</v>
+        <v>0.1664651862065583</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.170938828506209</v>
+        <v>0.1975586962918428</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.05763718955784469</v>
+        <v>0.0796315426997225</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.1808951203480831</v>
+        <v>0.1393737602649594</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.3137319699444419</v>
+        <v>0.2709231139437378</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.1406491624036477</v>
+        <v>0.1267725470500523</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.2071186977197286</v>
+        <v>0.2348263875014993</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.09665868300498204</v>
+        <v>0.1802298157549629</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.1134633507919531</v>
+        <v>-0.03864734299516925</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.1686805861185192</v>
+        <v>-0.07680333971426023</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.004431</t>
+          <t>X &gt; -0.004414</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2753</v>
+        <v>2762</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.5333487665824848</v>
+        <v>0.4832539332840753</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5599742089265689</v>
+        <v>0.5444401866350077</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4070367210382742</v>
+        <v>0.3524557875313619</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.148267395874683</v>
+        <v>0.1197658189389657</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.04285761555142642</v>
+        <v>0.06003501696913105</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5068860044992505</v>
+        <v>-0.5743982835076054</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.4108419216626586</v>
+        <v>-0.4140359430540741</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.3791269814559257</v>
+        <v>-0.4107723330185635</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1722592514363015</v>
+        <v>-0.1184777465172999</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.161672224939224</v>
+        <v>0.1505312230321181</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1460866824523492</v>
+        <v>0.1912970162536851</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.06025142483344581</v>
+        <v>0.007520195683412112</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1696553454187466</v>
+        <v>-0.07688715920863842</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.2607033611727658</v>
+        <v>-0.1957688644592324</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.1170755286498917</v>
+        <v>0.189811897536643</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.1895998769866196</v>
+        <v>0.2311743347093582</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.03146037208416175</v>
+        <v>0.00423212351028468</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.102934380654176</v>
+        <v>0.0733418100599792</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.1591056560600563</v>
+        <v>0.1285415902410065</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.03167043267041691</v>
+        <v>-0.03316930858952816</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.04434221894184986</v>
+        <v>-0.0006914774358364184</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.2291206422245864</v>
+        <v>-0.1267276709576066</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.4993082391107251</v>
+        <v>-0.4045067585642457</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.444682691099942</v>
+        <v>-0.328118278362119</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.00307</t>
+          <t>X &gt; -0.003055</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.5629498644835778</v>
+        <v>0.5532001652433394</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7318538100314669</v>
+        <v>0.6760972827259266</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.8654268066290882</v>
+        <v>0.8129764317040724</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.5620420271116799</v>
+        <v>0.5684675456132879</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.3813504300975623</v>
+        <v>0.4861834681347545</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.4786007936538397</v>
+        <v>-0.5551821141161071</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.242406786578691</v>
+        <v>-0.2461654905079484</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.3434246847204392</v>
+        <v>-0.4350766531741073</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3574353077298227</v>
+        <v>-0.3240068614006049</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.2504435266784455</v>
+        <v>0.233906827132472</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.4080435415111836</v>
+        <v>0.4510939649051267</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.3233935169451669</v>
+        <v>0.3517095475573555</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.02337103438299692</v>
+        <v>-0.04363243978991704</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.01153065617119609</v>
+        <v>-0.03669486772542285</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.4407704772920766</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.2816627816627886</v>
+        <v>0.2370675320558746</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.1709680930923696</v>
+        <v>0.1173794284975429</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.2448888909040647</v>
+        <v>0.1238946103991267</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.2896224903042324</v>
+        <v>0.1673053476570487</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.08392773633478612</v>
+        <v>-0.177642067261047</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.01953665638985314</v>
+        <v>-0.06185394366159613</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.1343082698036255</v>
+        <v>-0.1139601075430292</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.4826439893963084</v>
+        <v>-0.4693353167894969</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.402773634600905</v>
+        <v>-0.336356436326902</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.00171</t>
+          <t>X &gt; -0.001696</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3513842201890967</v>
+        <v>0.3201268325281532</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.311385151662321</v>
+        <v>1.239519953665038</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.365286227442837</v>
+        <v>1.236444323935729</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7632518318395185</v>
+        <v>0.687201382788281</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.3410682707393278</v>
+        <v>0.3684839850281705</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.767861871457022</v>
+        <v>-0.898837911779097</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.459896948435933</v>
+        <v>-0.4854607095102992</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.4975779381318972</v>
+        <v>-0.6177441222758446</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.3264451209535721</v>
+        <v>-0.3359997925865699</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1358132838973063</v>
+        <v>0.07692971392120285</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2801712399373102</v>
+        <v>0.2876525510541512</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.04465573186328697</v>
+        <v>0.01107059658285436</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.002341049356495262</v>
+        <v>-0.04179135795683919</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.04066554515374321</v>
+        <v>-0.005287059191438459</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.1435285651074452</v>
+        <v>0.0733217792951919</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.158169754664776</v>
+        <v>0.05463675818396752</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.3530958500355084</v>
+        <v>0.2360660173160198</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.447456839569341</v>
+        <v>0.2588123362993429</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.5161020816938731</v>
+        <v>0.3257469550286487</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.007928282802225795</v>
+        <v>-0.1708244880066943</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.08235199733963583</v>
+        <v>-0.0189942303769044</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.1235893673652129</v>
+        <v>-0.1551689566543928</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.4128614024980877</v>
+        <v>-0.4500301932367066</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.3585982524256153</v>
+        <v>-0.3261217011557349</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003499</t>
+          <t>X &gt; -0.0003376</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1998</v>
+        <v>1994</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.5694169623029595</v>
+        <v>0.4952596128664695</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.131501150500235</v>
+        <v>1.046959955627216</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.665120748060609</v>
+        <v>1.487181107972916</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9023162799638271</v>
+        <v>0.8449284605106513</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.5665258074165536</v>
+        <v>0.6690712177193916</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.3432178768749026</v>
+        <v>-0.4701068412875102</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4671107282627602</v>
+        <v>-0.5174321237096535</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.4960699297456443</v>
+        <v>-0.6728012211561634</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.2053305045607488</v>
+        <v>-0.2457696195478292</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.0477282651428439</v>
+        <v>-0.0448121416864069</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.3716632190254643</v>
+        <v>0.3558406122187279</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.1926644390188628</v>
+        <v>0.1790092811888258</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.01713329485602344</v>
+        <v>-0.008883966171701729</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.4943087824991963</v>
+        <v>0.4414847668063615</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.8640598209348838</v>
+        <v>0.7874538683588312</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.8897638390898521</v>
+        <v>0.7795068686014659</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.7859962829359546</v>
+        <v>0.7055066216891603</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.061160381908181</v>
+        <v>0.8525325615050576</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.9074365704287004</v>
+        <v>0.7468847336233253</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.4741723253692172</v>
+        <v>0.3407403928689803</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.6121966728911588</v>
+        <v>0.5540465971262805</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.6364508115821579</v>
+        <v>0.6091144909349282</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.310324923463611</v>
+        <v>0.2813555628200959</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.03429247004013547</v>
+        <v>0.09890500728047158</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.00101</t>
+          <t>X &gt; 0.001021</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.3106152387771246</v>
+        <v>0.260365790592644</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.09593800483303</v>
+        <v>1.198997608255354</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.809271111416365</v>
+        <v>1.752283556239092</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.345383094464282</v>
+        <v>1.409257916034356</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.50772462689833</v>
+        <v>1.632452893142002</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.449360800542415</v>
+        <v>0.4178154268208871</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.07352188085728528</v>
+        <v>-0.06554588715746945</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.02186567812563567</v>
+        <v>-0.1210897719625947</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.06335286004033946</v>
+        <v>0.006839137721513566</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.09990169209849142</v>
+        <v>0.02126145796351864</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4362278348830841</v>
+        <v>0.4541600040075053</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.5310774351710776</v>
+        <v>0.4894932086129344</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.5909788801455917</v>
+        <v>0.4974956638384</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.054831510548318</v>
+        <v>0.9354749523740935</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.119716731413007</v>
+        <v>0.9148844453398013</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.565215748507526</v>
+        <v>1.326586272645265</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.843672231441595</v>
+        <v>1.635416666666671</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>2.151719971027468</v>
+        <v>1.853220491461286</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.031484040759743</v>
+        <v>1.793027329326684</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.506782380396729</v>
+        <v>1.294292567460602</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.377502316245582</v>
+        <v>1.265765805010787</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.676890876412465</v>
+        <v>1.667500856141821</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.138357458813225</v>
+        <v>1.071190878839133</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.8749079448019543</v>
+        <v>0.8213485463093519</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.002371</t>
+          <t>X &gt; 0.00238</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3405170804286684</v>
+        <v>-0.1597884442822135</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.3973133819475905</v>
+        <v>0.6669119807399895</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.84708311179449</v>
+        <v>1.969973654425964</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.9691125907015845</v>
+        <v>1.212554953967576</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.128371623104805</v>
+        <v>1.432046318818742</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2523189564743831</v>
+        <v>-0.06118509168482689</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.7767428878894904</v>
+        <v>-0.5262341006172164</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2298718243917364</v>
+        <v>-0.1710885374251845</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5184176457773688</v>
+        <v>-0.3731926310413982</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.2187260610877786</v>
+        <v>-0.09663686553466988</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2746994222261918</v>
+        <v>-0.1544348542306579</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3541419334017206</v>
+        <v>0.3940656995488609</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.716128381397084</v>
+        <v>0.6818138461245056</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.237623762376238</v>
+        <v>1.17615404211714</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1.404562973046509</v>
+        <v>1.3190821684829</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.586408640864079</v>
+        <v>1.517785930579947</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.915791343366848</v>
+        <v>1.877152203856745</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.688239404380411</v>
+        <v>2.539133057782976</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.707601996400577</v>
+        <v>2.556398762160775</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.455871784370245</v>
+        <v>1.247861266849839</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.658358728986983</v>
+        <v>1.559410364169878</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.913638595392456</v>
+        <v>2.064679019660694</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.525861652245375</v>
+        <v>1.529496662457156</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.367247942068452</v>
+        <v>1.417811894053742</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.003731</t>
+          <t>X &gt; 0.003739</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>925</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.6110366325314374</v>
+        <v>0.650921658986185</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.7068303401019662</v>
+        <v>0.7275954684435959</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.95987695307312</v>
+        <v>1.946019646121911</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.24692293363038</v>
+        <v>1.461144329034113</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.2652767022025984</v>
+        <v>0.5404248986122084</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7318260029809736</v>
+        <v>-0.4854371943144429</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.9655615544708951</v>
+        <v>-0.7428847979450097</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.1555811450171447</v>
+        <v>0.3500442210119559</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.125859552508409</v>
+        <v>0.04786560381434413</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2529194696643771</v>
+        <v>0.004502280638021716</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.02114017249754596</v>
+        <v>0.2767372952423557</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.3882465279300717</v>
+        <v>0.5377897493732107</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.8797238582752414</v>
+        <v>1.035800857728887</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.627428620149416</v>
+        <v>1.647781850059211</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.722783707929466</v>
+        <v>1.71831564021717</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.778957497472028</v>
+        <v>1.741985250434688</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.603282445049693</v>
+        <v>1.530577956989241</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.858966980227144</v>
+        <v>2.580489550752375</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.386486246454623</v>
+        <v>2.108006629339748</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.99157967769402</v>
+        <v>1.634167440606376</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.746330807025295</v>
+        <v>2.42643446695692</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.994809169940517</v>
+        <v>2.782771405627308</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.404419017557707</v>
+        <v>2.12170156822237</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.436694872442537</v>
+        <v>2.242091322984344</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.005091</t>
+          <t>X &gt; 0.005097</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.6609864549742426</v>
+        <v>0.5948206772189977</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.454559445058841</v>
+        <v>1.611185931276694</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.132196249342378</v>
+        <v>2.320026191236451</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.560285953453935</v>
+        <v>1.867876446846182</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.8013643102437555</v>
+        <v>1.031308489075037</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.001024431461026154</v>
+        <v>0.3467273685654035</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3477930817664188</v>
+        <v>-0.02759728041345966</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.361301538360614</v>
+        <v>0.6492494571035934</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.7255610681590952</v>
+        <v>-0.4850937229738719</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.216389297086984</v>
+        <v>-0.7201354005214</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.9423296549250608</v>
+        <v>-0.447900385917066</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9389916112644485</v>
+        <v>-0.5842298859704087</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.087541548360349</v>
+        <v>0.1241599040121883</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.9607730871817779</v>
+        <v>1.138197932340653</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.584717236709821</v>
+        <v>0.7365484592915124</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.8970167115442109</v>
+        <v>1.017347569275259</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.904143298121042</v>
+        <v>1.053719611968205</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.438437844871615</v>
+        <v>2.323360050986125</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.327804321489523</v>
+        <v>1.219803777414874</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.600797961133267</v>
+        <v>1.519133976325847</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.624824031127581</v>
+        <v>1.459207154864295</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.973907248188738</v>
+        <v>2.088269985021682</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.540166663220369</v>
+        <v>1.43140982400196</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.03090664795743</v>
+        <v>2.115533171038322</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.006451</t>
+          <t>X &gt; 0.006456</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.735496972589537</v>
+        <v>2.151323449825348</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.938354582841868</v>
+        <v>2.617160386363466</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.471661698685431</v>
+        <v>2.963889772016373</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.579496209708644</v>
+        <v>2.37148757320815</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.8852827980932645</v>
+        <v>1.562121603927316</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.7198657111498505</v>
+        <v>0.1176317223809136</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1210888307662472</v>
+        <v>0.9239731976926819</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.918146203217475</v>
+        <v>1.686668412647052</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.2948469016061708</v>
+        <v>0.391109777847177</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7093396385745692</v>
+        <v>-0.04906983125116682</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.4352799964126461</v>
+        <v>0.2231651833531672</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.3556064607925364</v>
+        <v>0.1245191719423744</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1341346981577942</v>
+        <v>0.4331145989755854</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.601227864721956</v>
+        <v>2.853919683449945</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>2.122296036675458</v>
+        <v>2.349701244625393</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>1.820625610948191</v>
+        <v>2.021325548142556</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.686708473970718</v>
+        <v>1.917445136417548</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.65713658735384</v>
+        <v>2.674240746558446</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.266862064145037</v>
+        <v>2.286067872429797</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>2.205073747303196</v>
+        <v>2.253009805138397</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>1.302815349121346</v>
+        <v>1.258143887964145</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>2.126249963251816</v>
+        <v>2.435217501965923</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.220868560625959</v>
+        <v>2.252142745831385</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.504748537618504</v>
+        <v>2.806849629678133</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.007812</t>
+          <t>X &gt; 0.007815</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.725224315139464</v>
+        <v>4.012928827444959</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.613661802503927</v>
+        <v>4.211466436185525</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.184571324901519</v>
+        <v>4.734550112071723</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.801974448315917</v>
+        <v>3.475481246596843</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.242969690054352</v>
+        <v>2.755478662053058</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.8674358761517311</v>
+        <v>1.579078934717813</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.434772906547103</v>
+        <v>2.117330255818423</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.826204318936874</v>
+        <v>2.479076479076475</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.1412370705769916</v>
+        <v>0.3847831665383623</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4677241751849124</v>
+        <v>0.03317611576346735</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.4759783241198718</v>
+        <v>0.9720777970344656</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.365271079328124</v>
+        <v>-1.08228193521461</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4795045747556728</v>
+        <v>-0.4193962748876032</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.308345120226306</v>
+        <v>1.332369663679287</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.650201822645748</v>
+        <v>0.6502152817942317</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.09469696969696884</v>
+        <v>-0.1218140327194348</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.2178144647541274</v>
+        <v>0.21875</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.452259475218668</v>
+        <v>1.419199228171735</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.9101211341870936</v>
+        <v>0.8779079289626424</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.5597532324146641</v>
+        <v>0.5565812337098208</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.103869168735216</v>
+        <v>-1.220315169236905</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.1655763496763001</v>
+        <v>0.04680418800243302</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.4568099243887218</v>
+        <v>-0.6044159128489426</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.08421168433846304</v>
+        <v>-0.09541396754109144</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.009172</t>
+          <t>X &gt; 0.009174</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.60770779986283</v>
+        <v>5.885944700460833</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.405878978391627</v>
+        <v>5.068609293328386</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.858033339765264</v>
+        <v>6.67105804857966</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.989009956160672</v>
+        <v>4.935798706914305</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.78616746049201</v>
+        <v>3.517383423957824</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.528046941387082</v>
+        <v>2.531459887098762</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.490202303739501</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.922973517945962</v>
+        <v>2.860028860028862</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.5193739946583591</v>
+        <v>1.273672055427241</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.253541681378131</v>
+        <v>0.4776205602079031</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.3095353018242477</v>
+        <v>1.035569860526529</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.414300806826056</v>
+        <v>-0.9552978082304833</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.06369319568198506</v>
+        <v>0.2155243600330294</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.021805070680486</v>
+        <v>3.110147441457066</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.496609749978539</v>
+        <v>1.570850202429156</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.934927307759672</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.957079534944057</v>
+        <v>2.02827380952381</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.719290854244264</v>
+        <v>2.752532561505063</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.246567005211311</v>
+        <v>2.285046364582065</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.853702670251799</v>
+        <v>2.101121463594879</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.1517362124306985</v>
+        <v>0.2683154066806708</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.10487575826798</v>
+        <v>2.210443951007811</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>1.799640325822494</v>
+        <v>1.877709560205489</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>2.303518217526758</v>
+        <v>2.580123880037064</v>
       </c>
     </row>
     <row r="29">
@@ -5070,79 +5070,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7.228718103959345</v>
+        <v>7.885944700460833</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.270752899812422</v>
+        <v>4.068609293328393</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.81824109715825</v>
+        <v>6.742486620008243</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.38064939655608</v>
+        <v>5.435798706914305</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.595583561689963</v>
+        <v>3.374526281100678</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2463178637293737</v>
+        <v>1.388602744241616</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.372919904476703</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.007751937984501</v>
+        <v>2.07431457431457</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.124673923579053</v>
+        <v>-0.2977565160013214</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.259908440195254</v>
+        <v>-1.45095086836352</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1742545951347836</v>
+        <v>0.6069984319551054</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.264598201481327</v>
+        <v>-1.812440665373337</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.576166065438898</v>
+        <v>-1.498761354252686</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.3766681015927702</v>
+        <v>0.3958617271713507</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.4431624851716336</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.04940711462450764</v>
+        <v>-0.08213149303689704</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.17899458897773</v>
+        <v>0.171130952380949</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1.885748088055095</v>
+        <v>1.82396113293364</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.961982024974155</v>
+        <v>1.898894430227898</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.6942823803967286</v>
+        <v>0.8938114495371536</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.9391728784783879</v>
+        <v>-0.5410979247106198</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>1.166799341930691</v>
+        <v>1.549804535283549</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>1.077637690776378</v>
+        <v>1.432428190237012</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>1.001805437553102</v>
+        <v>1.270289195947548</v>
       </c>
     </row>
     <row r="30">
@@ -5152,79 +5152,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8.677993466278174</v>
+        <v>9.314516129032256</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.961574155851068</v>
+        <v>5.735275959995057</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.939014044018137</v>
+        <v>6.861534239055857</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.810601087377336</v>
+        <v>3.888179659295254</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.5424434650716066</v>
+        <v>1.231669138243532</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.169141073468694</v>
+        <v>-0.992349636710756</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.889828117037091</v>
+        <v>2.974473112961284</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3207504774744407</v>
+        <v>0.764790764790753</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.728538657878573</v>
+        <v>-1.012042230287037</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.984546121354676</v>
+        <v>-2.284284201696849</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.22739469175314</v>
+        <v>-1.535858710902041</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.023052307761517</v>
+        <v>-1.336250189182863</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.696939012298799</v>
+        <v>-1.498761354252686</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.9805328358922907</v>
+        <v>1.110147441457066</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.1607022491278869</v>
+        <v>-0.04819741661846422</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.5324989020641198</v>
+        <v>-0.4392743501797511</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.666416039041593</v>
+        <v>-0.5431547619047592</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.6780186194560684</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.187048220914136</v>
+        <v>1.254076128363756</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.8884571376782802</v>
+        <v>0.99019367390121</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.1395259234916395</v>
+        <v>0.2295213477136997</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.2153718849007404</v>
+        <v>0.1543588257584148</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.029976613989085</v>
+        <v>1.359531772575252</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.4687074675619272</v>
+        <v>0.7166235475165621</v>
       </c>
     </row>
     <row r="31">
@@ -5234,79 +5234,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8.932252301772714</v>
+        <v>9.248070946308005</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6.258294216873189</v>
+        <v>6.676582715255293</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.574661132754478</v>
+        <v>7.166074659875349</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.107321148399457</v>
+        <v>4.82948641455549</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.8475540676650439</v>
+        <v>1.646951530270115</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.474251676062138</v>
+        <v>-1.684486956755059</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.186548178059212</v>
+        <v>3.91577986822152</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.153950768393855</v>
+        <v>1.866673378301286</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.195437950308559</v>
+        <v>1.994602287985394</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.1622730473653533</v>
+        <v>0.6171554439288442</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.866172559708843</v>
+        <v>2.6335765050448</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.1669628086514265</v>
+        <v>0.6128085040618814</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.049056411042159</v>
+        <v>1.823497781959937</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.582363499507849</v>
+        <v>3.319449767038464</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>1.339424880289869</v>
+        <v>2.055900036316196</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.7642211589580015</v>
+        <v>1.454413357461434</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>1.799894665255387</v>
+        <v>2.51332364341085</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>3.449439926346479</v>
+        <v>4.124625584760878</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.448613041016934</v>
+        <v>3.757692463069439</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.047223556867316</v>
+        <v>3.390883559291218</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.328206800665996</v>
+        <v>1.66064836023606</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1.252360839256895</v>
+        <v>1.585485838280775</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.115070845856593</v>
+        <v>2.410515672396365</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>1.451003298515673</v>
+        <v>1.666981329269689</v>
       </c>
     </row>
     <row r="32">
@@ -5316,79 +5316,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>10.26892732265826</v>
+        <v>10.63647774950135</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.926631727315964</v>
+        <v>7.4054962869318</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.240492377533087</v>
+        <v>6.897070841756637</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.023778959594111</v>
+        <v>4.812131329515573</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.43234938930248</v>
+        <v>2.297767219266994</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-2.140082920840747</v>
+        <v>-1.276642458317014</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.854885688501987</v>
+        <v>4.644693439898028</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.321035146004547</v>
+        <v>2.100967026340157</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.6106426286711368</v>
+        <v>1.482627279307849</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1622730473653533</v>
+        <v>0.6865757840885109</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.863666294044684</v>
+        <v>1.705079455409262</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.1669628086514265</v>
+        <v>0.6822288442215481</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.9655142222368127</v>
+        <v>1.80614269692002</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.000074443534587</v>
+        <v>3.796714605636176</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>2.341931145954028</v>
+        <v>3.11456022375112</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>1.432558669400777</v>
+        <v>2.183326929137941</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.554280630167661</v>
+        <v>4.318252487562191</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>4.201319625594607</v>
+        <v>4.931637039117007</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.665331307270804</v>
+        <v>4.399830609546363</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2.348417718742589</v>
+        <v>3.121879741172506</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.3021121522803227</v>
+        <v>1.061897926358931</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>1.730025589367457</v>
+        <v>2.479272717836487</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>1.252620602601397</v>
+        <v>1.976638546398448</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>1.176788349378121</v>
+        <v>1.814499552108984</v>
       </c>
     </row>
     <row r="33">
@@ -5398,79 +5398,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>10.57933637280657</v>
+        <v>11.00282781734395</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.492265996475098</v>
+        <v>8.029648254367345</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.054246947444106</v>
+        <v>6.774954152475765</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.423861735340822</v>
+        <v>5.273461044576642</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5.005502455454092</v>
+        <v>5.906993813568207</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3121185144118357</v>
+        <v>0.6093819650208374</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.337951150321679</v>
+        <v>6.177936316424493</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.307446127586942</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.348933309501646</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.576017633465156</v>
+        <v>2.47762056020791</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>3.684939660948181</v>
+        <v>4.568037392994057</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.406190257500185</v>
+        <v>4.29145543852276</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.283028190644067</v>
+        <v>3.176563321071988</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.814242892179138</v>
+        <v>5.655601986911613</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>3.238668401938021</v>
+        <v>4.064356695935643</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>1.99819293855991</v>
+        <v>2.807478896573485</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>2.781706994242995</v>
+        <v>3.612689393939398</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.511728675742916</v>
+        <v>5.29798710695961</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.810188864006683</v>
+        <v>4.60335842501447</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>3.079603481314166</v>
+        <v>3.908853960982555</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>1.619626120687577</v>
+        <v>2.4323185505109</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>2.461211351939035</v>
+        <v>3.266246937646535</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.01660751356057233</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-1.009870959444392</v>
+        <v>-0.2886212077281911</v>
       </c>
     </row>
     <row r="34">
@@ -5483,158 +5483,158 @@
         <v>84</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>7.073438600853741</v>
+        <v>7.17165898617511</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.357709421551554</v>
+        <v>4.544799769518868</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.919690372520563</v>
+        <v>3.290105667627287</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.587688734030195</v>
+        <v>5.078655849771437</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.632850642435308</v>
+        <v>7.184050090624488</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.8674358761517311</v>
+        <v>1.388602744241616</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.047868144642337</v>
+        <v>6.545901684389854</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.769656699889261</v>
+        <v>6.240981240981235</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.811143881803964</v>
+        <v>6.368910150665343</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.228704396243671</v>
+        <v>6.763334845922202</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.502764038405594</v>
+        <v>7.035569860526536</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.033538444481401</v>
+        <v>5.568511715579042</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.29132875857767</v>
+        <v>6.834571979080657</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.07024988213108</v>
+        <v>6.586337917647548</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>4.221630394074332</v>
+        <v>4.713707345286302</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>3.625541125541126</v>
+        <v>4.084535173629767</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>2.301147798087463</v>
+        <v>2.790178571428569</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>4.577259475218668</v>
+        <v>5.038246847219355</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2.412198475190607</v>
+        <v>2.871756693412742</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>1.408568094682437</v>
+        <v>1.895866947995529</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-1.514930454235966</v>
+        <v>-1.052529934337578</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.400300225168877</v>
+        <v>0.06278373418332706</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-1.316301703163013</v>
+        <v>-0.8840579710144851</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-1.392133956386289</v>
+        <v>-1.046196965303949</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.01869</t>
+          <t>X &gt; 0.01868</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.431616654683978</v>
+        <v>2.171658986175117</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.096839856334164</v>
+        <v>1.925752150471247</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.108096169622009</v>
+        <v>2.09962947715109</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.293692874816948</v>
+        <v>4.364370135485728</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.856453126907354</v>
+        <v>6.945954852529248</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2463178637293737</v>
+        <v>1.388602744241616</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>5.271470629114383</v>
+        <v>6.307806446294613</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4.993259184361307</v>
+        <v>6.002886002885994</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>5.034746366276011</v>
+        <v>6.130814912570102</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.711106052558357</v>
+        <v>6.763334845922202</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>5.98516569472028</v>
+        <v>7.035569860526536</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>7.155691653591134</v>
+        <v>6.758987906055239</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>4.583254224416166</v>
+        <v>5.644095788604467</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>5.811450710288426</v>
+        <v>6.824433155742774</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>3.704032050389017</v>
+        <v>4.713707345286302</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>2.849143610013172</v>
+        <v>3.846439935534526</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>4.164501835354535</v>
+        <v>3.742559523809518</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>5.508936493852204</v>
+        <v>6.466818275790772</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>2.826277150138843</v>
+        <v>3.824137645793691</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>3.01312296010687</v>
+        <v>2.610152662281251</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4279739324968403</v>
+        <v>-0.814434696242337</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>0.9454554684129093</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2293451814238878</v>
+        <v>-0.6459627329192443</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.3051774346471632</v>
+        <v>-0.8081017272087081</v>
       </c>
     </row>
   </sheetData>
@@ -5824,1887 +5824,1887 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.02075</t>
+          <t>X &lt; -0.02072</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-11.61186160618559</v>
+        <v>-10.68548387096774</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-17.74373985381077</v>
+        <v>-16.64567642095732</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-16.28320817820408</v>
+        <v>-15.04322766570605</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-21.34398828460334</v>
+        <v>-19.92134415022856</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-12.98412658323757</v>
+        <v>-11.62547371889932</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-8.449334310183666</v>
+        <v>-7.182825827186953</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.42418154479865</v>
+        <v>-2.263622125133956</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.094708459723627</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.211630445318185</v>
+        <v>-2.440613658858467</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.08599539671699574</v>
+        <v>-0.379522296934951</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.261211116873916</v>
+        <v>-1.535858710902041</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.807865566634618</v>
+        <v>3.901845048912378</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.583254224416166</v>
+        <v>4.215524360033029</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.260726072607255</v>
+        <v>6.824433155742774</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>2.254756688070181</v>
+        <v>1.856564488143441</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>2.849143610013172</v>
+        <v>3.846439935534526</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>1.26595111071687</v>
+        <v>2.313988095238095</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.737440317741999</v>
+        <v>-0.6760388670663602</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-2.970824299136517</v>
+        <v>-1.890148068492024</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-2.78397848916849</v>
+        <v>-1.67556162343304</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-4.775800019453357</v>
+        <v>-3.671577553385198</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-3.402370618543621</v>
+        <v>-2.31816864676906</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.2293451814238878</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>2.593373289990517</v>
+        <v>3.477612558505569</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.01939</t>
+          <t>X &lt; -0.01936</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>83</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-6.65289530620305</v>
+        <v>-6.554674920881681</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-14.21658776720347</v>
+        <v>-14.02949741923616</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-12.04014898490916</v>
+        <v>-11.66973368980243</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-16.3675608356772</v>
+        <v>-15.87659371993596</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10.6792549226823</v>
+        <v>-10.12805547449312</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-8.082650182368056</v>
+        <v>-7.561483314278171</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.830502480716241</v>
+        <v>-2.332468940968724</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.710563182964421</v>
+        <v>2.181887724056395</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.067226743554613</v>
+        <v>-2.509460474693235</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.430503865374227</v>
+        <v>-0.8958734156956965</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.56608277742918</v>
+        <v>-3.033276955308239</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.9744449275565614</v>
+        <v>1.509418198654203</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>3.465740692025747</v>
+        <v>4.008983912528734</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.85911964690446</v>
+        <v>7.375207682420928</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>1.381699240890157</v>
+        <v>1.873776192102127</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>3.18090543994159</v>
+        <v>3.639899488030231</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>3.046988302964117</v>
+        <v>3.536019076305223</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-1.87712950929081</v>
+        <v>-1.416142137290123</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.4564188512580429</v>
+        <v>0.003139366964092005</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.9352462358184184</v>
+        <v>1.422545089131511</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.8121192092560463</v>
+        <v>-0.3497186893576583</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.8879651706651472</v>
+        <v>-0.4248812113129432</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>3.00096737314221</v>
+        <v>3.433211105290738</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>5.334773674135796</v>
+        <v>5.680710665218136</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.01803</t>
+          <t>X &lt; -0.018</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-7.249094536112381</v>
+        <v>-7.150874150791012</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-12.73851050971993</v>
+        <v>-12.55142016175262</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-9.021890383493187</v>
+        <v>-8.651475088386462</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-13.85855574314211</v>
+        <v>-13.36758862740087</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-12.13249054558629</v>
+        <v>-11.58129109739711</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-8.358754600038736</v>
+        <v>-7.300646151192844</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.964036617262423</v>
+        <v>-3.97201682321937</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.03391472868216994</v>
+        <v>0.8777019086297315</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.15909421343413</v>
+        <v>-4.149008356943881</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.973676556137285</v>
+        <v>-5.975987687214776</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.782950247308698</v>
+        <v>-7.765608342713527</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.811699650756694</v>
+        <v>-1.856623286875546</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1901382823871884</v>
+        <v>0.1212681008283241</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.094059405940598</v>
+        <v>2.96581754454985</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-1.730750558306624</v>
+        <v>-1.840048177541398</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.988636363636367</v>
+        <v>1.814039346432907</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.854719226658894</v>
+        <v>1.710158934707898</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-3.458454810495624</v>
+        <v>-3.57736434571143</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.1175634295712982</v>
+        <v>-0.2701186134110145</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.110949047063393</v>
+        <v>0.9753956666995123</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.5684028790973628</v>
+        <v>0.407951165318778</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.4925569176882618</v>
+        <v>0.332788643363493</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>4.933698296836994</v>
+        <v>4.700134468848049</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>6.599851144661677</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01667</t>
+          <t>X &lt; -0.01664</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-9.332766768924635</v>
+        <v>-9.145676420957322</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-8.985071532241342</v>
+        <v>-8.614656237134618</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-12.37659698025551</v>
+        <v>-11.88562986451427</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-10.9266731670885</v>
+        <v>-10.37547371889932</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.92406991535406</v>
+        <v>-3.968540112901231</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.993315896541702</v>
+        <v>-2.085050696562533</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.5688246385920763</v>
+        <v>0.2886002886002785</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.130941060280975</v>
+        <v>-4.047756516001321</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.804757637218373</v>
+        <v>-5.736665154077798</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.233400697759151</v>
+        <v>-8.143001568044902</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.106744695801737</v>
+        <v>-3.062440665373344</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.428104960856054</v>
+        <v>-2.391618497109825</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.9544197663009655</v>
+        <v>0.9315760128856354</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-2.406426233982302</v>
+        <v>-2.429149797570851</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.01023751023750918</v>
+        <v>-0.08213149303689704</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.1441546472149824</v>
+        <v>-0.1860119047619051</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-2.951698053738866</v>
+        <v>-2.997467438494937</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-1.83490577191364</v>
+        <v>-1.890148068492024</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.1537418398561883</v>
+        <v>0.1101526622812514</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-1.289705229010742</v>
+        <v>-1.350148981956622</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-1.365551190419843</v>
+        <v>-1.425311503911907</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.611626224764905</v>
+        <v>1.496894409937887</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>4.238496674244338</v>
+        <v>4.013326844219854</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.01531</t>
+          <t>X &lt; -0.01528</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.424899274100625</v>
+        <v>-5.237808926133312</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-6.862918323131616</v>
+        <v>-6.492503028024892</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-9.025147704893193</v>
+        <v>-8.534180589151951</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-7.91166281512163</v>
+        <v>-7.36046336693245</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.260822726559425</v>
+        <v>-1.406428311659006</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8429903885519678</v>
+        <v>-0.02759728041345966</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.3386521812934973</v>
+        <v>1.116757638496765</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.809641658689607</v>
+        <v>-1.653864176456807</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.312484342025364</v>
+        <v>-3.174553352835574</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.68805973635979</v>
+        <v>-6.525506744028334</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.317174103311437</v>
+        <v>-3.178900292702536</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.52062814097048</v>
+        <v>-1.395241685515622</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.63785502637856</v>
+        <v>2.704350340007785</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.9399963003990806</v>
+        <v>-0.8763547665149432</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.3843176288431849</v>
+        <v>0.4095869334641336</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.2504004918657117</v>
+        <v>0.3057065217391255</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.5843672192547444</v>
+        <v>-0.5518152645818901</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.3614511689688555</v>
+        <v>0.387284643723298</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.278223986236149</v>
+        <v>1.326508769941704</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.005750810970852172</v>
+        <v>0.03442658740154769</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.07009515043824877</v>
+        <v>-0.04073593455373725</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.394160583941613</v>
+        <v>2.376811594202898</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.508109352616138</v>
+        <v>4.388585643391693</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01395</t>
+          <t>X &lt; -0.01393</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.038437474877753</v>
+        <v>-2.940217089556384</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-8.192491381661299</v>
+        <v>-8.005401033693985</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-8.425691153583855</v>
+        <v>-8.055275858477131</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-9.741054811580817</v>
+        <v>-9.250087695839575</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-7.371478361893693</v>
+        <v>-7.116007281722041</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.007128583778574</v>
+        <v>-0.9349772901817843</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.234838638361296</v>
+        <v>1.281988890356573</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.9566271936082202</v>
+        <v>0.9770684469479534</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.8423764220230936</v>
+        <v>-1.3046411975848</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.615292098059584</v>
+        <v>-2.100692692804138</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.795220185959003</v>
+        <v>-4.238096232416666</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.619981859345657</v>
+        <v>-2.105039632671101</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2891561961404179</v>
+        <v>-0.810293195905011</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.557249589989674</v>
+        <v>1.953520935432969</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.0586154948631048</v>
+        <v>-0.5358623621147345</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1.266499349321442</v>
+        <v>0.6278512952591413</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.519085279828623</v>
+        <v>-0.07843875502008046</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.8127492890232304</v>
+        <v>-1.416142137290123</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.01663902441643472</v>
+        <v>-0.5992702715901217</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.43047869941514</v>
+        <v>0.8201354505772898</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.2744355989337635</v>
+        <v>-0.3497186893576583</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.8120865700400088</v>
+        <v>0.1775284272412705</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>3.540549012583405</v>
+        <v>2.830801466736524</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>4.078213691875469</v>
+        <v>3.271072111001274</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01259</t>
+          <t>X &lt; -0.01257</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.242788861004783</v>
+        <v>0.5243589178224184</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-4.027768013575233</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.957332281201126</v>
+        <v>-3.847055416902222</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-6.126596980255513</v>
+        <v>-6.116399095283498</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.316045989388151</v>
+        <v>-2.06503415845976</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.077519909765179</v>
+        <v>2.418822524461405</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.051152216891929</v>
+        <v>3.066048204536372</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.787719097262006</v>
+        <v>1.799589299589293</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.126458745453839</v>
+        <v>-1.437866406111212</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.899374421490329</v>
+        <v>-2.23391790133055</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.08836896652052</v>
+        <v>-4.365529040572369</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.889285857653249</v>
+        <v>-3.19980330273598</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.5641720624404059</v>
+        <v>-0.9493108048021384</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.648246598058826</v>
+        <v>3.12937821068784</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.5270491132861537</v>
+        <v>0.04337767495662348</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.121436035229145</v>
+        <v>1.085450924545519</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.480129735690092</v>
+        <v>1.462339743589737</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.1025434804463572</v>
+        <v>-0.1128520538795499</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.3792629369604583</v>
+        <v>-0.3791590575030099</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.285415385322842</v>
+        <v>0.796965849094434</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.2423524575200346</v>
+        <v>-0.2512478830555267</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.4719298549819939</v>
+        <v>0.1543588257584148</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>3.221652092216523</v>
+        <v>2.801839464882953</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>3.145819838993248</v>
+        <v>2.639700470593489</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01123</t>
+          <t>X &lt; -0.01121</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.4575135423057404</v>
+        <v>0.7083854176383895</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.746115715060476</v>
+        <v>-2.776387814826613</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.954626567370148</v>
+        <v>-2.411648718337631</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.356105176976826</v>
+        <v>-6.855142059636222</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.552922432226659</v>
+        <v>-2.252651419247748</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.07707415926739003</v>
+        <v>1.156314707075531</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.703667393802583</v>
+        <v>2.80025708508672</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.595580430377311</v>
+        <v>1.682328511596793</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.8525589437245884</v>
+        <v>-1.03527103400365</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.040412379097177</v>
+        <v>-2.23782659426363</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.255979292951849</v>
+        <v>-4.404615969903205</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.645032984090022</v>
+        <v>-3.055181664211901</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.01819505094614726</v>
+        <v>-0.511537196296814</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.510726072607262</v>
+        <v>2.898765327635928</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.7692494416933684</v>
+        <v>0.1840906205476145</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>0.3388905743266335</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.8130525599922223</v>
+        <v>0.6415142276422685</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.1251214771622884</v>
+        <v>-0.3043780076006257</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.3258967629046339</v>
+        <v>-0.4964198454955095</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.6942823803967286</v>
+        <v>0.531174729644782</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2649304542359658</v>
+        <v>-0.4427738367766025</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.09147376571480947</v>
+        <v>-0.5179363587318875</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2.535238913083482</v>
+        <v>1.758218451749741</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2.459406659860207</v>
+        <v>1.596079457460277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.009872</t>
+          <t>X &lt; -0.009849</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.951657924242781</v>
+        <v>-1.55587176122318</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.299948236106104</v>
+        <v>-3.126281908185327</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.400129447299264</v>
+        <v>-4.049850182262333</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-6.464434818093352</v>
+        <v>-5.8017428213249</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.547133215514648</v>
+        <v>-1.244521337946942</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1529722871135775</v>
+        <v>1.10193289235437</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.338295578414474</v>
+        <v>2.313539843332364</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.036193348678474</v>
+        <v>1.339723078853503</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.6288041110450564</v>
+        <v>-0.5390369746730883</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.084313643736834</v>
+        <v>-2.338432951497779</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.83414478655785</v>
+        <v>-3.069542418498798</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.239781842537518</v>
+        <v>-2.342779891364742</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.7466451317022518</v>
+        <v>0.2212577570707808</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.265292282652922</v>
+        <v>2.983057140453724</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.2098887110997651</v>
+        <v>-0.04023436517714885</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.9080531340805322</v>
+        <v>-0.8167229884979648</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.01457301078402651</v>
+        <v>0.08274108138238745</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.831742481728504</v>
+        <v>-1.722383826454809</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.615851100804178</v>
+        <v>-1.507921599309036</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.05914227713751075</v>
+        <v>0.04445748789042625</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.259222691678886</v>
+        <v>-0.1885388529551904</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.2133472956951366</v>
+        <v>0.07074678562464243</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.419330480745032</v>
+        <v>1.986622073578602</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>1.99867064131486</v>
+        <v>1.490034918754027</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.008512</t>
+          <t>X &lt; -0.00849</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.387365219281548</v>
+        <v>-2.316468689963457</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.557796613731639</v>
+        <v>-3.652293781798122</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.881609534628929</v>
+        <v>-3.817069627558908</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.201805893904535</v>
+        <v>-2.903389427355798</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.8757952740318302</v>
+        <v>-0.8426948539286769</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5873238313338049</v>
+        <v>1.388602744241616</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.222292970752548</v>
+        <v>2.516597655085825</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.663182649594987</v>
+        <v>1.936951936951935</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3001754494872202</v>
+        <v>0.4165291982843868</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.034537979358262</v>
+        <v>-1.203698121110769</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.16497271921881</v>
+        <v>-2.305089480132807</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.03353063667218947</v>
+        <v>-0.1091439620766366</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.660208704922397</v>
+        <v>1.523216667725336</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.256031236926518</v>
+        <v>4.022235353544978</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.06267667174032</v>
+        <v>0.8675534991324483</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>0.6046816937762856</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.9597661750156945</v>
+        <v>1.050251831501825</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.009855048659304089</v>
+        <v>0.3679171768896765</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.3376338521065136</v>
+        <v>0.03292885458490247</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.9759725212417933</v>
+        <v>1.346416398544982</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.4334263532757632</v>
+        <v>0.7789718971642472</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.5278676521515422</v>
+        <v>0.7038093752089623</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>2.673311139141049</v>
+        <v>2.595795508838997</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>2.597478885917774</v>
+        <v>2.433656514549533</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.007151</t>
+          <t>X &lt; -0.007131</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.575426552684306</v>
+        <v>-4.339893242916972</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.902428780215381</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.647287820625856</v>
+        <v>-5.384913314908779</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-4.257438101750843</v>
+        <v>-4.037456348532537</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.36402679706508</v>
+        <v>-2.593110201409949</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4068766657664469</v>
+        <v>0.2090483536780496</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.1291006376395387</v>
+        <v>0.1020397359407497</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.1491108071135372</v>
+        <v>0.02647709069727</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.048800095787072</v>
+        <v>-1.221740788609452</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.527598124764737</v>
+        <v>-2.476507880159062</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.665303188485169</v>
+        <v>-3.809777452710698</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.693775122454809</v>
+        <v>-2.022139223695753</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3196134906624621</v>
+        <v>-0.8434533594951503</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.350560587973696</v>
+        <v>0.9725327625579823</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.962429045304269</v>
+        <v>-1.315126206483043</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.077261981517303</v>
+        <v>-1.212537783993653</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.7383658797240926</v>
+        <v>-0.8577025993883893</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.5524264417013</v>
+        <v>-1.219944502715116</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.809348299547651</v>
+        <v>-1.464197871899614</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.386095870194296</v>
+        <v>-1.020253628675505</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.455828799389636</v>
+        <v>-1.128982533725967</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.919370412485506</v>
+        <v>-0.7454294593509658</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>1.157965913622419</v>
+        <v>1.333067411248514</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>1.55719304282195</v>
+        <v>1.629644013289322</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.005791</t>
+          <t>X &lt; -0.005773</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>533</v>
+        <v>549</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.82603229861715</v>
+        <v>-3.361467307820739</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.607374143524609</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.191420738590544</v>
+        <v>-3.050474042517642</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.793263646922178</v>
+        <v>-2.641074510612277</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.545875393433583</v>
+        <v>-1.72936982279542</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.159522971212809</v>
+        <v>1.440645419235118</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.239408447914485</v>
+        <v>1.192011494434098</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.7749772638690473</v>
+        <v>0.8870910510254788</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.07158548861428216</v>
+        <v>-0.07787621415380386</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.259989405299294</v>
+        <v>-1.238226434327615</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.917028459599202</v>
+        <v>-2.058887594586665</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.9721474119507221</v>
+        <v>-1.242573374194578</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.06747473098531742</v>
+        <v>-0.3538225043957937</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.154807069492001</v>
+        <v>0.8551383339889469</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.8117474430418312</v>
+        <v>-1.102061585236733</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.151939960351172</v>
+        <v>-1.269355016325989</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.5381935459267808</v>
+        <v>-0.6446379781420788</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.203781913299359</v>
+        <v>-0.9596714457809057</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.922469971627372</v>
+        <v>-1.655956031021297</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.9879606102574741</v>
+        <v>-0.7127721360533812</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.343590890373036</v>
+        <v>-1.098067274956882</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.7480797864315889</v>
+        <v>-0.6267817094804826</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.3878884156612514</v>
+        <v>0.5275995881840601</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.6872906840139663</v>
+        <v>0.7297593188490552</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.004431</t>
+          <t>X &lt; -0.004414</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>668</v>
+        <v>684</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.237597482708189</v>
+        <v>-2.014242448634619</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.348404976870533</v>
+        <v>-2.114588876769339</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.715418108741765</v>
+        <v>-1.331437272692945</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.8011531932732581</v>
+        <v>-0.5335890481877499</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.01794300835834406</v>
+        <v>-0.1447646469493762</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.884816122018627</v>
+        <v>2.140482443489745</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.49646363038493</v>
+        <v>1.491599261666373</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.366840595735866</v>
+        <v>1.479076479076475</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5167973170264872</v>
+        <v>0.4374147454857322</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.8504719994260483</v>
+        <v>-0.7972332409616811</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7889026282610843</v>
+        <v>-0.9635947175854156</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.06050601243258313</v>
+        <v>-0.2167848591912218</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.516630819700616</v>
+        <v>0.1303113274515866</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.8925668686271635</v>
+        <v>0.6130714180652532</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.6610988170130909</v>
+        <v>-0.9462759462759394</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.9622342831298027</v>
+        <v>-1.11596607950306</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.05137530070429364</v>
+        <v>-0.1964546783625778</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.6039771985553273</v>
+        <v>-0.4755376139335254</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.835847011660853</v>
+        <v>-0.6996718780158275</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.05198627631969543</v>
+        <v>0.09970988868057873</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.00248248108741933</v>
+        <v>0.1170607089372737</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.7634836740410336</v>
+        <v>0.7728923390287719</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>1.877311071288084</v>
+        <v>1.893719806763293</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.651778219262411</v>
+        <v>1.585381982064469</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.00307</t>
+          <t>X &lt; -0.003055</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>852</v>
+        <v>875</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.728912003350857</v>
+        <v>-1.669754991447711</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.235484700644889</v>
+        <v>-1.915661827151581</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.629420222993744</v>
+        <v>-2.315954938433329</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.834253592784513</v>
+        <v>-1.710715188746349</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.29397862585737</v>
+        <v>-1.355379348577166</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.282718268178314</v>
+        <v>1.486338531829176</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5777755674484837</v>
+        <v>0.577231434077639</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.8816362996453506</v>
+        <v>1.136610725651821</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.9231234815600544</v>
+        <v>0.9220738819112668</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.8975221129863371</v>
+        <v>-0.8366651540778065</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.372693837052289</v>
+        <v>-1.478715853759184</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.118875846789372</v>
+        <v>-1.183869236801911</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.07271218490253517</v>
+        <v>-0.01304706853839122</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.1076949800243199</v>
+        <v>-0.03270970140007989</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.467592663569782</v>
+        <v>-1.400578368999419</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.9901648059542794</v>
+        <v>-0.8392743501797568</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.6562456856218191</v>
+        <v>-0.4860119047619023</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.8780454537704827</v>
+        <v>-0.5046102956377965</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.013031265828609</v>
+        <v>-0.6330052113491647</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.1094870587593064</v>
+        <v>0.4958669479955375</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.08218191622426474</v>
+        <v>0.2712795894719378</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.2632438809981821</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.311677976399309</v>
+        <v>1.582608695652176</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.072654776008072</v>
+        <v>1.191898272791292</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.00171</t>
+          <t>X &lt; -0.001696</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1115</v>
+        <v>1143</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.7570849128995789</v>
+        <v>-0.6780433947772622</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.732284657785335</v>
+        <v>-2.441878481277541</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.838154506105845</v>
+        <v>-2.434532013532142</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.686099644553913</v>
+        <v>-1.414568071650912</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.8179430083583483</v>
+        <v>-0.6847071683766686</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.464792256426257</v>
+        <v>1.699974023354834</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8333068080863484</v>
+        <v>0.8677665559929437</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.9112841433866947</v>
+        <v>1.137009521288988</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.559043041467838</v>
+        <v>0.6535847191827102</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3921257539982506</v>
+        <v>-0.2671346845473295</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.691067999315834</v>
+        <v>-0.6942003692437027</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.2045567936138326</v>
+        <v>-0.1339004828961521</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1142629687298822</v>
+        <v>-0.02394570620869274</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1930604509467031</v>
+        <v>-0.09720163990776598</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.4039765571140279</v>
+        <v>-0.2544216385907205</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.4357077031495677</v>
+        <v>-0.2180520029731596</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.8379611549749768</v>
+        <v>-0.5843996062992147</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.032247297078811</v>
+        <v>-0.6297946475938048</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.174137669285066</v>
+        <v>-0.7652886759160964</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.09283747649057261</v>
+        <v>0.3241884078130539</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.2776018913260074</v>
+        <v>0.1067001619003847</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.1475106628389682</v>
+        <v>0.4689829592801829</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.7446301964785604</v>
+        <v>1.06257370002664</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.6332771048992143</v>
+        <v>0.8129456418701579</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003499</t>
+          <t>X &lt; -0.0003376</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1423</v>
+        <v>1452</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8224755059163087</v>
+        <v>-0.7059896809472406</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.607935889497661</v>
+        <v>-1.394552715661256</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.349576108445085</v>
+        <v>-1.99736866502159</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.353077816492451</v>
+        <v>-1.183575069993729</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.883586894922729</v>
+        <v>-0.8734909518377378</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.3889192776072221</v>
+        <v>0.555759318805606</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.5643618929796617</v>
+        <v>0.6229353805038471</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.6059350267336256</v>
+        <v>0.838050838050826</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.1984232690833494</v>
+        <v>0.3183455949461447</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1549119873727136</v>
+        <v>-0.0258182293381708</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6101021017523678</v>
+        <v>-0.5788927057929811</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.3586184182637027</v>
+        <v>-0.3347098621091575</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.1098792368840122</v>
+        <v>-0.07313948816281624</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.7804146473553288</v>
+        <v>-0.6942602720415607</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.298305490517947</v>
+        <v>-1.16980308367868</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.335054613455732</v>
+        <v>-1.159463252186846</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.188466841597304</v>
+        <v>-1.056732093663911</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.573812454254387</v>
+        <v>-1.258486722241493</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.357921073330061</v>
+        <v>-1.112895018511693</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.750317900108179</v>
+        <v>-0.4850854329568435</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.9422329320293343</v>
+        <v>-0.708177317257686</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.9767413279257795</v>
+        <v>-0.7144693157969968</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.5204215533502818</v>
+        <v>-0.2642232602706898</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.1330568891574373</v>
+        <v>-0.01313911406428758</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.00101</t>
+          <t>X &lt; 0.001021</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1822</v>
+        <v>1853</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2929973583965833</v>
+        <v>-0.2450395967433039</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.9799812102567245</v>
+        <v>-0.9988339929990175</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.601006795235428</v>
+        <v>-1.473716125180012</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.249212784070224</v>
+        <v>-1.231763054632424</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.39150413764466</v>
+        <v>-1.370618418369645</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.4652739671964028</v>
+        <v>-0.4316737534542341</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.005885234438551379</v>
+        <v>-0.01356449046093644</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.08909859906265183</v>
+        <v>0.03487124046865375</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.125624268078937</v>
+        <v>-0.02196607058244382</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.1565178173000348</v>
+        <v>-0.08703461220588338</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.4525344923852828</v>
+        <v>-0.4613513217394782</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5357007454474427</v>
+        <v>-0.4916859483922025</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.5868332400662624</v>
+        <v>-0.497066177800221</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.9949816899498103</v>
+        <v>-0.8758212579493048</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.050385261502967</v>
+        <v>-0.8564106101527571</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.442299709422997</v>
+        <v>-1.212537783993653</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.685805887496365</v>
+        <v>-1.478317817952863</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.955030152961378</v>
+        <v>-1.66516846385921</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.848727813132946</v>
+        <v>-1.612605858947653</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.387909400425194</v>
+        <v>-1.128186710164975</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.272921321815879</v>
+        <v>-1.048032722608852</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.535951854241553</v>
+        <v>-1.339061407543085</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.064884625086577</v>
+        <v>-0.8255942185410277</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.8341390789622167</v>
+        <v>-0.6099674276173204</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.002371</t>
+          <t>X &lt; 0.00238</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2213</v>
+        <v>2242</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1673966141666057</v>
+        <v>0.06836130910694749</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2329076410511632</v>
+        <v>-0.3310867553038364</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.019024126732049</v>
+        <v>-1.029923896304716</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.5859958138131631</v>
+        <v>-0.6666857651353908</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6724413127668782</v>
+        <v>-0.7403047378581746</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.07841797891651225</v>
+        <v>-0.02601283556046496</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.3650289712371304</v>
+        <v>0.2254303594760643</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.06767703161744976</v>
+        <v>0.03463203463202547</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2248985923212672</v>
+        <v>0.1878561372413827</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.06264823018750576</v>
+        <v>-0.004585845486033691</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.09283733144917505</v>
+        <v>0.02622406613400585</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.2499031626882626</v>
+        <v>-0.2693799860704473</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.4461229788740724</v>
+        <v>-0.4233556908737484</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.7308617297060849</v>
+        <v>-0.69020906478179</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.8215230259952406</v>
+        <v>-0.7668352953098392</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.9221101406487122</v>
+        <v>-0.8742784900434586</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.101133276724056</v>
+        <v>-1.067325196908904</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.521715974230396</v>
+        <v>-1.423125039921601</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.531354588795473</v>
+        <v>-1.431578550626917</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.8483427887507702</v>
+        <v>-0.6819943347253101</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.9583720908183935</v>
+        <v>-0.8036073604038592</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.097924647398273</v>
+        <v>-1.031052551446002</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.8872140789534413</v>
+        <v>-0.7428150331613779</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.8009304618841071</v>
+        <v>-0.6819388624196208</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.003731</t>
+          <t>X &lt; 0.003739</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2496</v>
+        <v>2521</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2412447277460856</v>
+        <v>-0.253930390969991</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.276339902235236</v>
+        <v>-0.2424342730343199</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.7379565302516866</v>
+        <v>-0.6876896286544181</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5135396554147462</v>
+        <v>-0.5488790758707367</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1501612481034655</v>
+        <v>-0.1715430341994022</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2186026376770656</v>
+        <v>0.1257771720237884</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.3061573511180669</v>
+        <v>0.2212913033246764</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.1086754942324006</v>
+        <v>-0.1796912934353685</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.004477141236286286</v>
+        <v>-0.0293702203530728</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.04354876974726096</v>
+        <v>-0.05202370856679295</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.05839934910510181</v>
+        <v>-0.1524773631078844</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.1942875101816099</v>
+        <v>-0.2482453670008198</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.3754330320355095</v>
+        <v>-0.4303007290053458</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.652942992140936</v>
+        <v>-0.6554899298810142</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.6878343914400418</v>
+        <v>-0.6809178315170996</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.7096969696969708</v>
+        <v>-0.690576138724019</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.6436141066744412</v>
+        <v>-0.6127997423701927</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.10845481049563</v>
+        <v>-1.000044758082559</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.9325634295712959</v>
+        <v>-0.8252336015156914</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.7857176196032682</v>
+        <v>-0.6106471564567073</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.064750382207158</v>
+        <v>-0.8608830932061977</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.157096138089692</v>
+        <v>-0.9524974278649978</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.9391824934446902</v>
+        <v>-0.7088629425866202</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.9514288281811645</v>
+        <v>-0.7520015402080915</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.005091</t>
+          <t>X &lt; 0.005097</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2715</v>
+        <v>2737</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1856368757719977</v>
+        <v>-0.1681709951642958</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3911323243640794</v>
+        <v>-0.3947041627255388</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.5654907471281732</v>
+        <v>-0.5769967288868756</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4530977123199378</v>
+        <v>-0.4957824253569854</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.2558696937401734</v>
+        <v>-0.2425833534508186</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.04831503959918138</v>
+        <v>-0.1381148130102829</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.043139393486328</v>
+        <v>-0.0402455017573331</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.1408306622110018</v>
+        <v>-0.215479116897825</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.1416483608232895</v>
+        <v>0.1150112111768848</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.2702094795682655</v>
+        <v>0.14052554746673</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.1987011288380955</v>
+        <v>0.06959337524924081</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.1982122435164371</v>
+        <v>0.1053319081369395</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.02217350608140833</v>
+        <v>-0.07747855541886395</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.2949927615832806</v>
+        <v>-0.3408186540587934</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.1963881915296994</v>
+        <v>-0.2357560286847402</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.2785204991087298</v>
+        <v>-0.3094989814405054</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.280333488800224</v>
+        <v>-0.3189628953771262</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.6794000109369591</v>
+        <v>-0.6494389609483875</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.3899521754337485</v>
+        <v>-0.3619573836748273</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.4605539564918359</v>
+        <v>-0.4029386640630861</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.466365332823159</v>
+        <v>-0.3497186893576583</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.5571609083453524</v>
+        <v>-0.4763654536145125</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.4449222235361106</v>
+        <v>-0.3057769873280947</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.572612777749093</v>
+        <v>-0.482928179528777</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.006451</t>
+          <t>X &lt; 0.006456</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2865</v>
+        <v>2888</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3490938216786716</v>
+        <v>-0.4294516335113556</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3881022480036194</v>
+        <v>-0.485023584461409</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4899259011733861</v>
+        <v>-0.5509729324874542</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3513628491420846</v>
+        <v>-0.4703406083159223</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2167247185904344</v>
+        <v>-0.2790832853576717</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.09389494294401857</v>
+        <v>-0.06852042204763364</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.06820328392908692</v>
+        <v>-0.2239313781009074</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.2224205756197648</v>
+        <v>-0.371498233567209</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.01263962951235698</v>
+        <v>-0.08610717879145113</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.09384169203789128</v>
+        <v>-0.03445673447807707</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.04041553850493074</v>
+        <v>-0.08756244382772849</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.02525687098243878</v>
+        <v>-0.06816284374745152</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.06864738219179856</v>
+        <v>-0.1269380135174316</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.5476043601575569</v>
+        <v>-0.5968325170778286</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.4540560364867545</v>
+        <v>-0.4983809466499025</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.3962034134447947</v>
+        <v>-0.4353225619955978</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.3701646293225238</v>
+        <v>-0.4151713651562261</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.5589253577246254</v>
+        <v>-0.562346331228504</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.4824553779853815</v>
+        <v>-0.4862924085810008</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.4698863194987055</v>
+        <v>-0.4447163441448581</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.2945678321997036</v>
+        <v>-0.2163130946605349</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.4542806593376696</v>
+        <v>-0.4094508502007912</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.4730823498250274</v>
+        <v>-0.3735006847562659</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.5282596108365567</v>
+        <v>-0.4806383318782821</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.007812</t>
+          <t>X &lt; 0.007815</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2975</v>
+        <v>2999</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5700860987457119</v>
+        <v>-0.6111924783590226</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5532532940856214</v>
+        <v>-0.607619050892005</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6374238559363476</v>
+        <v>-0.6845932606679312</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4633828138672698</v>
+        <v>-0.5295290687583076</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3794997522680319</v>
+        <v>-0.3887999449121153</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1737830186278373</v>
+        <v>-0.2798018438709988</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2580722917328799</v>
+        <v>-0.3594924015551726</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3165482739035355</v>
+        <v>-0.4133537998079859</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.02171134864162383</v>
+        <v>-0.06741064135123054</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.02802526285612572</v>
+        <v>-0.04729638331368591</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.1138276753060126</v>
+        <v>-0.1879975325323926</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1627559606335893</v>
+        <v>0.1195502160856279</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.03095597675716277</v>
+        <v>0.02150089098461905</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.2373184016356618</v>
+        <v>-0.2404846277378851</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.1378598809089056</v>
+        <v>-0.1377307341051903</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.02655708375264965</v>
+        <v>-0.02268694291325346</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.07341276439256461</v>
+        <v>-0.0736242923742978</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.2589751193240915</v>
+        <v>-0.2534634411598304</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.1773569844554927</v>
+        <v>-0.1722457176782726</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.1247844205431932</v>
+        <v>-0.09090377628352542</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.124872545540164</v>
+        <v>0.2077409961532055</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.06519137477618386</v>
+        <v>0.05246971187330729</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.02778431834236272</v>
+        <v>0.1492753623188463</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.02798829812298465</v>
+        <v>0.07362075171283067</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.009172</t>
+          <t>X &lt; 0.009174</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3076</v>
+        <v>3099</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.6389103800555915</v>
+        <v>-0.6731172699509287</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.5045228462344795</v>
+        <v>-0.5492776305238962</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6655809453088963</v>
+        <v>-0.7281811466171746</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.4884709705624601</v>
+        <v>-0.5650265269019457</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.353790167734914</v>
+        <v>-0.3734672983535745</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2133456120012411</v>
+        <v>-0.3271509946335058</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.3203324344249907</v>
+        <v>-0.4298375351656247</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.2566716573999557</v>
+        <v>-0.3632542835627817</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.09962819401665257</v>
+        <v>-0.1528788928209082</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.01233523747968235</v>
+        <v>-0.09472670667311434</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.07569636129832702</v>
+        <v>-0.1578317844672696</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1177626103382252</v>
+        <v>0.06658121364854708</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.0468189437955786</v>
+        <v>-0.06421263936923793</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.3783879198292581</v>
+        <v>-0.3901745160445387</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.2067557463740712</v>
+        <v>-0.2161293236808106</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.1443645013220092</v>
+        <v>-0.151166839134099</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.2590326660514748</v>
+        <v>-0.2683055376517345</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.3446119023489231</v>
+        <v>-0.3499819452647657</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.2910054938361455</v>
+        <v>-0.2967060495180931</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.2472760611617133</v>
+        <v>-0.2433059358582028</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.05612348227537467</v>
+        <v>-0.004818780243439846</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.2749869419608615</v>
+        <v>-0.1898229518319425</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.241120249366034</v>
+        <v>-0.1528751753155575</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.2976389412150695</v>
+        <v>-0.2314180043488037</v>
       </c>
     </row>
     <row r="29">
@@ -7714,79 +7714,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3146</v>
+        <v>3169</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6421097396945967</v>
+        <v>-0.7047465148776055</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2970637602187907</v>
+        <v>-0.3380944170139699</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.5178754308064626</v>
+        <v>-0.5719380516489423</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4235954004766782</v>
+        <v>-0.488109462756583</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2676971873160596</v>
+        <v>-0.2753952259636918</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.06296473809333492</v>
+        <v>-0.1638021373089913</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.2478759594509157</v>
+        <v>-0.3444982078950503</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1284918667186474</v>
+        <v>-0.2232071999513963</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.05767793846460023</v>
+        <v>0.01683458293432238</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1576149918209211</v>
+        <v>0.08768345328967087</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.02487551646639474</v>
+        <v>-0.09380595397039571</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.1581293007795708</v>
+        <v>0.1195920596109303</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.09904195792584147</v>
+        <v>0.0930368381120843</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.07155073669014911</v>
+        <v>-0.07373165174193019</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.07676619982004951</v>
+        <v>-0.07594394830200457</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.03423867600842101</v>
+        <v>-0.03149687245899457</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.05412172088763612</v>
+        <v>-0.05375761634626031</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.2035357371855682</v>
+        <v>-0.1995481446739973</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.2097960541349266</v>
+        <v>-0.2057668759141009</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.0993684132540622</v>
+        <v>-0.08575798444907434</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.04376542805470507</v>
+        <v>0.07189209172378952</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.1401199141626464</v>
+        <v>-0.07912733488005586</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.1326347187333994</v>
+        <v>-0.06912632012069508</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.1259758720463893</v>
+        <v>-0.05482218882346501</v>
       </c>
     </row>
     <row r="30">
@@ -7796,79 +7796,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3215</v>
+        <v>3238</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5670133167065998</v>
+        <v>-0.6122799959841743</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.329146779519732</v>
+        <v>-0.3508417283325755</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3904590350013351</v>
+        <v>-0.4224109632191002</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2205982171138956</v>
+        <v>-0.2609369898213956</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.07513103461535309</v>
+        <v>-0.05865344240162074</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.09834110953221398</v>
+        <v>0.02325021109560055</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1609570753249514</v>
+        <v>-0.2320907914200134</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.01907984736121193</v>
+        <v>-0.08918920358035365</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.07112412041536231</v>
+        <v>0.05620050821099909</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1524077065640768</v>
+        <v>0.1083897909771423</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.1036317173643724</v>
+        <v>0.05979709528007504</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.09081119859234121</v>
+        <v>0.04716524595670535</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.07095223587555921</v>
+        <v>0.05872027714332972</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1007296759452529</v>
+        <v>-0.1098155899662245</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.02685149945876475</v>
+        <v>-0.03425655521997584</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.003526889001747691</v>
+        <v>-0.009469875985637088</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.005203030860485569</v>
+        <v>-0.002649938328708856</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.08112561794904138</v>
+        <v>-0.08645571733516277</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.1136814419936627</v>
+        <v>-0.1187547486717975</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.0947825465992338</v>
+        <v>-0.07111855030745318</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.0284999591044155</v>
+        <v>0.009385112458680567</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.02358130632997302</v>
+        <v>0.04514704987997931</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.1036151359988366</v>
+        <v>-0.0324576828597074</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.06761347945523966</v>
+        <v>0.008981128169381236</v>
       </c>
     </row>
     <row r="31">
@@ -7878,79 +7878,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3251</v>
+        <v>3274</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4786106331386577</v>
+        <v>-0.4944010684199682</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3387045963783635</v>
+        <v>-0.3297956997368061</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.3540281641145171</v>
+        <v>-0.3543050556908725</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2550373472279901</v>
+        <v>-0.2622236714359474</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.08429017534790972</v>
+        <v>-0.06545463079034874</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.08932781530194234</v>
+        <v>0.04768970831035801</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.2062312912752802</v>
+        <v>-0.2442619653909404</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.09961691280138041</v>
+        <v>-0.1369316262933395</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.1018583788246374</v>
+        <v>-0.1133756794465697</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.03004910515689119</v>
+        <v>-0.07104124027870995</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1366125212896918</v>
+        <v>-0.1768252891974953</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.02981736994737361</v>
+        <v>-0.07085297734621321</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.09255874306512624</v>
+        <v>-0.1332471120261118</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1728117597035705</v>
+        <v>-0.2114116328425624</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1070418542051641</v>
+        <v>-0.1446539096634467</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.07743177632680442</v>
+        <v>-0.1136889057643344</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.1317074441015293</v>
+        <v>-0.1691398709742984</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.2182828203236298</v>
+        <v>-0.2535649994705409</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.217379154387018</v>
+        <v>-0.2345910606934751</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.1966546395725501</v>
+        <v>-0.1851057705610728</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.1064076105563956</v>
+        <v>-0.06331215384729205</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.1024067056337898</v>
+        <v>-0.02879135739176775</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.147790018046166</v>
+        <v>-0.07235313640888563</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.1130403441644035</v>
+        <v>-0.03316499625487523</v>
       </c>
     </row>
     <row r="32">
@@ -7960,79 +7960,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3288</v>
+        <v>3312</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.4242962224624733</v>
+        <v>-0.4391784522485338</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2898233075521759</v>
+        <v>-0.279235423442536</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2610288780082968</v>
+        <v>-0.2577491178512687</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2015667505094356</v>
+        <v>-0.203456995366615</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.09710169531865631</v>
+        <v>-0.07210064346080003</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.04641781375435983</v>
+        <v>0.01151136715024137</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1941173030919785</v>
+        <v>-0.2261162246061232</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.09192522101469791</v>
+        <v>-0.1234876234876339</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.06338576656764161</v>
+        <v>-0.06867841045793455</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.03157076166928618</v>
+        <v>-0.06597535079629324</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.07316533364616618</v>
+        <v>-0.107287282330617</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.03139662045366265</v>
+        <v>-0.06583588627758274</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.07604086280831979</v>
+        <v>-0.1101710098994744</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1579114855087624</v>
+        <v>-0.190273991414692</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.130811219513788</v>
+        <v>-0.1621906200425656</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.09469696969696884</v>
+        <v>-0.1251607529336312</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.1802453661585091</v>
+        <v>-0.2112992116099264</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.206329734600061</v>
+        <v>-0.2360147561561732</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.184941200600754</v>
+        <v>-0.214795986145667</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.1319630631026598</v>
+        <v>-0.1332559194868068</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.04881073378625445</v>
+        <v>-0.01934743056683885</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.1064805696470899</v>
+        <v>-0.04642108232384601</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.08745808301504354</v>
+        <v>-0.02632580480058522</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.08434806830843655</v>
+        <v>-0.01962691699477404</v>
       </c>
     </row>
     <row r="33">
@@ -8042,79 +8042,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3312</v>
+        <v>3336</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.3574887925923846</v>
+        <v>-0.3720402440379544</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2563677630115393</v>
+        <v>-0.2447575066375762</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2081224087575606</v>
+        <v>-0.2025961494713187</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.184220029475199</v>
+        <v>-0.1827097214868516</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2030058857058208</v>
+        <v>-0.1734830865808235</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.02917502045916365</v>
+        <v>-0.05956149462029714</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2134859013317225</v>
+        <v>-0.2415523368846237</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1140429338103743</v>
+        <v>-0.141846353063535</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1154738347145638</v>
+        <v>-0.116360770594838</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.08948132663237374</v>
+        <v>-0.1193943651652205</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1588900969327511</v>
+        <v>-0.1883349298160013</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.1495456194690803</v>
+        <v>-0.1790561287630013</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1117350248652969</v>
+        <v>-0.1414691095986242</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1946221112177469</v>
+        <v>-0.22278740612213</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.142373563425565</v>
+        <v>-0.1699142647927161</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1022270901788929</v>
+        <v>-0.12912397423991</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.1278684001363217</v>
+        <v>-0.1555644879848472</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1846452866860986</v>
+        <v>-0.2109623517205534</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.1618428989713507</v>
+        <v>-0.1883479231121044</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.1380457257552621</v>
+        <v>-0.1357840357512572</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.08959108772013025</v>
+        <v>-0.05672280645497807</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.1172298455384535</v>
+        <v>-0.054195352238537</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.03599181283200181</v>
+        <v>0.02743938189730954</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.003245067497402943</v>
+        <v>0.06291574452817628</v>
       </c>
     </row>
     <row r="34">
@@ -8124,161 +8124,161 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3337</v>
+        <v>3362</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1884661610510179</v>
+        <v>-0.1895986631179838</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1203098302098908</v>
+        <v>-0.09468013591849456</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.08308905968114288</v>
+        <v>-0.06244138134305643</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1540024017628099</v>
+        <v>-0.1359255475420653</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2049381083450967</v>
+        <v>-0.1584521276541295</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.06081619964132301</v>
+        <v>-0.07378102583444957</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.189886348926116</v>
+        <v>-0.2013044487292674</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1827242524916954</v>
+        <v>-0.1935108507044632</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1838555499496479</v>
+        <v>-0.167251841522706</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1936855086887661</v>
+        <v>-0.2060287288916101</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.200860695069899</v>
+        <v>-0.2131073881507177</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1638196865882833</v>
+        <v>-0.1764003571338648</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1944196626546315</v>
+        <v>-0.2069905694489904</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1887311527686961</v>
+        <v>-0.2006473390886043</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.1417886136961428</v>
+        <v>-0.1534367832046186</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.1273950264981636</v>
+        <v>-0.1382993607774594</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.09404472868401115</v>
+        <v>-0.1059754378153741</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.1511709337382214</v>
+        <v>-0.1619567496588274</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.09699191550785713</v>
+        <v>-0.1081462864902392</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.07195527300045512</v>
+        <v>-0.05430706100199956</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.002035613628301292</v>
+        <v>0.04950077393384333</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.02593664325812739</v>
+        <v>0.05145934711578093</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.003140129366329347</v>
+        <v>0.07490723861977244</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.001164023312668405</v>
+        <v>0.07912526352809124</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.01869</t>
+          <t>X &lt; 0.01868</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3352</v>
+        <v>3376</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.04084711343196545</v>
+        <v>-0.05630722237361852</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.03371519808883505</v>
+        <v>-0.02161184515643555</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.03267646214690245</v>
+        <v>-0.02409313523799028</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1064309067086597</v>
+        <v>-0.0997052473175728</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1586200247398963</v>
+        <v>-0.1232645878242096</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.04396726077068536</v>
+        <v>-0.06774880050119947</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1462123370605894</v>
+        <v>-0.1685524438573722</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1403082362039427</v>
+        <v>-0.1620398731247903</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1412370705769916</v>
+        <v>-0.1353518313318176</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1544549280921288</v>
+        <v>-0.1772466964292505</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1603648089728935</v>
+        <v>-0.1831630147421919</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1841728968922425</v>
+        <v>-0.1772576665539773</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1304460173452</v>
+        <v>-0.1532807350785319</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1554944310611859</v>
+        <v>-0.1775076087496643</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1116887711401162</v>
+        <v>-0.133306792717498</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.09469696969696884</v>
+        <v>-0.115903867234799</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1216254195651842</v>
+        <v>-0.1136965464577884</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.1491933453377925</v>
+        <v>-0.1699984852128509</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.0942911626663232</v>
+        <v>-0.1155251758567104</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.09832786990124731</v>
+        <v>-0.0610223165860333</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.02710134345603876</v>
+        <v>0.0400023730511947</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.05529639179295742</v>
+        <v>0.04163850877522179</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.03138272513338336</v>
+        <v>0.06599631780201776</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.02976323244039492</v>
+        <v>0.06952183406413326</v>
       </c>
     </row>
   </sheetData>
